--- a/docs/handbook/sbmig-reference.xlsx
+++ b/docs/handbook/sbmig-reference.xlsx
@@ -36,7 +36,7 @@
     <definedName function="false" hidden="true" localSheetId="12" name="_xlnm._FilterDatabase" vbProcedure="false">재배치!$A$4:$F$48</definedName>
     <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">저널이벤트!$A$4:$B$75</definedName>
     <definedName function="false" hidden="true" localSheetId="13" name="_xlnm._FilterDatabase" vbProcedure="false">지식노트!$A$4:$F$20</definedName>
-    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">픽스처!$A$4:$N$31</definedName>
+    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">픽스처!$A$4:$N$32</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">핸들러!$A$4:$H$30</definedName>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">CLI!$A$4:$H$119</definedName>
     <definedName function="false" hidden="true" localSheetId="11" name="_xlnm._FilterDatabase" vbProcedure="false">Jakarta라이브러리!$A$4:$G$48</definedName>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4396" uniqueCount="2313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4406" uniqueCount="2316">
   <si>
     <r>
       <rPr>
@@ -4695,7 +4695,7 @@
     <t xml:space="preserve">`hystrix`</t>
   </si>
   <si>
-    <t xml:space="preserve">`guide`: no OpenRewrite migration; the 2.2.x starter stays at its as-is version (⚠ carried over)</t>
+    <t xml:space="preserve">`recipe` (round 6): the project composite `com.company.migrate.HystrixToResilience4j` swaps the starter and the annotations; programmatic `HystrixCommand` subclasses go to the advisory-guided LLM</t>
   </si>
   <si>
     <t xml:space="preserve">replace with Resilience4j: starter swap, `@HystrixCommand` → `@CircuitBreaker(name, fallbackMethod)`, `hystrix.*` → `resilience4j.*` properties</t>
@@ -6733,6 +6733,15 @@
   </si>
   <si>
     <t xml:space="preserve">junit4, jaxb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">servlet-nonstandard-dirs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">servlet-nonstandard-dirs — pom with non-standard top-level directories (`APP` / `STATIC` / `DB`) → company layout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E12, W1</t>
   </si>
   <si>
     <t xml:space="preserve">servlet-tomcat</t>
@@ -15759,8 +15768,8 @@
         <v>21</v>
       </c>
       <c r="C10" s="4" t="n">
-        <f aca="false">COUNTA(픽스처!A5:A5031)</f>
-        <v>27</v>
+        <f aca="false">COUNTA(픽스처!A5:A5032)</f>
+        <v>28</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>22</v>
@@ -15907,7 +15916,7 @@
       </c>
       <c r="C20" s="6" t="n">
         <f aca="false">SUM(C5:C19)</f>
-        <v>830</v>
+        <v>831</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15950,12 +15959,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1378</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>1379</v>
+        <v>1382</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -15969,31 +15978,31 @@
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>1380</v>
+        <v>1383</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1381</v>
+        <v>1384</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>1382</v>
+        <v>1385</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>1383</v>
+        <v>1386</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>1384</v>
+        <v>1387</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>1387</v>
+        <v>1390</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>1388</v>
+        <v>1391</v>
       </c>
       <c r="J4" s="10" t="s">
         <v>1108</v>
@@ -16001,13 +16010,13 @@
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>1389</v>
+        <v>1392</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>178</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>1390</v>
+        <v>1393</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>461</v>
@@ -16019,21 +16028,21 @@
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="12" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>1392</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>1393</v>
+        <v>1396</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>178</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>1390</v>
+        <v>1393</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>379</v>
@@ -16042,30 +16051,30 @@
         <v>878</v>
       </c>
       <c r="F6" s="12" t="s">
+        <v>1397</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>1398</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>1399</v>
+      </c>
+      <c r="I6" s="12" t="s">
         <v>1394</v>
       </c>
-      <c r="G6" s="12" t="s">
-        <v>1395</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>1396</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>1391</v>
-      </c>
       <c r="J6" s="12" t="s">
-        <v>1397</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>1398</v>
+        <v>1401</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>178</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>1390</v>
+        <v>1393</v>
       </c>
       <c r="D7" s="12" t="s">
         <v>461</v>
@@ -16074,28 +16083,28 @@
         <v>878</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>1399</v>
+        <v>1402</v>
       </c>
       <c r="G7" s="13"/>
       <c r="H7" s="12" t="s">
-        <v>1400</v>
+        <v>1403</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>1401</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>1402</v>
+        <v>1405</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>178</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>1390</v>
+        <v>1393</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>379</v>
@@ -16104,28 +16113,28 @@
         <v>878</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>1403</v>
+        <v>1406</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="12" t="s">
-        <v>1400</v>
+        <v>1403</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>1404</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>1405</v>
+        <v>1408</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>178</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>1406</v>
+        <v>1409</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>379</v>
@@ -16134,30 +16143,30 @@
         <v>878</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>1407</v>
+        <v>1410</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>1408</v>
+        <v>1411</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>1409</v>
+        <v>1412</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>1411</v>
+        <v>1414</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>178</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>1406</v>
+        <v>1409</v>
       </c>
       <c r="D10" s="12" t="s">
         <v>379</v>
@@ -16166,28 +16175,28 @@
         <v>878</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>1407</v>
+        <v>1410</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>1408</v>
+        <v>1411</v>
       </c>
       <c r="H10" s="13"/>
       <c r="I10" s="12" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>1412</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>1413</v>
+        <v>1416</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>178</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>1406</v>
+        <v>1409</v>
       </c>
       <c r="D11" s="12" t="s">
         <v>379</v>
@@ -16196,28 +16205,28 @@
         <v>878</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>1414</v>
+        <v>1417</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="12" t="s">
-        <v>1415</v>
+        <v>1418</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>1416</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>1417</v>
+        <v>1420</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>178</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>1406</v>
+        <v>1409</v>
       </c>
       <c r="D12" s="12" t="s">
         <v>379</v>
@@ -16226,28 +16235,28 @@
         <v>878</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>1418</v>
+        <v>1421</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>1419</v>
+        <v>1422</v>
       </c>
       <c r="H12" s="13"/>
       <c r="I12" s="12" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>1420</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>1421</v>
+        <v>1424</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>178</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>1406</v>
+        <v>1409</v>
       </c>
       <c r="D13" s="12" t="s">
         <v>379</v>
@@ -16256,28 +16265,28 @@
         <v>878</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>1422</v>
+        <v>1425</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>1423</v>
+        <v>1426</v>
       </c>
       <c r="H13" s="13"/>
       <c r="I13" s="12" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>1424</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>1425</v>
+        <v>1428</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>178</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>1426</v>
+        <v>1429</v>
       </c>
       <c r="D14" s="12" t="s">
         <v>379</v>
@@ -16286,30 +16295,30 @@
         <v>878</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>1427</v>
+        <v>1430</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>1428</v>
+        <v>1431</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>1429</v>
+        <v>1432</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>1430</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>1431</v>
+        <v>1434</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>178</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>1406</v>
+        <v>1409</v>
       </c>
       <c r="D15" s="12" t="s">
         <v>379</v>
@@ -16319,21 +16328,21 @@
       <c r="G15" s="13"/>
       <c r="H15" s="13"/>
       <c r="I15" s="12" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>1432</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>1433</v>
+        <v>1436</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>178</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>1406</v>
+        <v>1409</v>
       </c>
       <c r="D16" s="12" t="s">
         <v>379</v>
@@ -16342,24 +16351,24 @@
       <c r="F16" s="13"/>
       <c r="G16" s="13"/>
       <c r="H16" s="12" t="s">
-        <v>1434</v>
+        <v>1437</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>1435</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>1436</v>
+        <v>1439</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>178</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>1406</v>
+        <v>1409</v>
       </c>
       <c r="D17" s="12" t="s">
         <v>379</v>
@@ -16369,21 +16378,21 @@
       <c r="G17" s="13"/>
       <c r="H17" s="13"/>
       <c r="I17" s="12" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>1437</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>1438</v>
+        <v>1441</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>178</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>1406</v>
+        <v>1409</v>
       </c>
       <c r="D18" s="12" t="s">
         <v>379</v>
@@ -16393,21 +16402,21 @@
       <c r="G18" s="13"/>
       <c r="H18" s="13"/>
       <c r="I18" s="12" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>1439</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>1440</v>
+        <v>1443</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>178</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>1406</v>
+        <v>1409</v>
       </c>
       <c r="D19" s="12" t="s">
         <v>379</v>
@@ -16417,21 +16426,21 @@
       <c r="G19" s="13"/>
       <c r="H19" s="13"/>
       <c r="I19" s="12" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>1441</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>1442</v>
+        <v>1445</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>178</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>1406</v>
+        <v>1409</v>
       </c>
       <c r="D20" s="12" t="s">
         <v>379</v>
@@ -16441,21 +16450,21 @@
       <c r="G20" s="13"/>
       <c r="H20" s="13"/>
       <c r="I20" s="12" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>1443</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>1444</v>
+        <v>1447</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>178</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>1445</v>
+        <v>1448</v>
       </c>
       <c r="D21" s="12" t="s">
         <v>379</v>
@@ -16465,15 +16474,15 @@
       <c r="G21" s="13"/>
       <c r="H21" s="13"/>
       <c r="I21" s="12" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>950</v>
@@ -16485,19 +16494,19 @@
       <c r="E22" s="13"/>
       <c r="F22" s="13"/>
       <c r="G22" s="12" t="s">
-        <v>1408</v>
+        <v>1411</v>
       </c>
       <c r="H22" s="13"/>
       <c r="I22" s="12" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>1448</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>1449</v>
+        <v>1452</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>950</v>
@@ -16509,19 +16518,19 @@
       <c r="E23" s="13"/>
       <c r="F23" s="13"/>
       <c r="G23" s="12" t="s">
-        <v>1408</v>
+        <v>1411</v>
       </c>
       <c r="H23" s="13"/>
       <c r="I23" s="12" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>1450</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>1451</v>
+        <v>1454</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>950</v>
@@ -16535,15 +16544,15 @@
       <c r="G24" s="13"/>
       <c r="H24" s="13"/>
       <c r="I24" s="12" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>1452</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>1453</v>
+        <v>1456</v>
       </c>
       <c r="B25" s="12" t="s">
         <v>950</v>
@@ -16557,15 +16566,15 @@
       <c r="G25" s="13"/>
       <c r="H25" s="13"/>
       <c r="I25" s="12" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>1454</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>1455</v>
+        <v>1458</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>178</v>
@@ -16579,15 +16588,15 @@
       <c r="G26" s="13"/>
       <c r="H26" s="13"/>
       <c r="I26" s="12" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>1456</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>1457</v>
+        <v>1460</v>
       </c>
       <c r="B27" s="12" t="s">
         <v>178</v>
@@ -16601,15 +16610,15 @@
       <c r="G27" s="13"/>
       <c r="H27" s="13"/>
       <c r="I27" s="12" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>1458</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>1459</v>
+        <v>1462</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>178</v>
@@ -16623,21 +16632,21 @@
       <c r="G28" s="13"/>
       <c r="H28" s="13"/>
       <c r="I28" s="12" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>1460</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>1461</v>
+        <v>1464</v>
       </c>
       <c r="B29" s="12" t="s">
         <v>178</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>1462</v>
+        <v>1465</v>
       </c>
       <c r="D29" s="12" t="s">
         <v>379</v>
@@ -16647,21 +16656,21 @@
       <c r="G29" s="13"/>
       <c r="H29" s="13"/>
       <c r="I29" s="12" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>1463</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>1464</v>
+        <v>1467</v>
       </c>
       <c r="B30" s="12" t="s">
         <v>178</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>1462</v>
+        <v>1465</v>
       </c>
       <c r="D30" s="12" t="s">
         <v>379</v>
@@ -16671,15 +16680,15 @@
       <c r="G30" s="13"/>
       <c r="H30" s="13"/>
       <c r="I30" s="12" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>1465</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>1466</v>
+        <v>1469</v>
       </c>
       <c r="B31" s="12" t="s">
         <v>178</v>
@@ -16693,15 +16702,15 @@
       <c r="G31" s="13"/>
       <c r="H31" s="13"/>
       <c r="I31" s="12" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="J31" s="12" t="s">
-        <v>1467</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>1468</v>
+        <v>1471</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>178</v>
@@ -16715,15 +16724,15 @@
       <c r="G32" s="13"/>
       <c r="H32" s="13"/>
       <c r="I32" s="12" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>1469</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>1470</v>
+        <v>1473</v>
       </c>
       <c r="B33" s="12" t="s">
         <v>178</v>
@@ -16737,15 +16746,15 @@
       <c r="G33" s="13"/>
       <c r="H33" s="13"/>
       <c r="I33" s="12" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="J33" s="12" t="s">
-        <v>1471</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>1472</v>
+        <v>1475</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>178</v>
@@ -16759,15 +16768,15 @@
       <c r="G34" s="13"/>
       <c r="H34" s="13"/>
       <c r="I34" s="12" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="J34" s="12" t="s">
-        <v>1473</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>1474</v>
+        <v>1477</v>
       </c>
       <c r="B35" s="12" t="s">
         <v>178</v>
@@ -16781,15 +16790,15 @@
       <c r="G35" s="13"/>
       <c r="H35" s="13"/>
       <c r="I35" s="12" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="J35" s="12" t="s">
-        <v>1475</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>1476</v>
+        <v>1479</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>178</v>
@@ -16803,15 +16812,15 @@
       <c r="G36" s="13"/>
       <c r="H36" s="13"/>
       <c r="I36" s="12" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>1477</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>1478</v>
+        <v>1481</v>
       </c>
       <c r="B37" s="12" t="s">
         <v>178</v>
@@ -16825,15 +16834,15 @@
       <c r="G37" s="13"/>
       <c r="H37" s="13"/>
       <c r="I37" s="12" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="J37" s="12" t="s">
-        <v>1479</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>1480</v>
+        <v>1483</v>
       </c>
       <c r="B38" s="12" t="s">
         <v>178</v>
@@ -16847,10 +16856,10 @@
       <c r="G38" s="13"/>
       <c r="H38" s="13"/>
       <c r="I38" s="12" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="J38" s="12" t="s">
-        <v>1481</v>
+        <v>1484</v>
       </c>
     </row>
   </sheetData>
@@ -16892,12 +16901,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>1482</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>1483</v>
+        <v>1486</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -16912,48 +16921,48 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>1484</v>
+        <v>1487</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1485</v>
+        <v>1488</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>1382</v>
+        <v>1385</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>1486</v>
+        <v>1489</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>1487</v>
+        <v>1490</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>1488</v>
+        <v>1491</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>1489</v>
+        <v>1492</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>1490</v>
+        <v>1493</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>1491</v>
+        <v>1494</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>1492</v>
+        <v>1495</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>1493</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>1494</v>
+        <v>1497</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>1494</v>
+        <v>1497</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>1495</v>
+        <v>1498</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>794</v>
@@ -16962,28 +16971,28 @@
         <v>1001</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>1496</v>
+        <v>1499</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>1497</v>
+        <v>1500</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>1498</v>
+        <v>1501</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>1499</v>
+        <v>1502</v>
       </c>
       <c r="J5" s="13"/>
       <c r="K5" s="12" t="s">
-        <v>1500</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>1501</v>
+        <v>1504</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>1501</v>
+        <v>1504</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="12" t="s">
@@ -16993,28 +17002,28 @@
         <v>1001</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>1502</v>
+        <v>1505</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>1503</v>
+        <v>1506</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>1504</v>
+        <v>1507</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>1440</v>
+        <v>1443</v>
       </c>
       <c r="J6" s="13"/>
       <c r="K6" s="12" t="s">
-        <v>1505</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="C7" s="13"/>
       <c r="D7" s="12" t="s">
@@ -17024,115 +17033,115 @@
         <v>1001</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>1507</v>
+        <v>1510</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>1508</v>
+        <v>1511</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>1509</v>
+        <v>1512</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>1453</v>
+        <v>1456</v>
       </c>
       <c r="J7" s="13"/>
       <c r="K7" s="12" t="s">
-        <v>1510</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>1511</v>
+        <v>1514</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>1511</v>
+        <v>1514</v>
       </c>
       <c r="C8" s="13"/>
       <c r="D8" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E8" s="12" t="s">
+        <v>1515</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>1516</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>1517</v>
+      </c>
+      <c r="H8" s="12" t="s">
         <v>1512</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>1513</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>1514</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>1509</v>
       </c>
       <c r="I8" s="13"/>
       <c r="J8" s="13"/>
       <c r="K8" s="12" t="s">
-        <v>1515</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>1516</v>
+        <v>1519</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>1516</v>
+        <v>1519</v>
       </c>
       <c r="C9" s="13"/>
       <c r="D9" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E9" s="12" t="s">
+        <v>1515</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>1520</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>1521</v>
+      </c>
+      <c r="H9" s="12" t="s">
         <v>1512</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>1517</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>1518</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>1509</v>
       </c>
       <c r="I9" s="13"/>
       <c r="J9" s="13"/>
       <c r="K9" s="12" t="s">
-        <v>1519</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>1520</v>
+        <v>1523</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>1520</v>
+        <v>1523</v>
       </c>
       <c r="C10" s="13"/>
       <c r="D10" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E10" s="12" t="s">
+        <v>1515</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>1524</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>1525</v>
+      </c>
+      <c r="H10" s="12" t="s">
         <v>1512</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>1521</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>1522</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>1509</v>
       </c>
       <c r="I10" s="13"/>
       <c r="J10" s="13"/>
       <c r="K10" s="12" t="s">
-        <v>1523</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>1524</v>
+        <v>1527</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>1524</v>
+        <v>1527</v>
       </c>
       <c r="C11" s="13"/>
       <c r="D11" s="12" t="s">
@@ -17142,1072 +17151,1072 @@
         <v>1001</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>1525</v>
+        <v>1528</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>1526</v>
+        <v>1529</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>1527</v>
+        <v>1530</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>1442</v>
+        <v>1445</v>
       </c>
       <c r="J11" s="13"/>
       <c r="K11" s="12" t="s">
-        <v>1528</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>1529</v>
+        <v>1532</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>1529</v>
+        <v>1532</v>
       </c>
       <c r="C12" s="13"/>
       <c r="D12" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>1530</v>
+        <v>1533</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>1531</v>
+        <v>1534</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>1532</v>
+        <v>1535</v>
       </c>
       <c r="I12" s="13"/>
       <c r="J12" s="13"/>
       <c r="K12" s="12" t="s">
-        <v>1533</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>1534</v>
+        <v>1537</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>1534</v>
+        <v>1537</v>
       </c>
       <c r="C13" s="13"/>
       <c r="D13" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>1535</v>
+        <v>1538</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>1536</v>
+        <v>1539</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>1504</v>
+        <v>1507</v>
       </c>
       <c r="I13" s="13"/>
       <c r="J13" s="13"/>
       <c r="K13" s="12" t="s">
-        <v>1537</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>1538</v>
+        <v>1541</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>1538</v>
+        <v>1541</v>
       </c>
       <c r="C14" s="13"/>
       <c r="D14" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>1539</v>
+        <v>1542</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>1540</v>
+        <v>1543</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="I14" s="13"/>
       <c r="J14" s="13"/>
       <c r="K14" s="12" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="C15" s="13"/>
       <c r="D15" s="12" t="s">
         <v>817</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>1544</v>
+        <v>1547</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>1545</v>
+        <v>1548</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>1504</v>
+        <v>1507</v>
       </c>
       <c r="I15" s="13"/>
       <c r="J15" s="13"/>
       <c r="K15" s="12" t="s">
-        <v>1546</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>1547</v>
+        <v>1550</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>1547</v>
+        <v>1550</v>
       </c>
       <c r="C16" s="13"/>
       <c r="D16" s="12" t="s">
         <v>835</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>1548</v>
+        <v>1551</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>1549</v>
+        <v>1552</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>1550</v>
+        <v>1553</v>
       </c>
       <c r="I16" s="13"/>
       <c r="J16" s="13"/>
       <c r="K16" s="12" t="s">
-        <v>1551</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>1552</v>
+        <v>1555</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>1552</v>
+        <v>1555</v>
       </c>
       <c r="C17" s="13"/>
       <c r="D17" s="12" t="s">
         <v>835</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>1553</v>
+        <v>1556</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>1554</v>
+        <v>1557</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>1555</v>
+        <v>1558</v>
       </c>
       <c r="I17" s="13"/>
       <c r="J17" s="13"/>
       <c r="K17" s="12" t="s">
-        <v>1556</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>1557</v>
+        <v>1560</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>1557</v>
+        <v>1560</v>
       </c>
       <c r="C18" s="13"/>
       <c r="D18" s="12" t="s">
         <v>835</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>1558</v>
+        <v>1561</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>1559</v>
+        <v>1562</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>1560</v>
+        <v>1563</v>
       </c>
       <c r="I18" s="13"/>
       <c r="J18" s="13"/>
       <c r="K18" s="12" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="C19" s="13"/>
       <c r="D19" s="12" t="s">
         <v>835</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>1565</v>
+        <v>1568</v>
       </c>
       <c r="I19" s="13"/>
       <c r="J19" s="13"/>
       <c r="K19" s="12" t="s">
-        <v>1566</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>1567</v>
+        <v>1570</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>1567</v>
+        <v>1570</v>
       </c>
       <c r="C20" s="13"/>
       <c r="D20" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>1568</v>
+        <v>1571</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>1569</v>
+        <v>1572</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>1570</v>
+        <v>1573</v>
       </c>
       <c r="I20" s="13"/>
       <c r="J20" s="13"/>
       <c r="K20" s="12" t="s">
-        <v>1571</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>1572</v>
+        <v>1575</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>1572</v>
+        <v>1575</v>
       </c>
       <c r="C21" s="13"/>
       <c r="D21" s="12" t="s">
         <v>835</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>1573</v>
+        <v>1576</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>1574</v>
+        <v>1577</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>1575</v>
+        <v>1578</v>
       </c>
       <c r="I21" s="13"/>
       <c r="J21" s="13"/>
       <c r="K21" s="12" t="s">
-        <v>1576</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B22" s="13"/>
       <c r="C22" s="12" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="D22" s="12" t="s">
         <v>817</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>1579</v>
+        <v>1582</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>1581</v>
+        <v>1584</v>
       </c>
       <c r="I22" s="13"/>
       <c r="J22" s="13"/>
       <c r="K22" s="12" t="s">
-        <v>1582</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>1583</v>
+        <v>1586</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>1583</v>
+        <v>1586</v>
       </c>
       <c r="C23" s="13"/>
       <c r="D23" s="12" t="s">
         <v>835</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>1584</v>
+        <v>1587</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>1585</v>
+        <v>1588</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>1586</v>
+        <v>1589</v>
       </c>
       <c r="I23" s="13"/>
       <c r="J23" s="13"/>
       <c r="K23" s="12" t="s">
-        <v>1587</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>1588</v>
+        <v>1591</v>
       </c>
       <c r="B24" s="13"/>
       <c r="C24" s="12" t="s">
-        <v>1589</v>
+        <v>1592</v>
       </c>
       <c r="D24" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>1590</v>
+        <v>1593</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>1591</v>
+        <v>1594</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>1592</v>
+        <v>1595</v>
       </c>
       <c r="I24" s="13"/>
       <c r="J24" s="13"/>
       <c r="K24" s="12" t="s">
-        <v>1593</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>1594</v>
+        <v>1597</v>
       </c>
       <c r="B25" s="13"/>
       <c r="C25" s="12" t="s">
-        <v>1595</v>
+        <v>1598</v>
       </c>
       <c r="D25" s="12" t="s">
         <v>817</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>1596</v>
+        <v>1599</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>1597</v>
+        <v>1600</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>1598</v>
+        <v>1601</v>
       </c>
       <c r="I25" s="13"/>
       <c r="J25" s="13"/>
       <c r="K25" s="12" t="s">
-        <v>1599</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>1600</v>
+        <v>1603</v>
       </c>
       <c r="B26" s="13"/>
       <c r="C26" s="12" t="s">
-        <v>1601</v>
+        <v>1604</v>
       </c>
       <c r="D26" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>1602</v>
+        <v>1605</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>1603</v>
+        <v>1606</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>1604</v>
+        <v>1607</v>
       </c>
       <c r="I26" s="13"/>
       <c r="J26" s="13"/>
       <c r="K26" s="12" t="s">
-        <v>1605</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>1606</v>
+        <v>1609</v>
       </c>
       <c r="B27" s="13"/>
       <c r="C27" s="12" t="s">
-        <v>1607</v>
+        <v>1610</v>
       </c>
       <c r="D27" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>1608</v>
+        <v>1611</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>1609</v>
+        <v>1612</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>1604</v>
+        <v>1607</v>
       </c>
       <c r="I27" s="13"/>
       <c r="J27" s="13"/>
       <c r="K27" s="12" t="s">
-        <v>1610</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>1611</v>
+        <v>1614</v>
       </c>
       <c r="B28" s="13"/>
       <c r="C28" s="12" t="s">
-        <v>1612</v>
+        <v>1615</v>
       </c>
       <c r="D28" s="12" t="s">
         <v>835</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>1613</v>
+        <v>1616</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>1614</v>
+        <v>1617</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>1615</v>
+        <v>1618</v>
       </c>
       <c r="I28" s="13"/>
       <c r="J28" s="13"/>
       <c r="K28" s="12" t="s">
-        <v>1616</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>1617</v>
+        <v>1620</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>1617</v>
+        <v>1620</v>
       </c>
       <c r="C29" s="13"/>
       <c r="D29" s="12" t="s">
         <v>835</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>1618</v>
+        <v>1621</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>1620</v>
+        <v>1623</v>
       </c>
       <c r="I29" s="13"/>
       <c r="J29" s="13"/>
       <c r="K29" s="12" t="s">
-        <v>1621</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>1622</v>
+        <v>1625</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="12" t="s">
-        <v>1623</v>
+        <v>1626</v>
       </c>
       <c r="D30" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>1624</v>
+        <v>1627</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>1625</v>
+        <v>1628</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>1626</v>
+        <v>1629</v>
       </c>
       <c r="I30" s="13"/>
       <c r="J30" s="13"/>
       <c r="K30" s="12" t="s">
-        <v>1627</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>1628</v>
+        <v>1631</v>
       </c>
       <c r="B31" s="13"/>
       <c r="C31" s="12" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>1630</v>
+        <v>1633</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>1632</v>
+        <v>1635</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="I31" s="13"/>
       <c r="J31" s="13"/>
       <c r="K31" s="12" t="s">
-        <v>1634</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>1635</v>
+        <v>1638</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>1635</v>
+        <v>1638</v>
       </c>
       <c r="C32" s="13"/>
       <c r="D32" s="12" t="s">
         <v>835</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>1636</v>
+        <v>1639</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>1637</v>
+        <v>1640</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>1638</v>
+        <v>1641</v>
       </c>
       <c r="I32" s="13"/>
       <c r="J32" s="13"/>
       <c r="K32" s="12" t="s">
-        <v>1639</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>1640</v>
+        <v>1643</v>
       </c>
       <c r="B33" s="13"/>
       <c r="C33" s="12" t="s">
-        <v>1641</v>
+        <v>1644</v>
       </c>
       <c r="D33" s="12" t="s">
         <v>817</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>1642</v>
+        <v>1645</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
       <c r="I33" s="13"/>
       <c r="J33" s="13"/>
       <c r="K33" s="12" t="s">
-        <v>1645</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>1646</v>
+        <v>1649</v>
       </c>
       <c r="B34" s="13"/>
       <c r="C34" s="12" t="s">
-        <v>1647</v>
+        <v>1650</v>
       </c>
       <c r="D34" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>1648</v>
+        <v>1651</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>1649</v>
+        <v>1652</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>1650</v>
+        <v>1653</v>
       </c>
       <c r="I34" s="13"/>
       <c r="J34" s="13"/>
       <c r="K34" s="12" t="s">
-        <v>1651</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>1652</v>
+        <v>1655</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>1652</v>
+        <v>1655</v>
       </c>
       <c r="C35" s="13"/>
       <c r="D35" s="12" t="s">
         <v>835</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>1653</v>
+        <v>1656</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>1654</v>
+        <v>1657</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>1655</v>
+        <v>1658</v>
       </c>
       <c r="I35" s="13"/>
       <c r="J35" s="13"/>
       <c r="K35" s="12" t="s">
-        <v>1656</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>1657</v>
+        <v>1660</v>
       </c>
       <c r="B36" s="13"/>
       <c r="C36" s="12" t="s">
-        <v>1658</v>
+        <v>1661</v>
       </c>
       <c r="D36" s="12" t="s">
         <v>817</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>1659</v>
+        <v>1662</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>1660</v>
+        <v>1663</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>1661</v>
+        <v>1664</v>
       </c>
       <c r="I36" s="13"/>
       <c r="J36" s="13"/>
       <c r="K36" s="12" t="s">
-        <v>1662</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>1663</v>
+        <v>1666</v>
       </c>
       <c r="B37" s="13"/>
       <c r="C37" s="12" t="s">
-        <v>1664</v>
+        <v>1667</v>
       </c>
       <c r="D37" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>1665</v>
+        <v>1668</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>1666</v>
+        <v>1669</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>1667</v>
+        <v>1670</v>
       </c>
       <c r="I37" s="13"/>
       <c r="J37" s="13"/>
       <c r="K37" s="12" t="s">
-        <v>1668</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>1669</v>
+        <v>1672</v>
       </c>
       <c r="B38" s="13"/>
       <c r="C38" s="12" t="s">
-        <v>1670</v>
+        <v>1673</v>
       </c>
       <c r="D38" s="12" t="s">
         <v>817</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>1671</v>
+        <v>1674</v>
       </c>
       <c r="G38" s="12" t="s">
-        <v>1672</v>
+        <v>1675</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>1673</v>
+        <v>1676</v>
       </c>
       <c r="I38" s="13"/>
       <c r="J38" s="13"/>
       <c r="K38" s="12" t="s">
-        <v>1674</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>1675</v>
+        <v>1678</v>
       </c>
       <c r="B39" s="13"/>
       <c r="C39" s="12" t="s">
-        <v>1676</v>
+        <v>1679</v>
       </c>
       <c r="D39" s="12" t="s">
         <v>835</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>1677</v>
+        <v>1680</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>1678</v>
+        <v>1681</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>1679</v>
+        <v>1682</v>
       </c>
       <c r="I39" s="13"/>
       <c r="J39" s="13"/>
       <c r="K39" s="12" t="s">
-        <v>1680</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>1681</v>
+        <v>1684</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>1681</v>
+        <v>1684</v>
       </c>
       <c r="C40" s="13"/>
       <c r="D40" s="12" t="s">
         <v>835</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>1682</v>
+        <v>1685</v>
       </c>
       <c r="G40" s="12" t="s">
-        <v>1683</v>
+        <v>1686</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>1684</v>
+        <v>1687</v>
       </c>
       <c r="I40" s="13"/>
       <c r="J40" s="13"/>
       <c r="K40" s="12" t="s">
-        <v>1685</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>1686</v>
+        <v>1689</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>1686</v>
+        <v>1689</v>
       </c>
       <c r="C41" s="13"/>
       <c r="D41" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>1687</v>
+        <v>1690</v>
       </c>
       <c r="G41" s="12" t="s">
-        <v>1688</v>
+        <v>1691</v>
       </c>
       <c r="H41" s="12" t="s">
-        <v>1689</v>
+        <v>1692</v>
       </c>
       <c r="I41" s="13"/>
       <c r="J41" s="13"/>
       <c r="K41" s="12" t="s">
-        <v>1690</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>1691</v>
+        <v>1694</v>
       </c>
       <c r="B42" s="13"/>
       <c r="C42" s="12" t="s">
-        <v>1692</v>
+        <v>1695</v>
       </c>
       <c r="D42" s="12" t="s">
         <v>835</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>1693</v>
+        <v>1696</v>
       </c>
       <c r="G42" s="12" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="H42" s="12" t="s">
-        <v>1695</v>
+        <v>1698</v>
       </c>
       <c r="I42" s="13"/>
       <c r="J42" s="13"/>
       <c r="K42" s="12" t="s">
-        <v>1696</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>1697</v>
+        <v>1700</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>1698</v>
+        <v>1701</v>
       </c>
       <c r="C43" s="13"/>
       <c r="D43" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>1699</v>
+        <v>1702</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>1700</v>
+        <v>1703</v>
       </c>
       <c r="H43" s="12" t="s">
-        <v>1701</v>
+        <v>1704</v>
       </c>
       <c r="I43" s="13"/>
       <c r="J43" s="13"/>
       <c r="K43" s="12" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>1703</v>
+        <v>1706</v>
       </c>
       <c r="B44" s="13"/>
       <c r="C44" s="12" t="s">
-        <v>1704</v>
+        <v>1707</v>
       </c>
       <c r="D44" s="12" t="s">
         <v>835</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>1705</v>
+        <v>1708</v>
       </c>
       <c r="G44" s="12" t="s">
-        <v>1706</v>
+        <v>1709</v>
       </c>
       <c r="H44" s="12" t="s">
-        <v>1707</v>
+        <v>1710</v>
       </c>
       <c r="I44" s="13"/>
       <c r="J44" s="13"/>
       <c r="K44" s="12" t="s">
-        <v>1708</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>1709</v>
+        <v>1712</v>
       </c>
       <c r="B45" s="13"/>
       <c r="C45" s="12" t="s">
-        <v>1710</v>
+        <v>1713</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>1630</v>
+        <v>1633</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F45" s="12" t="s">
-        <v>1711</v>
+        <v>1714</v>
       </c>
       <c r="G45" s="12" t="s">
-        <v>1712</v>
+        <v>1715</v>
       </c>
       <c r="H45" s="12" t="s">
-        <v>1713</v>
+        <v>1716</v>
       </c>
       <c r="I45" s="13"/>
       <c r="J45" s="13"/>
       <c r="K45" s="12" t="s">
-        <v>1714</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>1715</v>
+        <v>1718</v>
       </c>
       <c r="B46" s="13"/>
       <c r="C46" s="12" t="s">
-        <v>1716</v>
+        <v>1719</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>1630</v>
+        <v>1633</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F46" s="12" t="s">
-        <v>1717</v>
+        <v>1720</v>
       </c>
       <c r="G46" s="12" t="s">
-        <v>1718</v>
+        <v>1721</v>
       </c>
       <c r="H46" s="12" t="s">
-        <v>1719</v>
+        <v>1722</v>
       </c>
       <c r="I46" s="13"/>
       <c r="J46" s="13"/>
       <c r="K46" s="12" t="s">
-        <v>1720</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>1721</v>
+        <v>1724</v>
       </c>
       <c r="B47" s="13"/>
       <c r="C47" s="12" t="s">
-        <v>1722</v>
+        <v>1725</v>
       </c>
       <c r="D47" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>1723</v>
+        <v>1726</v>
       </c>
       <c r="G47" s="12" t="s">
-        <v>1724</v>
+        <v>1727</v>
       </c>
       <c r="H47" s="12" t="s">
-        <v>1719</v>
+        <v>1722</v>
       </c>
       <c r="I47" s="13"/>
       <c r="J47" s="13"/>
       <c r="K47" s="12" t="s">
-        <v>1725</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="s">
-        <v>1726</v>
+        <v>1729</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>1726</v>
+        <v>1729</v>
       </c>
       <c r="C48" s="13"/>
       <c r="D48" s="12" t="s">
@@ -18217,600 +18226,600 @@
         <v>1001</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>1727</v>
+        <v>1730</v>
       </c>
       <c r="G48" s="12" t="s">
-        <v>1728</v>
+        <v>1731</v>
       </c>
       <c r="H48" s="12" t="s">
-        <v>1729</v>
+        <v>1732</v>
       </c>
       <c r="I48" s="12" t="s">
-        <v>1444</v>
+        <v>1447</v>
       </c>
       <c r="J48" s="13"/>
       <c r="K48" s="12" t="s">
-        <v>1730</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="12" t="s">
-        <v>1731</v>
+        <v>1734</v>
       </c>
       <c r="B49" s="13"/>
       <c r="C49" s="12" t="s">
-        <v>1732</v>
+        <v>1735</v>
       </c>
       <c r="D49" s="12" t="s">
         <v>817</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>1733</v>
+        <v>1736</v>
       </c>
       <c r="G49" s="12" t="s">
-        <v>1734</v>
+        <v>1737</v>
       </c>
       <c r="H49" s="12" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
       <c r="I49" s="13"/>
       <c r="J49" s="13"/>
       <c r="K49" s="12" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="12" t="s">
-        <v>1737</v>
+        <v>1740</v>
       </c>
       <c r="B50" s="13"/>
       <c r="C50" s="12" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
       <c r="D50" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>1739</v>
+        <v>1742</v>
       </c>
       <c r="G50" s="12" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
       <c r="H50" s="12" t="s">
-        <v>1741</v>
+        <v>1744</v>
       </c>
       <c r="I50" s="13"/>
       <c r="J50" s="13"/>
       <c r="K50" s="12" t="s">
-        <v>1742</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="12" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
       <c r="B51" s="13"/>
       <c r="C51" s="12" t="s">
-        <v>1744</v>
+        <v>1747</v>
       </c>
       <c r="D51" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F51" s="12" t="s">
-        <v>1745</v>
+        <v>1748</v>
       </c>
       <c r="G51" s="12" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
       <c r="H51" s="12" t="s">
-        <v>1747</v>
+        <v>1750</v>
       </c>
       <c r="I51" s="13"/>
       <c r="J51" s="13"/>
       <c r="K51" s="12" t="s">
-        <v>1748</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="12" t="s">
-        <v>1749</v>
+        <v>1752</v>
       </c>
       <c r="B52" s="13"/>
       <c r="C52" s="12" t="s">
-        <v>1750</v>
+        <v>1753</v>
       </c>
       <c r="D52" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F52" s="12" t="s">
-        <v>1751</v>
+        <v>1754</v>
       </c>
       <c r="G52" s="12" t="s">
-        <v>1752</v>
+        <v>1755</v>
       </c>
       <c r="H52" s="12" t="s">
-        <v>1753</v>
+        <v>1756</v>
       </c>
       <c r="I52" s="13"/>
       <c r="J52" s="13"/>
       <c r="K52" s="12" t="s">
-        <v>1754</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="12" t="s">
-        <v>1755</v>
+        <v>1758</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>1755</v>
+        <v>1758</v>
       </c>
       <c r="C53" s="13"/>
       <c r="D53" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F53" s="12" t="s">
-        <v>1756</v>
+        <v>1759</v>
       </c>
       <c r="G53" s="12" t="s">
-        <v>1757</v>
+        <v>1760</v>
       </c>
       <c r="H53" s="12" t="s">
-        <v>1758</v>
+        <v>1761</v>
       </c>
       <c r="I53" s="13"/>
       <c r="J53" s="13"/>
       <c r="K53" s="12" t="s">
-        <v>1759</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="12" t="s">
-        <v>1760</v>
+        <v>1763</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>1760</v>
+        <v>1763</v>
       </c>
       <c r="C54" s="13"/>
       <c r="D54" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F54" s="12" t="s">
-        <v>1761</v>
+        <v>1764</v>
       </c>
       <c r="G54" s="12" t="s">
-        <v>1762</v>
+        <v>1765</v>
       </c>
       <c r="H54" s="12" t="s">
-        <v>1763</v>
+        <v>1766</v>
       </c>
       <c r="I54" s="13"/>
       <c r="J54" s="13"/>
       <c r="K54" s="12" t="s">
-        <v>1764</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="12" t="s">
-        <v>1765</v>
+        <v>1768</v>
       </c>
       <c r="B55" s="13"/>
       <c r="C55" s="12" t="s">
-        <v>1766</v>
+        <v>1769</v>
       </c>
       <c r="D55" s="12" t="s">
         <v>835</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F55" s="12" t="s">
-        <v>1767</v>
+        <v>1770</v>
       </c>
       <c r="G55" s="12" t="s">
-        <v>1768</v>
+        <v>1771</v>
       </c>
       <c r="H55" s="12" t="s">
-        <v>1769</v>
+        <v>1772</v>
       </c>
       <c r="I55" s="13"/>
       <c r="J55" s="13"/>
       <c r="K55" s="12" t="s">
-        <v>1770</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="12" t="s">
-        <v>1771</v>
+        <v>1774</v>
       </c>
       <c r="B56" s="13"/>
       <c r="C56" s="12" t="s">
-        <v>1772</v>
+        <v>1775</v>
       </c>
       <c r="D56" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F56" s="12" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="G56" s="12" t="s">
-        <v>1774</v>
+        <v>1777</v>
       </c>
       <c r="H56" s="12" t="s">
-        <v>1775</v>
+        <v>1778</v>
       </c>
       <c r="I56" s="13"/>
       <c r="J56" s="13"/>
       <c r="K56" s="12" t="s">
-        <v>1776</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="12" t="s">
-        <v>1777</v>
+        <v>1780</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>1777</v>
+        <v>1780</v>
       </c>
       <c r="C57" s="13"/>
       <c r="D57" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F57" s="12" t="s">
-        <v>1778</v>
+        <v>1781</v>
       </c>
       <c r="G57" s="12" t="s">
-        <v>1779</v>
+        <v>1782</v>
       </c>
       <c r="H57" s="12" t="s">
-        <v>1780</v>
+        <v>1783</v>
       </c>
       <c r="I57" s="13"/>
       <c r="J57" s="13"/>
       <c r="K57" s="12" t="s">
-        <v>1781</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="12" t="s">
-        <v>1782</v>
+        <v>1785</v>
       </c>
       <c r="B58" s="13"/>
       <c r="C58" s="12" t="s">
-        <v>1783</v>
+        <v>1786</v>
       </c>
       <c r="D58" s="12" t="s">
         <v>835</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>1784</v>
+        <v>1787</v>
       </c>
       <c r="G58" s="12" t="s">
-        <v>1785</v>
+        <v>1788</v>
       </c>
       <c r="H58" s="12" t="s">
-        <v>1786</v>
+        <v>1789</v>
       </c>
       <c r="I58" s="13"/>
       <c r="J58" s="13"/>
       <c r="K58" s="12" t="s">
-        <v>1787</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="12" t="s">
-        <v>1788</v>
+        <v>1791</v>
       </c>
       <c r="B59" s="13"/>
       <c r="C59" s="12" t="s">
-        <v>1789</v>
+        <v>1792</v>
       </c>
       <c r="D59" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F59" s="12" t="s">
-        <v>1790</v>
+        <v>1793</v>
       </c>
       <c r="G59" s="12" t="s">
-        <v>1791</v>
+        <v>1794</v>
       </c>
       <c r="H59" s="12" t="s">
-        <v>1792</v>
+        <v>1795</v>
       </c>
       <c r="I59" s="13"/>
       <c r="J59" s="13"/>
       <c r="K59" s="12" t="s">
-        <v>1793</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="12" t="s">
-        <v>1794</v>
+        <v>1797</v>
       </c>
       <c r="B60" s="13"/>
       <c r="C60" s="12" t="s">
-        <v>1795</v>
+        <v>1798</v>
       </c>
       <c r="D60" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F60" s="12" t="s">
-        <v>1796</v>
+        <v>1799</v>
       </c>
       <c r="G60" s="12" t="s">
-        <v>1797</v>
+        <v>1800</v>
       </c>
       <c r="H60" s="12" t="s">
-        <v>1763</v>
+        <v>1766</v>
       </c>
       <c r="I60" s="13"/>
       <c r="J60" s="13"/>
       <c r="K60" s="12" t="s">
-        <v>1798</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="12" t="s">
-        <v>1799</v>
+        <v>1802</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>1799</v>
+        <v>1802</v>
       </c>
       <c r="C61" s="13"/>
       <c r="D61" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F61" s="12" t="s">
-        <v>1800</v>
+        <v>1803</v>
       </c>
       <c r="G61" s="12" t="s">
-        <v>1801</v>
+        <v>1804</v>
       </c>
       <c r="H61" s="12" t="s">
-        <v>1802</v>
+        <v>1805</v>
       </c>
       <c r="I61" s="13"/>
       <c r="J61" s="13"/>
       <c r="K61" s="12" t="s">
-        <v>1803</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="12" t="s">
-        <v>1804</v>
+        <v>1807</v>
       </c>
       <c r="B62" s="12" t="s">
-        <v>1805</v>
+        <v>1808</v>
       </c>
       <c r="C62" s="13"/>
       <c r="D62" s="12" t="s">
         <v>835</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F62" s="12" t="s">
-        <v>1806</v>
+        <v>1809</v>
       </c>
       <c r="G62" s="12" t="s">
-        <v>1807</v>
+        <v>1810</v>
       </c>
       <c r="H62" s="12" t="s">
-        <v>1808</v>
+        <v>1811</v>
       </c>
       <c r="I62" s="13"/>
       <c r="J62" s="13"/>
       <c r="K62" s="12" t="s">
-        <v>1809</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="12" t="s">
-        <v>1810</v>
+        <v>1813</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>1811</v>
+        <v>1814</v>
       </c>
       <c r="C63" s="13"/>
       <c r="D63" s="12" t="s">
         <v>817</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F63" s="12" t="s">
-        <v>1812</v>
+        <v>1815</v>
       </c>
       <c r="G63" s="12" t="s">
-        <v>1813</v>
+        <v>1816</v>
       </c>
       <c r="H63" s="12" t="s">
-        <v>1814</v>
+        <v>1817</v>
       </c>
       <c r="I63" s="13"/>
       <c r="J63" s="13"/>
       <c r="K63" s="12" t="s">
-        <v>1815</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="12" t="s">
-        <v>1816</v>
+        <v>1819</v>
       </c>
       <c r="B64" s="13"/>
       <c r="C64" s="12" t="s">
-        <v>1817</v>
+        <v>1820</v>
       </c>
       <c r="D64" s="12" t="s">
         <v>835</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F64" s="12" t="s">
-        <v>1818</v>
+        <v>1821</v>
       </c>
       <c r="G64" s="12" t="s">
-        <v>1819</v>
+        <v>1822</v>
       </c>
       <c r="H64" s="12" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="I64" s="13"/>
       <c r="J64" s="13"/>
       <c r="K64" s="12" t="s">
-        <v>1821</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="12" t="s">
-        <v>1822</v>
+        <v>1825</v>
       </c>
       <c r="B65" s="13"/>
       <c r="C65" s="12" t="s">
-        <v>1823</v>
+        <v>1826</v>
       </c>
       <c r="D65" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F65" s="12" t="s">
-        <v>1824</v>
+        <v>1827</v>
       </c>
       <c r="G65" s="12" t="s">
-        <v>1825</v>
+        <v>1828</v>
       </c>
       <c r="H65" s="12" t="s">
-        <v>1814</v>
+        <v>1817</v>
       </c>
       <c r="I65" s="13"/>
       <c r="J65" s="13"/>
       <c r="K65" s="12" t="s">
-        <v>1826</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="12" t="s">
-        <v>1827</v>
+        <v>1830</v>
       </c>
       <c r="B66" s="13"/>
       <c r="C66" s="12" t="s">
-        <v>1828</v>
+        <v>1831</v>
       </c>
       <c r="D66" s="12" t="s">
         <v>835</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F66" s="12" t="s">
-        <v>1829</v>
+        <v>1832</v>
       </c>
       <c r="G66" s="12" t="s">
-        <v>1830</v>
+        <v>1833</v>
       </c>
       <c r="H66" s="12" t="s">
-        <v>1831</v>
+        <v>1834</v>
       </c>
       <c r="I66" s="13"/>
       <c r="J66" s="13"/>
       <c r="K66" s="12" t="s">
-        <v>1832</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="12" t="s">
-        <v>1833</v>
+        <v>1836</v>
       </c>
       <c r="B67" s="13"/>
       <c r="C67" s="12" t="s">
-        <v>1834</v>
+        <v>1837</v>
       </c>
       <c r="D67" s="12" t="s">
         <v>817</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F67" s="12" t="s">
-        <v>1835</v>
+        <v>1838</v>
       </c>
       <c r="G67" s="12" t="s">
-        <v>1836</v>
+        <v>1839</v>
       </c>
       <c r="H67" s="12" t="s">
-        <v>1837</v>
+        <v>1840</v>
       </c>
       <c r="I67" s="13"/>
       <c r="J67" s="13"/>
       <c r="K67" s="12" t="s">
-        <v>1838</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="12" t="s">
-        <v>1839</v>
+        <v>1842</v>
       </c>
       <c r="B68" s="13"/>
       <c r="C68" s="12" t="s">
-        <v>1840</v>
+        <v>1843</v>
       </c>
       <c r="D68" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F68" s="12" t="s">
-        <v>1841</v>
+        <v>1844</v>
       </c>
       <c r="G68" s="12" t="s">
-        <v>1842</v>
+        <v>1845</v>
       </c>
       <c r="H68" s="12" t="s">
-        <v>1837</v>
+        <v>1840</v>
       </c>
       <c r="I68" s="13"/>
       <c r="J68" s="13"/>
       <c r="K68" s="12" t="s">
-        <v>1843</v>
+        <v>1846</v>
       </c>
     </row>
   </sheetData>
@@ -18848,12 +18857,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>1844</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>1845</v>
+        <v>1848</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -18864,626 +18873,626 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>1846</v>
+        <v>1849</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1847</v>
+        <v>1850</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>1848</v>
+        <v>1851</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>1849</v>
+        <v>1852</v>
       </c>
       <c r="E4" s="11" t="s">
         <v>1144</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>1850</v>
+        <v>1853</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>1851</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>1852</v>
+        <v>1855</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>1853</v>
+        <v>1856</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>1854</v>
+        <v>1857</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>1855</v>
+        <v>1858</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>1186</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>1856</v>
+        <v>1859</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>1857</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>1858</v>
+        <v>1861</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="12" t="s">
-        <v>1859</v>
+        <v>1862</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>1859</v>
+        <v>1862</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>1186</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>1860</v>
+        <v>1863</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>1861</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>1862</v>
+        <v>1865</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="12" t="s">
-        <v>1863</v>
+        <v>1866</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>1864</v>
+        <v>1867</v>
       </c>
       <c r="E7" s="12" t="s">
         <v>1186</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>1865</v>
+        <v>1868</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>1866</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>1867</v>
+        <v>1870</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>1868</v>
+        <v>1871</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>1869</v>
+        <v>1872</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>1870</v>
+        <v>1873</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>1158</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>1871</v>
+        <v>1874</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>1872</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>1873</v>
+        <v>1876</v>
       </c>
       <c r="B9" s="13"/>
       <c r="C9" s="12" t="s">
-        <v>1869</v>
+        <v>1872</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>1874</v>
+        <v>1877</v>
       </c>
       <c r="E9" s="12" t="s">
         <v>1186</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>1875</v>
+        <v>1878</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>1876</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>1877</v>
+        <v>1880</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="12" t="s">
-        <v>1869</v>
+        <v>1872</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>1874</v>
+        <v>1877</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>1186</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>1875</v>
+        <v>1878</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>1876</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>1878</v>
+        <v>1881</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="12" t="s">
-        <v>1869</v>
+        <v>1872</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>1874</v>
+        <v>1877</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>1186</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>1875</v>
+        <v>1878</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>1876</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>1879</v>
+        <v>1882</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="12" t="s">
-        <v>1869</v>
+        <v>1872</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>1874</v>
+        <v>1877</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>1186</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>1875</v>
+        <v>1878</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>1876</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>1880</v>
+        <v>1883</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="12" t="s">
-        <v>1869</v>
+        <v>1872</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>1874</v>
+        <v>1877</v>
       </c>
       <c r="E13" s="12" t="s">
         <v>1186</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>1875</v>
+        <v>1878</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>1876</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>1881</v>
+        <v>1884</v>
       </c>
       <c r="B14" s="13"/>
       <c r="C14" s="12" t="s">
-        <v>1882</v>
+        <v>1885</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>1883</v>
+        <v>1886</v>
       </c>
       <c r="E14" s="12" t="s">
         <v>1186</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>1884</v>
+        <v>1887</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>1885</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>1886</v>
+        <v>1889</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="12" t="s">
-        <v>1882</v>
+        <v>1885</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>1883</v>
+        <v>1886</v>
       </c>
       <c r="E15" s="12" t="s">
         <v>1186</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>1884</v>
+        <v>1887</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>1885</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>1887</v>
+        <v>1890</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="12" t="s">
-        <v>1882</v>
+        <v>1885</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>1883</v>
+        <v>1886</v>
       </c>
       <c r="E16" s="12" t="s">
         <v>1186</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>1884</v>
+        <v>1887</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>1885</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>1888</v>
+        <v>1891</v>
       </c>
       <c r="B17" s="13"/>
       <c r="C17" s="12" t="s">
-        <v>1882</v>
+        <v>1885</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>1883</v>
+        <v>1886</v>
       </c>
       <c r="E17" s="12" t="s">
         <v>1186</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>1884</v>
+        <v>1887</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>1885</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>1889</v>
+        <v>1892</v>
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="12" t="s">
-        <v>1882</v>
+        <v>1885</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>1883</v>
+        <v>1886</v>
       </c>
       <c r="E18" s="12" t="s">
         <v>1186</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>1884</v>
+        <v>1887</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>1885</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>1890</v>
+        <v>1893</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="12" t="s">
-        <v>1882</v>
+        <v>1885</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>1883</v>
+        <v>1886</v>
       </c>
       <c r="E19" s="12" t="s">
         <v>1186</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>1884</v>
+        <v>1887</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>1885</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>1891</v>
+        <v>1894</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="12" t="s">
-        <v>1869</v>
+        <v>1872</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>1854</v>
+        <v>1857</v>
       </c>
       <c r="E20" s="12" t="s">
         <v>1186</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>1892</v>
+        <v>1895</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>1893</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>1894</v>
+        <v>1897</v>
       </c>
       <c r="B21" s="13"/>
       <c r="C21" s="12" t="s">
-        <v>1869</v>
+        <v>1872</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>1854</v>
+        <v>1857</v>
       </c>
       <c r="E21" s="12" t="s">
         <v>1186</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>1892</v>
+        <v>1895</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>1893</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>1895</v>
+        <v>1898</v>
       </c>
       <c r="B22" s="13"/>
       <c r="C22" s="12" t="s">
-        <v>1896</v>
+        <v>1899</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>1897</v>
+        <v>1900</v>
       </c>
       <c r="E22" s="12" t="s">
         <v>1186</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>1898</v>
+        <v>1901</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>1899</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>1900</v>
+        <v>1903</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="12" t="s">
-        <v>1896</v>
+        <v>1899</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>1897</v>
+        <v>1900</v>
       </c>
       <c r="E23" s="12" t="s">
         <v>1186</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>1898</v>
+        <v>1901</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>1899</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>1901</v>
+        <v>1904</v>
       </c>
       <c r="B24" s="13"/>
       <c r="C24" s="12" t="s">
-        <v>1896</v>
+        <v>1899</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>1897</v>
+        <v>1900</v>
       </c>
       <c r="E24" s="12" t="s">
         <v>1186</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>1898</v>
+        <v>1901</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>1899</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>1902</v>
+        <v>1905</v>
       </c>
       <c r="B25" s="13"/>
       <c r="C25" s="12" t="s">
-        <v>1896</v>
+        <v>1899</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>1897</v>
+        <v>1900</v>
       </c>
       <c r="E25" s="12" t="s">
         <v>1186</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>1898</v>
+        <v>1901</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>1899</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>1903</v>
+        <v>1906</v>
       </c>
       <c r="B26" s="13"/>
       <c r="C26" s="12" t="s">
-        <v>1896</v>
+        <v>1899</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>1897</v>
+        <v>1900</v>
       </c>
       <c r="E26" s="12" t="s">
         <v>1186</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>1898</v>
+        <v>1901</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>1899</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>1904</v>
+        <v>1907</v>
       </c>
       <c r="B27" s="13"/>
       <c r="C27" s="12" t="s">
-        <v>1896</v>
+        <v>1899</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>1897</v>
+        <v>1900</v>
       </c>
       <c r="E27" s="12" t="s">
         <v>1186</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>1898</v>
+        <v>1901</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>1899</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>1905</v>
+        <v>1908</v>
       </c>
       <c r="B28" s="13"/>
       <c r="C28" s="12" t="s">
-        <v>1896</v>
+        <v>1899</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>1897</v>
+        <v>1900</v>
       </c>
       <c r="E28" s="12" t="s">
         <v>1186</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>1898</v>
+        <v>1901</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>1899</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>1906</v>
+        <v>1909</v>
       </c>
       <c r="B29" s="13"/>
       <c r="C29" s="12" t="s">
-        <v>1673</v>
+        <v>1676</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>1907</v>
+        <v>1910</v>
       </c>
       <c r="E29" s="12" t="s">
         <v>59</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>1908</v>
+        <v>1911</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>1909</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>1910</v>
+        <v>1913</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="12" t="s">
-        <v>1673</v>
+        <v>1676</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>1907</v>
+        <v>1910</v>
       </c>
       <c r="E30" s="12" t="s">
         <v>59</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>1908</v>
+        <v>1911</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>1909</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>1911</v>
+        <v>1914</v>
       </c>
       <c r="B31" s="13"/>
       <c r="C31" s="12" t="s">
-        <v>1673</v>
+        <v>1676</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>1907</v>
+        <v>1910</v>
       </c>
       <c r="E31" s="12" t="s">
         <v>59</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>1908</v>
+        <v>1911</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>1909</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>1912</v>
+        <v>1915</v>
       </c>
       <c r="B32" s="13"/>
       <c r="C32" s="12" t="s">
-        <v>1673</v>
+        <v>1676</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>1907</v>
+        <v>1910</v>
       </c>
       <c r="E32" s="12" t="s">
         <v>59</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>1908</v>
+        <v>1911</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>1909</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>1913</v>
+        <v>1916</v>
       </c>
       <c r="B33" s="13"/>
       <c r="C33" s="12" t="s">
-        <v>1869</v>
+        <v>1872</v>
       </c>
       <c r="D33" s="12" t="s">
         <v>61</v>
@@ -19492,19 +19501,19 @@
         <v>1186</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>1914</v>
+        <v>1917</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>1915</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>1916</v>
+        <v>1919</v>
       </c>
       <c r="B34" s="13"/>
       <c r="C34" s="12" t="s">
-        <v>1869</v>
+        <v>1872</v>
       </c>
       <c r="D34" s="12" t="s">
         <v>61</v>
@@ -19513,19 +19522,19 @@
         <v>1186</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>1917</v>
+        <v>1920</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>1918</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>1919</v>
+        <v>1922</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="12" t="s">
-        <v>1869</v>
+        <v>1872</v>
       </c>
       <c r="D35" s="12" t="s">
         <v>61</v>
@@ -19534,19 +19543,19 @@
         <v>1186</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>1917</v>
+        <v>1920</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>1918</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>1920</v>
+        <v>1923</v>
       </c>
       <c r="B36" s="13"/>
       <c r="C36" s="12" t="s">
-        <v>1869</v>
+        <v>1872</v>
       </c>
       <c r="D36" s="12" t="s">
         <v>61</v>
@@ -19555,262 +19564,262 @@
         <v>1186</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>1917</v>
+        <v>1920</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>1918</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>1921</v>
+        <v>1924</v>
       </c>
       <c r="B37" s="13"/>
       <c r="C37" s="12" t="s">
-        <v>1922</v>
+        <v>1925</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>1923</v>
+        <v>1926</v>
       </c>
       <c r="E37" s="12" t="s">
         <v>1158</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>1924</v>
+        <v>1927</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>1925</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>1926</v>
+        <v>1929</v>
       </c>
       <c r="B38" s="13"/>
       <c r="C38" s="12" t="s">
-        <v>1922</v>
+        <v>1925</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>1923</v>
+        <v>1926</v>
       </c>
       <c r="E38" s="12" t="s">
         <v>1158</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>1924</v>
+        <v>1927</v>
       </c>
       <c r="G38" s="12" t="s">
-        <v>1925</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B39" s="13"/>
       <c r="C39" s="12" t="s">
-        <v>1869</v>
+        <v>1872</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>1638</v>
+        <v>1641</v>
       </c>
       <c r="E39" s="12" t="s">
         <v>1186</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>1928</v>
+        <v>1931</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>1929</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B40" s="13"/>
       <c r="C40" s="12" t="s">
-        <v>1869</v>
+        <v>1872</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>1638</v>
+        <v>1641</v>
       </c>
       <c r="E40" s="12" t="s">
         <v>1186</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>1928</v>
+        <v>1931</v>
       </c>
       <c r="G40" s="12" t="s">
-        <v>1929</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>1931</v>
+        <v>1934</v>
       </c>
       <c r="B41" s="13"/>
       <c r="C41" s="12" t="s">
-        <v>1932</v>
+        <v>1935</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>1933</v>
+        <v>1936</v>
       </c>
       <c r="E41" s="12" t="s">
         <v>1186</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>1934</v>
+        <v>1937</v>
       </c>
       <c r="G41" s="12" t="s">
-        <v>1935</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B42" s="13"/>
       <c r="C42" s="12" t="s">
-        <v>1937</v>
+        <v>1940</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>1938</v>
+        <v>1941</v>
       </c>
       <c r="E42" s="12" t="s">
         <v>1186</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>1939</v>
+        <v>1942</v>
       </c>
       <c r="G42" s="12" t="s">
-        <v>1940</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>1941</v>
+        <v>1944</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="12" t="s">
-        <v>1942</v>
+        <v>1945</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
       <c r="E43" s="12" t="s">
         <v>281</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>1943</v>
+        <v>1946</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>1944</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B44" s="13"/>
       <c r="C44" s="12" t="s">
-        <v>1946</v>
+        <v>1949</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>1938</v>
+        <v>1941</v>
       </c>
       <c r="E44" s="12" t="s">
         <v>1186</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>1947</v>
+        <v>1950</v>
       </c>
       <c r="G44" s="12" t="s">
-        <v>1948</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>1949</v>
+        <v>1952</v>
       </c>
       <c r="B45" s="13"/>
       <c r="C45" s="12" t="s">
-        <v>1946</v>
+        <v>1949</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>1938</v>
+        <v>1941</v>
       </c>
       <c r="E45" s="12" t="s">
         <v>1186</v>
       </c>
       <c r="F45" s="12" t="s">
-        <v>1947</v>
+        <v>1950</v>
       </c>
       <c r="G45" s="12" t="s">
-        <v>1948</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>1950</v>
+        <v>1953</v>
       </c>
       <c r="B46" s="13"/>
       <c r="C46" s="12" t="s">
-        <v>1946</v>
+        <v>1949</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>1938</v>
+        <v>1941</v>
       </c>
       <c r="E46" s="12" t="s">
         <v>1186</v>
       </c>
       <c r="F46" s="12" t="s">
-        <v>1947</v>
+        <v>1950</v>
       </c>
       <c r="G46" s="12" t="s">
-        <v>1948</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>1951</v>
+        <v>1954</v>
       </c>
       <c r="B47" s="13"/>
       <c r="C47" s="12" t="s">
-        <v>1946</v>
+        <v>1949</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>1938</v>
+        <v>1941</v>
       </c>
       <c r="E47" s="12" t="s">
         <v>1186</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>1947</v>
+        <v>1950</v>
       </c>
       <c r="G47" s="12" t="s">
-        <v>1948</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="s">
-        <v>1952</v>
+        <v>1955</v>
       </c>
       <c r="B48" s="13"/>
       <c r="C48" s="12" t="s">
-        <v>1946</v>
+        <v>1949</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>1938</v>
+        <v>1941</v>
       </c>
       <c r="E48" s="12" t="s">
         <v>1186</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>1947</v>
+        <v>1950</v>
       </c>
       <c r="G48" s="12" t="s">
-        <v>1948</v>
+        <v>1951</v>
       </c>
     </row>
   </sheetData>
@@ -19847,12 +19856,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>1953</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>1954</v>
+        <v>1957</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -19862,243 +19871,243 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>1847</v>
+        <v>1850</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1955</v>
+        <v>1958</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>1956</v>
+        <v>1959</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>1957</v>
+        <v>1960</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>1958</v>
+        <v>1961</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>1959</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>1960</v>
+        <v>1963</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>1961</v>
+        <v>1964</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>1863</v>
+        <v>1866</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="12" t="s">
-        <v>1962</v>
+        <v>1965</v>
       </c>
       <c r="F5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>1963</v>
+        <v>1966</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>1961</v>
+        <v>1964</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>1863</v>
+        <v>1866</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="12" t="s">
-        <v>1962</v>
+        <v>1965</v>
       </c>
       <c r="F6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
+        <v>1967</v>
+      </c>
+      <c r="B7" s="12" t="s">
         <v>1964</v>
       </c>
-      <c r="B7" s="12" t="s">
-        <v>1961</v>
-      </c>
       <c r="C7" s="12" t="s">
-        <v>1863</v>
+        <v>1866</v>
       </c>
       <c r="D7" s="13"/>
       <c r="E7" s="12" t="s">
-        <v>1962</v>
+        <v>1965</v>
       </c>
       <c r="F7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>1965</v>
+        <v>1968</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>1966</v>
+        <v>1969</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>1967</v>
+        <v>1970</v>
       </c>
       <c r="D8" s="13"/>
       <c r="E8" s="12" t="s">
-        <v>1968</v>
+        <v>1971</v>
       </c>
       <c r="F8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>1969</v>
+        <v>1972</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>1970</v>
+        <v>1973</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>1869</v>
+        <v>1872</v>
       </c>
       <c r="D9" s="13"/>
       <c r="E9" s="12" t="s">
-        <v>1971</v>
+        <v>1974</v>
       </c>
       <c r="F9" s="13"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>1972</v>
+        <v>1975</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>1973</v>
+        <v>1976</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>1938</v>
+        <v>1941</v>
       </c>
       <c r="D10" s="13"/>
       <c r="E10" s="12" t="s">
-        <v>1974</v>
+        <v>1977</v>
       </c>
       <c r="F10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>1975</v>
+        <v>1978</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>1976</v>
+        <v>1979</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>1938</v>
+        <v>1941</v>
       </c>
       <c r="D11" s="13"/>
       <c r="E11" s="12" t="s">
-        <v>1977</v>
+        <v>1980</v>
       </c>
       <c r="F11" s="13"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>1978</v>
+        <v>1981</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>1976</v>
+        <v>1979</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>1938</v>
+        <v>1941</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="12" t="s">
-        <v>1977</v>
+        <v>1980</v>
       </c>
       <c r="F12" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>1979</v>
+        <v>1982</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>1980</v>
+        <v>1983</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>1981</v>
+        <v>1984</v>
       </c>
       <c r="D13" s="13"/>
       <c r="E13" s="12" t="s">
-        <v>1982</v>
+        <v>1985</v>
       </c>
       <c r="F13" s="13"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>1983</v>
+        <v>1986</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>1984</v>
+        <v>1987</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>1985</v>
+        <v>1988</v>
       </c>
       <c r="D14" s="13"/>
       <c r="E14" s="12" t="s">
-        <v>1982</v>
+        <v>1985</v>
       </c>
       <c r="F14" s="13"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>1987</v>
+        <v>1990</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>1988</v>
+        <v>1991</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="12" t="s">
-        <v>1989</v>
+        <v>1992</v>
       </c>
       <c r="F15" s="13"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>1990</v>
+        <v>1993</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>1991</v>
+        <v>1994</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>1992</v>
+        <v>1995</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>1993</v>
+        <v>1996</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>1994</v>
+        <v>1997</v>
       </c>
       <c r="F16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>1995</v>
+        <v>1998</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>1996</v>
+        <v>1999</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>1719</v>
+        <v>1722</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="12" t="s">
-        <v>1997</v>
+        <v>2000</v>
       </c>
       <c r="F17" s="13"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>1998</v>
+        <v>2001</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>1999</v>
+        <v>2002</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>2000</v>
+        <v>2003</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="13"/>
@@ -20106,13 +20115,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>2001</v>
+        <v>2004</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>2002</v>
+        <v>2005</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>2000</v>
+        <v>2003</v>
       </c>
       <c r="D19" s="13"/>
       <c r="E19" s="13"/>
@@ -20120,13 +20129,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
+        <v>2006</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>2005</v>
+      </c>
+      <c r="C20" s="12" t="s">
         <v>2003</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>2002</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>2000</v>
       </c>
       <c r="D20" s="13"/>
       <c r="E20" s="13"/>
@@ -20134,13 +20143,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>2004</v>
+        <v>2007</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>2005</v>
+        <v>2008</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>2000</v>
+        <v>2003</v>
       </c>
       <c r="D21" s="13"/>
       <c r="E21" s="13"/>
@@ -20148,13 +20157,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>2006</v>
+        <v>2009</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>2007</v>
+        <v>2010</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>2008</v>
+        <v>2011</v>
       </c>
       <c r="D22" s="13"/>
       <c r="E22" s="13"/>
@@ -20162,10 +20171,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>2009</v>
+        <v>2012</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>2010</v>
+        <v>2013</v>
       </c>
       <c r="C23" s="13"/>
       <c r="D23" s="13"/>
@@ -20176,10 +20185,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>2012</v>
+        <v>2015</v>
       </c>
       <c r="C24" s="13"/>
       <c r="D24" s="13"/>
@@ -20190,10 +20199,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="C25" s="13"/>
       <c r="D25" s="13"/>
@@ -20204,10 +20213,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="C26" s="13"/>
       <c r="D26" s="13"/>
@@ -20218,10 +20227,10 @@
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="C27" s="13"/>
       <c r="D27" s="13"/>
@@ -20232,10 +20241,10 @@
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="C28" s="13"/>
       <c r="D28" s="13"/>
@@ -20246,10 +20255,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="C29" s="12" t="s">
         <v>61</v>
@@ -20260,13 +20269,13 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>2024</v>
+        <v>2027</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="D30" s="13"/>
       <c r="E30" s="13"/>
@@ -20274,13 +20283,13 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>2026</v>
+        <v>2029</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>2024</v>
+        <v>2027</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="D31" s="13"/>
       <c r="E31" s="13"/>
@@ -20288,13 +20297,13 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>2027</v>
+        <v>2030</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>2028</v>
+        <v>2031</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>2029</v>
+        <v>2032</v>
       </c>
       <c r="D32" s="13"/>
       <c r="E32" s="13"/>
@@ -20302,13 +20311,13 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>2030</v>
+        <v>2033</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>2031</v>
+        <v>2034</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>2032</v>
+        <v>2035</v>
       </c>
       <c r="D33" s="13"/>
       <c r="E33" s="13"/>
@@ -20316,13 +20325,13 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>2033</v>
+        <v>2036</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>2031</v>
+        <v>2034</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>2032</v>
+        <v>2035</v>
       </c>
       <c r="D34" s="13"/>
       <c r="E34" s="13"/>
@@ -20330,13 +20339,13 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
+        <v>2037</v>
+      </c>
+      <c r="B35" s="12" t="s">
         <v>2034</v>
       </c>
-      <c r="B35" s="12" t="s">
-        <v>2031</v>
-      </c>
       <c r="C35" s="12" t="s">
-        <v>2032</v>
+        <v>2035</v>
       </c>
       <c r="D35" s="13"/>
       <c r="E35" s="13"/>
@@ -20344,13 +20353,13 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
+        <v>2038</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>2034</v>
+      </c>
+      <c r="C36" s="12" t="s">
         <v>2035</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>2031</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>2032</v>
       </c>
       <c r="D36" s="13"/>
       <c r="E36" s="13"/>
@@ -20358,13 +20367,13 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>2036</v>
+        <v>2039</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>2031</v>
+        <v>2034</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>2032</v>
+        <v>2035</v>
       </c>
       <c r="D37" s="13"/>
       <c r="E37" s="13"/>
@@ -20372,13 +20381,13 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>2037</v>
+        <v>2040</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>2038</v>
+        <v>2041</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>2039</v>
+        <v>2042</v>
       </c>
       <c r="D38" s="13"/>
       <c r="E38" s="13"/>
@@ -20386,13 +20395,13 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>2040</v>
+        <v>2043</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>2038</v>
+        <v>2041</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>2039</v>
+        <v>2042</v>
       </c>
       <c r="D39" s="13"/>
       <c r="E39" s="13"/>
@@ -20400,13 +20409,13 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>2041</v>
+        <v>2044</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>2042</v>
+        <v>2045</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>2043</v>
+        <v>2046</v>
       </c>
       <c r="D40" s="13"/>
       <c r="E40" s="13"/>
@@ -20414,13 +20423,13 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>2044</v>
+        <v>2047</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>2045</v>
+        <v>2048</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>2046</v>
+        <v>2049</v>
       </c>
       <c r="D41" s="13"/>
       <c r="E41" s="13"/>
@@ -20428,13 +20437,13 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>2047</v>
+        <v>2050</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>2045</v>
+        <v>2048</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>2046</v>
+        <v>2049</v>
       </c>
       <c r="D42" s="13"/>
       <c r="E42" s="13"/>
@@ -20442,13 +20451,13 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>2048</v>
+        <v>2051</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>2049</v>
+        <v>2052</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>1992</v>
+        <v>1995</v>
       </c>
       <c r="D43" s="13"/>
       <c r="E43" s="13"/>
@@ -20456,13 +20465,13 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>2050</v>
+        <v>2053</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>2051</v>
+        <v>2054</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>2052</v>
+        <v>2055</v>
       </c>
       <c r="D44" s="13"/>
       <c r="E44" s="13"/>
@@ -20470,13 +20479,13 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>2053</v>
+        <v>2056</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>2054</v>
+        <v>2057</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>2055</v>
+        <v>2058</v>
       </c>
       <c r="D45" s="13"/>
       <c r="E45" s="13"/>
@@ -20484,13 +20493,13 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>2056</v>
+        <v>2059</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>2057</v>
+        <v>2060</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>2055</v>
+        <v>2058</v>
       </c>
       <c r="D46" s="13"/>
       <c r="E46" s="13"/>
@@ -20498,13 +20507,13 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
+        <v>2061</v>
+      </c>
+      <c r="B47" s="12" t="s">
+        <v>2057</v>
+      </c>
+      <c r="C47" s="12" t="s">
         <v>2058</v>
-      </c>
-      <c r="B47" s="12" t="s">
-        <v>2054</v>
-      </c>
-      <c r="C47" s="12" t="s">
-        <v>2055</v>
       </c>
       <c r="D47" s="13"/>
       <c r="E47" s="13"/>
@@ -20512,16 +20521,16 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="s">
-        <v>2059</v>
+        <v>2062</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>2060</v>
+        <v>2063</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>2061</v>
+        <v>2064</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>2062</v>
+        <v>2065</v>
       </c>
       <c r="E48" s="13"/>
       <c r="F48" s="13"/>
@@ -20560,12 +20569,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>2063</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>2064</v>
+        <v>2067</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -20575,30 +20584,30 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>2065</v>
+        <v>2068</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1488</v>
+        <v>1491</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>2066</v>
+        <v>2069</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>1143</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>2067</v>
+        <v>2070</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>2068</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>2069</v>
+        <v>2072</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>2070</v>
+        <v>2073</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -20609,16 +20618,16 @@
     </row>
     <row r="6" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>2071</v>
+        <v>2074</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>2072</v>
+        <v>2075</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>2073</v>
+        <v>2076</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>2074</v>
+        <v>2077</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>461</v>
@@ -20627,34 +20636,34 @@
     </row>
     <row r="7" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>2075</v>
+        <v>2078</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>2076</v>
+        <v>2079</v>
       </c>
       <c r="C7" s="12" t="s">
+        <v>2080</v>
+      </c>
+      <c r="D7" s="12" t="s">
         <v>2077</v>
       </c>
-      <c r="D7" s="12" t="s">
-        <v>2074</v>
-      </c>
       <c r="E7" s="12" t="s">
-        <v>2078</v>
+        <v>2081</v>
       </c>
       <c r="F7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>2079</v>
+        <v>2082</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>2080</v>
+        <v>2083</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>2081</v>
+        <v>2084</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>2082</v>
+        <v>2085</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>379</v>
@@ -20663,52 +20672,52 @@
     </row>
     <row r="9" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>2083</v>
+        <v>2086</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>2084</v>
+        <v>2087</v>
       </c>
       <c r="C9" s="12" t="s">
+        <v>2088</v>
+      </c>
+      <c r="D9" s="12" t="s">
         <v>2085</v>
       </c>
-      <c r="D9" s="12" t="s">
-        <v>2082</v>
-      </c>
       <c r="E9" s="12" t="s">
-        <v>2086</v>
+        <v>2089</v>
       </c>
       <c r="F9" s="13"/>
     </row>
     <row r="10" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>2087</v>
+        <v>2090</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="C10" s="12" t="s">
+        <v>2092</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>2093</v>
+      </c>
+      <c r="E10" s="12" t="s">
         <v>2089</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>2090</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>2086</v>
       </c>
       <c r="F10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>2091</v>
+        <v>2094</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>2093</v>
+        <v>2096</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>2094</v>
+        <v>2097</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>379</v>
@@ -20717,16 +20726,16 @@
     </row>
     <row r="12" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>2095</v>
+        <v>2098</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>2096</v>
+        <v>2099</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>2097</v>
+        <v>2100</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>2098</v>
+        <v>2101</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>379</v>
@@ -20735,106 +20744,106 @@
     </row>
     <row r="13" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>2099</v>
+        <v>2102</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>2100</v>
+        <v>2103</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>2101</v>
+        <v>2104</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>2102</v>
+        <v>2105</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>2086</v>
+        <v>2089</v>
       </c>
       <c r="F13" s="13"/>
     </row>
     <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>2103</v>
+        <v>2106</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>2104</v>
+        <v>2107</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>2105</v>
+        <v>2108</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>2074</v>
+        <v>2077</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>2078</v>
+        <v>2081</v>
       </c>
       <c r="F14" s="13"/>
     </row>
     <row r="15" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>2106</v>
+        <v>2109</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>2107</v>
+        <v>2110</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>2108</v>
+        <v>2111</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>2074</v>
+        <v>2077</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>2109</v>
+        <v>2112</v>
       </c>
       <c r="F15" s="13"/>
     </row>
     <row r="16" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>2110</v>
+        <v>2113</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>2111</v>
+        <v>2114</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>2112</v>
+        <v>2115</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>2098</v>
+        <v>2101</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>2086</v>
+        <v>2089</v>
       </c>
       <c r="F16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>2113</v>
+        <v>2116</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>2114</v>
+        <v>2117</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>2115</v>
+        <v>2118</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>2074</v>
+        <v>2077</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>2086</v>
+        <v>2089</v>
       </c>
       <c r="F17" s="13"/>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>2116</v>
+        <v>2119</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>2117</v>
+        <v>2120</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>2118</v>
+        <v>2121</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>2119</v>
+        <v>2122</v>
       </c>
       <c r="E18" s="12" t="s">
         <v>379</v>
@@ -20843,37 +20852,37 @@
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>2120</v>
+        <v>2123</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>2121</v>
+        <v>2124</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>2122</v>
+        <v>2125</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>2074</v>
+        <v>2077</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>2086</v>
+        <v>2089</v>
       </c>
       <c r="F19" s="13"/>
     </row>
     <row r="20" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>2123</v>
+        <v>2126</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>2124</v>
+        <v>2127</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>2125</v>
+        <v>2128</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>2074</v>
+        <v>2077</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>2086</v>
+        <v>2089</v>
       </c>
       <c r="F20" s="13"/>
     </row>
@@ -20908,12 +20917,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>2126</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>2127</v>
+        <v>2130</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -20923,15 +20932,15 @@
         <v>39</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>2128</v>
+        <v>2131</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>1850</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>2129</v>
+        <v>2132</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>1204</v>
@@ -20940,7 +20949,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>2129</v>
+        <v>2132</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>1199</v>
@@ -20949,7 +20958,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>2129</v>
+        <v>2132</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>1157</v>
@@ -20958,7 +20967,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>2129</v>
+        <v>2132</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>1194</v>
@@ -20967,7 +20976,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>2129</v>
+        <v>2132</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>1231</v>
@@ -20976,34 +20985,34 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>2129</v>
+        <v>2132</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>2130</v>
+        <v>2133</v>
       </c>
       <c r="C10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>2131</v>
+        <v>2134</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="C11" s="13"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>2131</v>
+        <v>2134</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="C12" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>2131</v>
+        <v>2134</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>369</v>
@@ -21012,7 +21021,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>2131</v>
+        <v>2134</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>461</v>
@@ -21021,7 +21030,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>2131</v>
+        <v>2134</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>379</v>
@@ -21030,7 +21039,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>2131</v>
+        <v>2134</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>383</v>
@@ -21039,16 +21048,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>2131</v>
+        <v>2134</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>1333</v>
+        <v>1336</v>
       </c>
       <c r="C17" s="13"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>2131</v>
+        <v>2134</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>399</v>
@@ -21057,7 +21066,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>2132</v>
+        <v>2135</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>178</v>
@@ -21066,16 +21075,16 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>2132</v>
+        <v>2135</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>2133</v>
+        <v>2136</v>
       </c>
       <c r="C20" s="13"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>2132</v>
+        <v>2135</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>383</v>
@@ -21084,25 +21093,25 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>2132</v>
+        <v>2135</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>2134</v>
+        <v>2137</v>
       </c>
       <c r="C22" s="13"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>2132</v>
+        <v>2135</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>2135</v>
+        <v>2138</v>
       </c>
       <c r="C23" s="13"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>2132</v>
+        <v>2135</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>227</v>
@@ -21111,7 +21120,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>2136</v>
+        <v>2139</v>
       </c>
       <c r="B25" s="12" t="s">
         <v>890</v>
@@ -21120,188 +21129,188 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>2136</v>
+        <v>2139</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>2137</v>
+        <v>2140</v>
       </c>
       <c r="C26" s="13"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>2136</v>
+        <v>2139</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>2138</v>
+        <v>2141</v>
       </c>
       <c r="C27" s="13"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>2136</v>
+        <v>2139</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>2139</v>
+        <v>2142</v>
       </c>
       <c r="C28" s="13"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>2136</v>
+        <v>2139</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>2140</v>
+        <v>2143</v>
       </c>
       <c r="C29" s="13"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>2136</v>
+        <v>2139</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>2141</v>
+        <v>2144</v>
       </c>
       <c r="C30" s="13"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>2136</v>
+        <v>2139</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>2142</v>
+        <v>2145</v>
       </c>
       <c r="C31" s="13"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>2136</v>
+        <v>2139</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>2143</v>
+        <v>2146</v>
       </c>
       <c r="C32" s="13"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>2136</v>
+        <v>2139</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>1317</v>
+        <v>1320</v>
       </c>
       <c r="C33" s="13"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>2136</v>
+        <v>2139</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>2144</v>
+        <v>2147</v>
       </c>
       <c r="C34" s="13"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>2136</v>
+        <v>2139</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>2130</v>
+        <v>2133</v>
       </c>
       <c r="C35" s="13"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>2145</v>
+        <v>2148</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>2133</v>
+        <v>2136</v>
       </c>
       <c r="C36" s="13"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>2145</v>
+        <v>2148</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>2146</v>
+        <v>2149</v>
       </c>
       <c r="C37" s="13"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>2145</v>
+        <v>2148</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>2147</v>
+        <v>2150</v>
       </c>
       <c r="C38" s="13"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>2145</v>
+        <v>2148</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>1299</v>
+        <v>1302</v>
       </c>
       <c r="C39" s="13"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>2145</v>
+        <v>2148</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>2148</v>
+        <v>2151</v>
       </c>
       <c r="C40" s="13"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>2145</v>
+        <v>2148</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>2149</v>
+        <v>2152</v>
       </c>
       <c r="C41" s="13"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>2145</v>
+        <v>2148</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>1269</v>
+        <v>1272</v>
       </c>
       <c r="C42" s="13"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>2150</v>
+        <v>2153</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>2151</v>
+        <v>2154</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>2152</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>2150</v>
+        <v>2153</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>2153</v>
+        <v>2156</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>2152</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>2150</v>
+        <v>2153</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>2154</v>
+        <v>2157</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>2152</v>
+        <v>2155</v>
       </c>
     </row>
   </sheetData>
@@ -21338,12 +21347,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>2155</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>2156</v>
+        <v>2159</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -21356,113 +21365,113 @@
         <v>1106</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>2157</v>
+        <v>2160</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>2158</v>
+        <v>2161</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>2159</v>
+        <v>2162</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>2160</v>
+        <v>2163</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>1850</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>2161</v>
+        <v>2164</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>2162</v>
+        <v>2165</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>2163</v>
+        <v>2166</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>2164</v>
+        <v>2167</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>2165</v>
+        <v>2168</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>2166</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>2167</v>
+        <v>2170</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>2168</v>
+        <v>2171</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>2169</v>
+        <v>2172</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>2170</v>
+        <v>2173</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>2171</v>
+        <v>2174</v>
       </c>
       <c r="F6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>2172</v>
+        <v>2175</v>
       </c>
       <c r="B7" s="13" t="s">
+        <v>2176</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>2177</v>
+      </c>
+      <c r="D7" s="12" t="s">
         <v>2173</v>
       </c>
-      <c r="C7" s="13" t="s">
-        <v>2174</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>2170</v>
-      </c>
       <c r="E7" s="12" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="F7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>2169</v>
+        <v>2172</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="F8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>2183</v>
+        <v>2186</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>2184</v>
+        <v>2187</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>2185</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21470,54 +21479,54 @@
         <v>375</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>2186</v>
+        <v>2189</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>2188</v>
+        <v>2191</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>2189</v>
+        <v>2192</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>2191</v>
+        <v>2194</v>
       </c>
       <c r="B11" s="13" t="s">
+        <v>2195</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>2172</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>2196</v>
+      </c>
+      <c r="E11" s="13" t="s">
         <v>2192</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>2169</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>2193</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>2189</v>
       </c>
       <c r="F11" s="13"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>2194</v>
+        <v>2197</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>2195</v>
+        <v>2198</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>2169</v>
+        <v>2172</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>2196</v>
+        <v>2199</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>2197</v>
+        <v>2200</v>
       </c>
       <c r="F12" s="13"/>
     </row>
@@ -21526,16 +21535,16 @@
         <v>417</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>2198</v>
+        <v>2201</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>2169</v>
+        <v>2172</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>2199</v>
+        <v>2202</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>2200</v>
+        <v>2203</v>
       </c>
       <c r="F13" s="13"/>
     </row>
@@ -21544,482 +21553,482 @@
         <v>442</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>2201</v>
+        <v>2204</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>2169</v>
+        <v>2172</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>2202</v>
+        <v>2205</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>2189</v>
+        <v>2192</v>
       </c>
       <c r="F14" s="13"/>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>2203</v>
+        <v>2206</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>2204</v>
+        <v>2207</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>2205</v>
+        <v>2208</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>2206</v>
+        <v>2209</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>2207</v>
+        <v>2210</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>2208</v>
+        <v>2211</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>2209</v>
+        <v>2212</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>2210</v>
+        <v>2213</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>2211</v>
+        <v>2214</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>2212</v>
+        <v>2215</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>2213</v>
+        <v>2216</v>
       </c>
       <c r="F16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
+        <v>2217</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>2218</v>
+      </c>
+      <c r="C17" s="13" t="s">
         <v>2214</v>
       </c>
-      <c r="B17" s="12" t="s">
-        <v>2215</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>2211</v>
-      </c>
       <c r="D17" s="12" t="s">
-        <v>2216</v>
+        <v>2219</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>2217</v>
+        <v>2220</v>
       </c>
       <c r="F17" s="13"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>2218</v>
+        <v>2221</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>2219</v>
+        <v>2222</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>2220</v>
+        <v>2223</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>2221</v>
+        <v>2224</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>2222</v>
+        <v>2225</v>
       </c>
       <c r="F18" s="13"/>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>2223</v>
+        <v>2226</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>2224</v>
+        <v>2227</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>2225</v>
+        <v>2228</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>2226</v>
+        <v>2229</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>2227</v>
+        <v>2230</v>
       </c>
       <c r="F19" s="13"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>2228</v>
+        <v>2231</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>2229</v>
+        <v>2232</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>2169</v>
+        <v>2172</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>2230</v>
+        <v>2233</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>2231</v>
+        <v>2234</v>
       </c>
       <c r="F20" s="13"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>2232</v>
+        <v>2235</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>2233</v>
+        <v>2236</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>2169</v>
+        <v>2172</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>2234</v>
+        <v>2237</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>2235</v>
+        <v>2238</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>2236</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>2237</v>
+        <v>2240</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>2238</v>
+        <v>2241</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>2169</v>
+        <v>2172</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>2239</v>
+        <v>2242</v>
       </c>
       <c r="E22" s="13"/>
       <c r="F22" s="13"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>2240</v>
+        <v>2243</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>2241</v>
+        <v>2244</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>2242</v>
+        <v>2245</v>
       </c>
       <c r="E23" s="13"/>
       <c r="F23" s="13"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>2243</v>
+        <v>2246</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>2244</v>
+        <v>2247</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>2245</v>
+        <v>2248</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>2246</v>
+        <v>2249</v>
       </c>
       <c r="F24" s="13"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>2247</v>
+        <v>2250</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>2248</v>
+        <v>2251</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>369</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>2249</v>
+        <v>2252</v>
       </c>
       <c r="E25" s="13"/>
       <c r="F25" s="13"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>2250</v>
+        <v>2253</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>2251</v>
+        <v>2254</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>2252</v>
+        <v>2255</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>2253</v>
+        <v>2256</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>2254</v>
+        <v>2257</v>
       </c>
       <c r="F26" s="13"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
+        <v>2258</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>2259</v>
+      </c>
+      <c r="C27" s="13" t="s">
         <v>2255</v>
       </c>
-      <c r="B27" s="12" t="s">
-        <v>2256</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>2252</v>
-      </c>
       <c r="D27" s="13" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E27" s="13" t="s">
         <v>2257</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>2254</v>
       </c>
       <c r="F27" s="13"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>2258</v>
+        <v>2261</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>2259</v>
+        <v>2262</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>2260</v>
+        <v>2263</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>2261</v>
+        <v>2264</v>
       </c>
       <c r="E28" s="13"/>
       <c r="F28" s="13" t="s">
-        <v>2262</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>2263</v>
+        <v>2266</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>2264</v>
+        <v>2267</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>1317</v>
+        <v>1320</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>2265</v>
+        <v>2268</v>
       </c>
       <c r="E29" s="13"/>
       <c r="F29" s="13"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>2266</v>
+        <v>2269</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>2267</v>
+        <v>2270</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>2268</v>
+        <v>2271</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>2252</v>
+        <v>2255</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>2269</v>
+        <v>2272</v>
       </c>
       <c r="F30" s="13"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>2270</v>
+        <v>2273</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>2271</v>
+        <v>2274</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>2272</v>
+        <v>2275</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>2273</v>
+        <v>2276</v>
       </c>
       <c r="E31" s="13"/>
       <c r="F31" s="13"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>2274</v>
+        <v>2277</v>
       </c>
       <c r="B32" s="13" t="s">
+        <v>2278</v>
+      </c>
+      <c r="C32" s="12" t="s">
         <v>2275</v>
       </c>
-      <c r="C32" s="12" t="s">
-        <v>2272</v>
-      </c>
       <c r="D32" s="13" t="s">
-        <v>2276</v>
+        <v>2279</v>
       </c>
       <c r="E32" s="13"/>
       <c r="F32" s="13"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>2277</v>
+        <v>2280</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>2278</v>
+        <v>2281</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>2272</v>
+        <v>2275</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>2279</v>
+        <v>2282</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>2280</v>
+        <v>2283</v>
       </c>
       <c r="F33" s="13"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>2281</v>
+        <v>2284</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>2282</v>
+        <v>2285</v>
       </c>
       <c r="C34" s="12" t="s">
         <v>383</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>2283</v>
+        <v>2286</v>
       </c>
       <c r="E34" s="13"/>
       <c r="F34" s="13" t="s">
-        <v>2284</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>2285</v>
+        <v>2288</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>2286</v>
+        <v>2289</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>2287</v>
+        <v>2290</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>2288</v>
+        <v>2291</v>
       </c>
       <c r="E35" s="13"/>
       <c r="F35" s="13"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>2289</v>
+        <v>2292</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>2290</v>
+        <v>2293</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>2291</v>
+        <v>2294</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>2292</v>
+        <v>2295</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>2293</v>
+        <v>2296</v>
       </c>
       <c r="F36" s="13"/>
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>2294</v>
+        <v>2297</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>2295</v>
+        <v>2298</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>2169</v>
+        <v>2172</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>2296</v>
+        <v>2299</v>
       </c>
       <c r="E37" s="13"/>
       <c r="F37" s="12" t="s">
-        <v>2297</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>2298</v>
+        <v>2301</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>2299</v>
+        <v>2302</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>2169</v>
+        <v>2172</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>2300</v>
+        <v>2303</v>
       </c>
       <c r="E38" s="13"/>
       <c r="F38" s="13"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>2301</v>
+        <v>2304</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>2302</v>
+        <v>2305</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>2169</v>
+        <v>2172</v>
       </c>
       <c r="D39" s="13"/>
       <c r="E39" s="13"/>
       <c r="F39" s="12" t="s">
-        <v>2303</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>2304</v>
+        <v>2307</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>2305</v>
+        <v>2308</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>2169</v>
+        <v>2172</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>2306</v>
+        <v>2309</v>
       </c>
       <c r="E40" s="13"/>
       <c r="F40" s="12" t="s">
-        <v>2307</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>2308</v>
+        <v>2311</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>2309</v>
+        <v>2312</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>2169</v>
+        <v>2172</v>
       </c>
       <c r="D41" s="13"/>
       <c r="E41" s="13"/>
@@ -22027,16 +22036,16 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>2310</v>
+        <v>2313</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>2311</v>
+        <v>2314</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>2169</v>
+        <v>2172</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>2312</v>
+        <v>2315</v>
       </c>
       <c r="E42" s="13"/>
       <c r="F42" s="13"/>
@@ -27865,7 +27874,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="12" t="s">
         <v>793</v>
       </c>
@@ -31141,7 +31150,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr defaultColWidth="7.2421875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21.7"/>
@@ -32097,7 +32106,7 @@
       <c r="M28" s="13"/>
       <c r="N28" s="13"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
         <v>1247</v>
       </c>
@@ -32117,7 +32126,7 @@
       </c>
       <c r="H29" s="13"/>
       <c r="I29" s="12" t="s">
-        <v>1249</v>
+        <v>1196</v>
       </c>
       <c r="J29" s="12" t="s">
         <v>1162</v>
@@ -32129,9 +32138,11 @@
         <v>393</v>
       </c>
       <c r="M29" s="13"/>
-      <c r="N29" s="13"/>
-    </row>
-    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N29" s="12" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
         <v>1250</v>
       </c>
@@ -32151,7 +32162,7 @@
       </c>
       <c r="H30" s="13"/>
       <c r="I30" s="12" t="s">
-        <v>1196</v>
+        <v>1252</v>
       </c>
       <c r="J30" s="12" t="s">
         <v>1162</v>
@@ -32163,9 +32174,7 @@
         <v>393</v>
       </c>
       <c r="M30" s="13"/>
-      <c r="N30" s="12" t="s">
-        <v>1252</v>
-      </c>
+      <c r="N30" s="13"/>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
@@ -32175,21 +32184,19 @@
         <v>1254</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>1199</v>
+        <v>1194</v>
       </c>
       <c r="D31" s="12" t="s">
         <v>1195</v>
       </c>
       <c r="E31" s="13"/>
-      <c r="F31" s="12" t="s">
-        <v>1200</v>
-      </c>
+      <c r="F31" s="13"/>
       <c r="G31" s="12" t="s">
         <v>138</v>
       </c>
       <c r="H31" s="13"/>
       <c r="I31" s="12" t="s">
-        <v>1255</v>
+        <v>1196</v>
       </c>
       <c r="J31" s="12" t="s">
         <v>1162</v>
@@ -32198,13 +32205,51 @@
         <v>393</v>
       </c>
       <c r="L31" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="M31" s="13"/>
+      <c r="N31" s="12" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="12" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>1199</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>1195</v>
+      </c>
+      <c r="E32" s="13"/>
+      <c r="F32" s="12" t="s">
+        <v>1200</v>
+      </c>
+      <c r="G32" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="H32" s="13"/>
+      <c r="I32" s="12" t="s">
+        <v>1258</v>
+      </c>
+      <c r="J32" s="12" t="s">
+        <v>1162</v>
+      </c>
+      <c r="K32" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="L32" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="M31" s="13"/>
-      <c r="N31" s="13"/>
+      <c r="M32" s="13"/>
+      <c r="N32" s="13"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:N31"/>
+  <autoFilter ref="A4:N32"/>
   <mergeCells count="1">
     <mergeCell ref="A2:N2"/>
   </mergeCells>
@@ -32233,29 +32278,29 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>1257</v>
+        <v>1260</v>
       </c>
       <c r="B2" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>1258</v>
+        <v>1261</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1259</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>1260</v>
+        <v>1263</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>1261</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32263,79 +32308,79 @@
         <v>412</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>1263</v>
+        <v>1266</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>1264</v>
+        <v>1267</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B9" s="12" t="s">
         <v>1265</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>1262</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>1266</v>
+        <v>1269</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>1268</v>
+        <v>1271</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>1269</v>
+        <v>1272</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B13" s="12" t="s">
         <v>1270</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>1267</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>1271</v>
+        <v>1274</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>1272</v>
+        <v>1275</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32343,247 +32388,247 @@
         <v>227</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>1273</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>1274</v>
+        <v>1277</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>1275</v>
+        <v>1278</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>1276</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>1277</v>
+        <v>1280</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>1278</v>
+        <v>1281</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>1279</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>1280</v>
+        <v>1283</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>1281</v>
+        <v>1284</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>1285</v>
+        <v>1288</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>1287</v>
+        <v>1290</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>1288</v>
+        <v>1291</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>1289</v>
+        <v>1292</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>1290</v>
+        <v>1293</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>1293</v>
+        <v>1296</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>1294</v>
+        <v>1297</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>1295</v>
+        <v>1298</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>1296</v>
+        <v>1299</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>1297</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>1298</v>
+        <v>1301</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>1299</v>
+        <v>1302</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>1301</v>
+        <v>1304</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>1302</v>
+        <v>1305</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>1303</v>
+        <v>1306</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>1304</v>
+        <v>1307</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>1305</v>
+        <v>1308</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>1306</v>
+        <v>1309</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>1307</v>
+        <v>1310</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>1308</v>
+        <v>1311</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>1309</v>
+        <v>1312</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>1310</v>
+        <v>1313</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32591,31 +32636,31 @@
         <v>369</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="s">
-        <v>1311</v>
+        <v>1314</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="12" t="s">
-        <v>1312</v>
+        <v>1315</v>
       </c>
       <c r="B49" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="12" t="s">
-        <v>1313</v>
+        <v>1316</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32623,15 +32668,15 @@
         <v>399</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="12" t="s">
-        <v>1314</v>
+        <v>1317</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32639,111 +32684,111 @@
         <v>383</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="12" t="s">
-        <v>1315</v>
+        <v>1318</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="12" t="s">
-        <v>1316</v>
+        <v>1319</v>
       </c>
       <c r="B55" s="12" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="12" t="s">
-        <v>1317</v>
+        <v>1320</v>
       </c>
       <c r="B56" s="12" t="s">
-        <v>1318</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="12" t="s">
-        <v>1319</v>
+        <v>1322</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="12" t="s">
-        <v>1321</v>
+        <v>1324</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="12" t="s">
-        <v>1322</v>
+        <v>1325</v>
       </c>
       <c r="B59" s="12" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="12" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B60" s="12" t="s">
         <v>1323</v>
-      </c>
-      <c r="B60" s="12" t="s">
-        <v>1320</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="12" t="s">
-        <v>1324</v>
+        <v>1327</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="12" t="s">
-        <v>1325</v>
+        <v>1328</v>
       </c>
       <c r="B62" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="12" t="s">
-        <v>1326</v>
+        <v>1329</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="12" t="s">
-        <v>1327</v>
+        <v>1330</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="12" t="s">
-        <v>1328</v>
+        <v>1331</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="12" t="s">
-        <v>1329</v>
+        <v>1332</v>
       </c>
       <c r="B66" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32751,71 +32796,71 @@
         <v>1062</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="12" t="s">
-        <v>1330</v>
+        <v>1333</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="12" t="s">
-        <v>1331</v>
+        <v>1334</v>
       </c>
       <c r="B69" s="12" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="12" t="s">
-        <v>1332</v>
+        <v>1335</v>
       </c>
       <c r="B70" s="12" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="12" t="s">
-        <v>1333</v>
+        <v>1336</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="12" t="s">
-        <v>1334</v>
+        <v>1337</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="12" t="s">
-        <v>1335</v>
+        <v>1338</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="12" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="B74" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="12" t="s">
-        <v>1337</v>
+        <v>1340</v>
       </c>
       <c r="B75" s="12" t="s">
-        <v>1338</v>
+        <v>1341</v>
       </c>
     </row>
   </sheetData>
@@ -32848,269 +32893,269 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1339</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>1340</v>
+        <v>1343</v>
       </c>
       <c r="B2" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>1341</v>
+        <v>1344</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1342</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>1343</v>
+        <v>1346</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>1344</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>1345</v>
+        <v>1348</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>1346</v>
+        <v>1349</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>1347</v>
+        <v>1350</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>1349</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>1350</v>
+        <v>1353</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>1349</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>1351</v>
+        <v>1354</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>1352</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>1353</v>
+        <v>1356</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>1354</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>1355</v>
+        <v>1358</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>1356</v>
+        <v>1359</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>1352</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>1357</v>
+        <v>1360</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>1358</v>
+        <v>1361</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>1360</v>
+        <v>1363</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>1349</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>1361</v>
+        <v>1364</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>1362</v>
+        <v>1365</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>1363</v>
+        <v>1366</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>1364</v>
+        <v>1367</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>1349</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>1349</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>1366</v>
+        <v>1369</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>1349</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>1367</v>
+        <v>1370</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>1352</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>1368</v>
+        <v>1371</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>1369</v>
+        <v>1372</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>1349</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>1370</v>
+        <v>1373</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>1371</v>
+        <v>1374</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>1372</v>
+        <v>1375</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>1373</v>
+        <v>1376</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>1261</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>1374</v>
+        <v>1377</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>1375</v>
+        <v>1378</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>1349</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>1376</v>
+        <v>1379</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>1338</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>1349</v>
+        <v>1352</v>
       </c>
     </row>
   </sheetData>

--- a/docs/handbook/sbmig-reference.xlsx
+++ b/docs/handbook/sbmig-reference.xlsx
@@ -38,7 +38,7 @@
     <definedName function="false" hidden="true" localSheetId="13" name="_xlnm._FilterDatabase" vbProcedure="false">지식노트!$A$4:$F$20</definedName>
     <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">픽스처!$A$4:$N$32</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">핸들러!$A$4:$H$30</definedName>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">CLI!$A$4:$H$119</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">CLI!$A$4:$H$120</definedName>
     <definedName function="false" hidden="true" localSheetId="11" name="_xlnm._FilterDatabase" vbProcedure="false">Jakarta라이브러리!$A$4:$G$48</definedName>
     <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">REST_API!$A$4:$E$18</definedName>
   </definedNames>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4406" uniqueCount="2316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4412" uniqueCount="2320">
   <si>
     <r>
       <rPr>
@@ -5768,6 +5768,18 @@
   </si>
   <si>
     <t xml:space="preserve">seconds uvicorn waits for open connections (SSE streams) on shutdown before closing them</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_upload_mb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">--max-upload-mb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">largest project zip the UI accepts, in MB (default: $SBMIG_MAX_UPLOAD_MB or 512; 0 = no limit, e.g. for one oversized project)</t>
   </si>
   <si>
     <t xml:space="preserve">sbmig version</t>
@@ -15738,8 +15750,8 @@
         <v>16</v>
       </c>
       <c r="C8" s="4" t="n">
-        <f aca="false">COUNTA(CLI!A5:A5119)</f>
-        <v>115</v>
+        <f aca="false">COUNTA(CLI!A5:A5120)</f>
+        <v>116</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>17</v>
@@ -15916,7 +15928,7 @@
       </c>
       <c r="C20" s="6" t="n">
         <f aca="false">SUM(C5:C19)</f>
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15959,12 +15971,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1381</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>1382</v>
+        <v>1386</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -15978,45 +15990,45 @@
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>1383</v>
+        <v>1387</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1384</v>
+        <v>1388</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>1385</v>
+        <v>1389</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>1386</v>
+        <v>1390</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>1388</v>
+        <v>1392</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>1389</v>
+        <v>1393</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>1390</v>
+        <v>1394</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>1391</v>
+        <v>1395</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>1392</v>
+        <v>1396</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>178</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>1393</v>
+        <v>1397</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>461</v>
@@ -16028,21 +16040,21 @@
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="12" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>1396</v>
+        <v>1400</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>178</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>1393</v>
+        <v>1397</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>379</v>
@@ -16051,30 +16063,30 @@
         <v>878</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>1397</v>
+        <v>1401</v>
       </c>
       <c r="G6" s="12" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>1403</v>
+      </c>
+      <c r="I6" s="12" t="s">
         <v>1398</v>
       </c>
-      <c r="H6" s="12" t="s">
-        <v>1399</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>1394</v>
-      </c>
       <c r="J6" s="12" t="s">
-        <v>1400</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>1401</v>
+        <v>1405</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>178</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>1393</v>
+        <v>1397</v>
       </c>
       <c r="D7" s="12" t="s">
         <v>461</v>
@@ -16083,28 +16095,28 @@
         <v>878</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>1402</v>
+        <v>1406</v>
       </c>
       <c r="G7" s="13"/>
       <c r="H7" s="12" t="s">
-        <v>1403</v>
+        <v>1407</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>1404</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>1405</v>
+        <v>1409</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>178</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>1393</v>
+        <v>1397</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>379</v>
@@ -16113,28 +16125,28 @@
         <v>878</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>1406</v>
+        <v>1410</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="12" t="s">
-        <v>1403</v>
+        <v>1407</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>1408</v>
+        <v>1412</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>178</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>1409</v>
+        <v>1413</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>379</v>
@@ -16143,30 +16155,30 @@
         <v>878</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>1411</v>
+        <v>1415</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>1412</v>
+        <v>1416</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>1413</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>1414</v>
+        <v>1418</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>178</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>1409</v>
+        <v>1413</v>
       </c>
       <c r="D10" s="12" t="s">
         <v>379</v>
@@ -16175,28 +16187,28 @@
         <v>878</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>1411</v>
+        <v>1415</v>
       </c>
       <c r="H10" s="13"/>
       <c r="I10" s="12" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>1415</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>1416</v>
+        <v>1420</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>178</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>1409</v>
+        <v>1413</v>
       </c>
       <c r="D11" s="12" t="s">
         <v>379</v>
@@ -16205,28 +16217,28 @@
         <v>878</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>1417</v>
+        <v>1421</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="12" t="s">
-        <v>1418</v>
+        <v>1422</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>1419</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>1420</v>
+        <v>1424</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>178</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>1409</v>
+        <v>1413</v>
       </c>
       <c r="D12" s="12" t="s">
         <v>379</v>
@@ -16235,28 +16247,28 @@
         <v>878</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>1421</v>
+        <v>1425</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>1422</v>
+        <v>1426</v>
       </c>
       <c r="H12" s="13"/>
       <c r="I12" s="12" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>1423</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>1424</v>
+        <v>1428</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>178</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>1409</v>
+        <v>1413</v>
       </c>
       <c r="D13" s="12" t="s">
         <v>379</v>
@@ -16265,28 +16277,28 @@
         <v>878</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>1425</v>
+        <v>1429</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>1426</v>
+        <v>1430</v>
       </c>
       <c r="H13" s="13"/>
       <c r="I13" s="12" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>1427</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>1428</v>
+        <v>1432</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>178</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>1429</v>
+        <v>1433</v>
       </c>
       <c r="D14" s="12" t="s">
         <v>379</v>
@@ -16295,30 +16307,30 @@
         <v>878</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>1430</v>
+        <v>1434</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>1431</v>
+        <v>1435</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>1432</v>
+        <v>1436</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>1433</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>1434</v>
+        <v>1438</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>178</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>1409</v>
+        <v>1413</v>
       </c>
       <c r="D15" s="12" t="s">
         <v>379</v>
@@ -16328,21 +16340,21 @@
       <c r="G15" s="13"/>
       <c r="H15" s="13"/>
       <c r="I15" s="12" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>1435</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>1436</v>
+        <v>1440</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>178</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>1409</v>
+        <v>1413</v>
       </c>
       <c r="D16" s="12" t="s">
         <v>379</v>
@@ -16351,24 +16363,24 @@
       <c r="F16" s="13"/>
       <c r="G16" s="13"/>
       <c r="H16" s="12" t="s">
-        <v>1437</v>
+        <v>1441</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>1438</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>1439</v>
+        <v>1443</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>178</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>1409</v>
+        <v>1413</v>
       </c>
       <c r="D17" s="12" t="s">
         <v>379</v>
@@ -16378,21 +16390,21 @@
       <c r="G17" s="13"/>
       <c r="H17" s="13"/>
       <c r="I17" s="12" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>1440</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>1441</v>
+        <v>1445</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>178</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>1409</v>
+        <v>1413</v>
       </c>
       <c r="D18" s="12" t="s">
         <v>379</v>
@@ -16402,21 +16414,21 @@
       <c r="G18" s="13"/>
       <c r="H18" s="13"/>
       <c r="I18" s="12" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>1442</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>178</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>1409</v>
+        <v>1413</v>
       </c>
       <c r="D19" s="12" t="s">
         <v>379</v>
@@ -16426,21 +16438,21 @@
       <c r="G19" s="13"/>
       <c r="H19" s="13"/>
       <c r="I19" s="12" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>1444</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>1445</v>
+        <v>1449</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>178</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>1409</v>
+        <v>1413</v>
       </c>
       <c r="D20" s="12" t="s">
         <v>379</v>
@@ -16450,21 +16462,21 @@
       <c r="G20" s="13"/>
       <c r="H20" s="13"/>
       <c r="I20" s="12" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>1446</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>1447</v>
+        <v>1451</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>178</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>1448</v>
+        <v>1452</v>
       </c>
       <c r="D21" s="12" t="s">
         <v>379</v>
@@ -16474,15 +16486,15 @@
       <c r="G21" s="13"/>
       <c r="H21" s="13"/>
       <c r="I21" s="12" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>1450</v>
+        <v>1454</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>950</v>
@@ -16494,19 +16506,19 @@
       <c r="E22" s="13"/>
       <c r="F22" s="13"/>
       <c r="G22" s="12" t="s">
-        <v>1411</v>
+        <v>1415</v>
       </c>
       <c r="H22" s="13"/>
       <c r="I22" s="12" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>1451</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>1452</v>
+        <v>1456</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>950</v>
@@ -16518,19 +16530,19 @@
       <c r="E23" s="13"/>
       <c r="F23" s="13"/>
       <c r="G23" s="12" t="s">
-        <v>1411</v>
+        <v>1415</v>
       </c>
       <c r="H23" s="13"/>
       <c r="I23" s="12" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>1453</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>1454</v>
+        <v>1458</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>950</v>
@@ -16544,15 +16556,15 @@
       <c r="G24" s="13"/>
       <c r="H24" s="13"/>
       <c r="I24" s="12" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>1455</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>1456</v>
+        <v>1460</v>
       </c>
       <c r="B25" s="12" t="s">
         <v>950</v>
@@ -16566,15 +16578,15 @@
       <c r="G25" s="13"/>
       <c r="H25" s="13"/>
       <c r="I25" s="12" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>1458</v>
+        <v>1462</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>178</v>
@@ -16588,15 +16600,15 @@
       <c r="G26" s="13"/>
       <c r="H26" s="13"/>
       <c r="I26" s="12" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>1459</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>1460</v>
+        <v>1464</v>
       </c>
       <c r="B27" s="12" t="s">
         <v>178</v>
@@ -16610,15 +16622,15 @@
       <c r="G27" s="13"/>
       <c r="H27" s="13"/>
       <c r="I27" s="12" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>1461</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>1462</v>
+        <v>1466</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>178</v>
@@ -16632,21 +16644,21 @@
       <c r="G28" s="13"/>
       <c r="H28" s="13"/>
       <c r="I28" s="12" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>1463</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>1464</v>
+        <v>1468</v>
       </c>
       <c r="B29" s="12" t="s">
         <v>178</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="D29" s="12" t="s">
         <v>379</v>
@@ -16656,21 +16668,21 @@
       <c r="G29" s="13"/>
       <c r="H29" s="13"/>
       <c r="I29" s="12" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>1466</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="B30" s="12" t="s">
         <v>178</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="D30" s="12" t="s">
         <v>379</v>
@@ -16680,15 +16692,15 @@
       <c r="G30" s="13"/>
       <c r="H30" s="13"/>
       <c r="I30" s="12" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>1468</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
       <c r="B31" s="12" t="s">
         <v>178</v>
@@ -16702,15 +16714,15 @@
       <c r="G31" s="13"/>
       <c r="H31" s="13"/>
       <c r="I31" s="12" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J31" s="12" t="s">
-        <v>1470</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>1471</v>
+        <v>1475</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>178</v>
@@ -16724,15 +16736,15 @@
       <c r="G32" s="13"/>
       <c r="H32" s="13"/>
       <c r="I32" s="12" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>1472</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>1473</v>
+        <v>1477</v>
       </c>
       <c r="B33" s="12" t="s">
         <v>178</v>
@@ -16746,15 +16758,15 @@
       <c r="G33" s="13"/>
       <c r="H33" s="13"/>
       <c r="I33" s="12" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J33" s="12" t="s">
-        <v>1474</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>1475</v>
+        <v>1479</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>178</v>
@@ -16768,15 +16780,15 @@
       <c r="G34" s="13"/>
       <c r="H34" s="13"/>
       <c r="I34" s="12" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J34" s="12" t="s">
-        <v>1476</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>1477</v>
+        <v>1481</v>
       </c>
       <c r="B35" s="12" t="s">
         <v>178</v>
@@ -16790,15 +16802,15 @@
       <c r="G35" s="13"/>
       <c r="H35" s="13"/>
       <c r="I35" s="12" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J35" s="12" t="s">
-        <v>1478</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>1479</v>
+        <v>1483</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>178</v>
@@ -16812,15 +16824,15 @@
       <c r="G36" s="13"/>
       <c r="H36" s="13"/>
       <c r="I36" s="12" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>1480</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>1481</v>
+        <v>1485</v>
       </c>
       <c r="B37" s="12" t="s">
         <v>178</v>
@@ -16834,15 +16846,15 @@
       <c r="G37" s="13"/>
       <c r="H37" s="13"/>
       <c r="I37" s="12" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J37" s="12" t="s">
-        <v>1482</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>1483</v>
+        <v>1487</v>
       </c>
       <c r="B38" s="12" t="s">
         <v>178</v>
@@ -16856,10 +16868,10 @@
       <c r="G38" s="13"/>
       <c r="H38" s="13"/>
       <c r="I38" s="12" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J38" s="12" t="s">
-        <v>1484</v>
+        <v>1488</v>
       </c>
     </row>
   </sheetData>
@@ -16901,12 +16913,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>1485</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>1486</v>
+        <v>1490</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -16921,48 +16933,48 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>1487</v>
+        <v>1491</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1488</v>
+        <v>1492</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>1385</v>
+        <v>1389</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>1489</v>
+        <v>1493</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>1490</v>
+        <v>1494</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>1491</v>
+        <v>1495</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>1492</v>
+        <v>1496</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>1493</v>
+        <v>1497</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>1494</v>
+        <v>1498</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>1495</v>
+        <v>1499</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>1496</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>1497</v>
+        <v>1501</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>1497</v>
+        <v>1501</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>1498</v>
+        <v>1502</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>794</v>
@@ -16971,28 +16983,28 @@
         <v>1001</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>1499</v>
+        <v>1503</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>1500</v>
+        <v>1504</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>1501</v>
+        <v>1505</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>1502</v>
+        <v>1506</v>
       </c>
       <c r="J5" s="13"/>
       <c r="K5" s="12" t="s">
-        <v>1503</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>1504</v>
+        <v>1508</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>1504</v>
+        <v>1508</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="12" t="s">
@@ -17002,28 +17014,28 @@
         <v>1001</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>1505</v>
+        <v>1509</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>1506</v>
+        <v>1510</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>1507</v>
+        <v>1511</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="J6" s="13"/>
       <c r="K6" s="12" t="s">
-        <v>1508</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>1509</v>
+        <v>1513</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>1509</v>
+        <v>1513</v>
       </c>
       <c r="C7" s="13"/>
       <c r="D7" s="12" t="s">
@@ -17033,115 +17045,115 @@
         <v>1001</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>1510</v>
+        <v>1514</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>1511</v>
+        <v>1515</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>1512</v>
+        <v>1516</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>1456</v>
+        <v>1460</v>
       </c>
       <c r="J7" s="13"/>
       <c r="K7" s="12" t="s">
-        <v>1513</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>1514</v>
+        <v>1518</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>1514</v>
+        <v>1518</v>
       </c>
       <c r="C8" s="13"/>
       <c r="D8" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F8" s="12" t="s">
+        <v>1520</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>1521</v>
+      </c>
+      <c r="H8" s="12" t="s">
         <v>1516</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>1517</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>1512</v>
       </c>
       <c r="I8" s="13"/>
       <c r="J8" s="13"/>
       <c r="K8" s="12" t="s">
-        <v>1518</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>1519</v>
+        <v>1523</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>1519</v>
+        <v>1523</v>
       </c>
       <c r="C9" s="13"/>
       <c r="D9" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>1520</v>
+        <v>1524</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>1521</v>
+        <v>1525</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>1512</v>
+        <v>1516</v>
       </c>
       <c r="I9" s="13"/>
       <c r="J9" s="13"/>
       <c r="K9" s="12" t="s">
-        <v>1522</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>1523</v>
+        <v>1527</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>1523</v>
+        <v>1527</v>
       </c>
       <c r="C10" s="13"/>
       <c r="D10" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>1524</v>
+        <v>1528</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>1525</v>
+        <v>1529</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>1512</v>
+        <v>1516</v>
       </c>
       <c r="I10" s="13"/>
       <c r="J10" s="13"/>
       <c r="K10" s="12" t="s">
-        <v>1526</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>1527</v>
+        <v>1531</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>1527</v>
+        <v>1531</v>
       </c>
       <c r="C11" s="13"/>
       <c r="D11" s="12" t="s">
@@ -17151,1072 +17163,1072 @@
         <v>1001</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>1528</v>
+        <v>1532</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>1529</v>
+        <v>1533</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>1530</v>
+        <v>1534</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>1445</v>
+        <v>1449</v>
       </c>
       <c r="J11" s="13"/>
       <c r="K11" s="12" t="s">
-        <v>1531</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>1532</v>
+        <v>1536</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>1532</v>
+        <v>1536</v>
       </c>
       <c r="C12" s="13"/>
       <c r="D12" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>1533</v>
+        <v>1537</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>1534</v>
+        <v>1538</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>1535</v>
+        <v>1539</v>
       </c>
       <c r="I12" s="13"/>
       <c r="J12" s="13"/>
       <c r="K12" s="12" t="s">
-        <v>1536</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>1537</v>
+        <v>1541</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>1537</v>
+        <v>1541</v>
       </c>
       <c r="C13" s="13"/>
       <c r="D13" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>1538</v>
+        <v>1542</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>1539</v>
+        <v>1543</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>1507</v>
+        <v>1511</v>
       </c>
       <c r="I13" s="13"/>
       <c r="J13" s="13"/>
       <c r="K13" s="12" t="s">
-        <v>1540</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="C14" s="13"/>
       <c r="D14" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>1543</v>
+        <v>1547</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>1544</v>
+        <v>1548</v>
       </c>
       <c r="I14" s="13"/>
       <c r="J14" s="13"/>
       <c r="K14" s="12" t="s">
-        <v>1545</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>1546</v>
+        <v>1550</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>1546</v>
+        <v>1550</v>
       </c>
       <c r="C15" s="13"/>
       <c r="D15" s="12" t="s">
         <v>817</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>1547</v>
+        <v>1551</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>1548</v>
+        <v>1552</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>1507</v>
+        <v>1511</v>
       </c>
       <c r="I15" s="13"/>
       <c r="J15" s="13"/>
       <c r="K15" s="12" t="s">
-        <v>1549</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>1550</v>
+        <v>1554</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>1550</v>
+        <v>1554</v>
       </c>
       <c r="C16" s="13"/>
       <c r="D16" s="12" t="s">
         <v>835</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>1551</v>
+        <v>1555</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>1552</v>
+        <v>1556</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>1553</v>
+        <v>1557</v>
       </c>
       <c r="I16" s="13"/>
       <c r="J16" s="13"/>
       <c r="K16" s="12" t="s">
-        <v>1554</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>1555</v>
+        <v>1559</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>1555</v>
+        <v>1559</v>
       </c>
       <c r="C17" s="13"/>
       <c r="D17" s="12" t="s">
         <v>835</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>1556</v>
+        <v>1560</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>1557</v>
+        <v>1561</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>1558</v>
+        <v>1562</v>
       </c>
       <c r="I17" s="13"/>
       <c r="J17" s="13"/>
       <c r="K17" s="12" t="s">
-        <v>1559</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>1560</v>
+        <v>1564</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>1560</v>
+        <v>1564</v>
       </c>
       <c r="C18" s="13"/>
       <c r="D18" s="12" t="s">
         <v>835</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>1561</v>
+        <v>1565</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="I18" s="13"/>
       <c r="J18" s="13"/>
       <c r="K18" s="12" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
       <c r="C19" s="13"/>
       <c r="D19" s="12" t="s">
         <v>835</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>1566</v>
+        <v>1570</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>1568</v>
+        <v>1572</v>
       </c>
       <c r="I19" s="13"/>
       <c r="J19" s="13"/>
       <c r="K19" s="12" t="s">
-        <v>1569</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>1570</v>
+        <v>1574</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>1570</v>
+        <v>1574</v>
       </c>
       <c r="C20" s="13"/>
       <c r="D20" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>1571</v>
+        <v>1575</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>1572</v>
+        <v>1576</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>1573</v>
+        <v>1577</v>
       </c>
       <c r="I20" s="13"/>
       <c r="J20" s="13"/>
       <c r="K20" s="12" t="s">
-        <v>1574</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>1575</v>
+        <v>1579</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>1575</v>
+        <v>1579</v>
       </c>
       <c r="C21" s="13"/>
       <c r="D21" s="12" t="s">
         <v>835</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>1576</v>
+        <v>1580</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>1577</v>
+        <v>1581</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>1578</v>
+        <v>1582</v>
       </c>
       <c r="I21" s="13"/>
       <c r="J21" s="13"/>
       <c r="K21" s="12" t="s">
-        <v>1579</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>1580</v>
+        <v>1584</v>
       </c>
       <c r="B22" s="13"/>
       <c r="C22" s="12" t="s">
-        <v>1581</v>
+        <v>1585</v>
       </c>
       <c r="D22" s="12" t="s">
         <v>817</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>1583</v>
+        <v>1587</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>1584</v>
+        <v>1588</v>
       </c>
       <c r="I22" s="13"/>
       <c r="J22" s="13"/>
       <c r="K22" s="12" t="s">
-        <v>1585</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>1586</v>
+        <v>1590</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>1586</v>
+        <v>1590</v>
       </c>
       <c r="C23" s="13"/>
       <c r="D23" s="12" t="s">
         <v>835</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>1587</v>
+        <v>1591</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>1588</v>
+        <v>1592</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>1589</v>
+        <v>1593</v>
       </c>
       <c r="I23" s="13"/>
       <c r="J23" s="13"/>
       <c r="K23" s="12" t="s">
-        <v>1590</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>1591</v>
+        <v>1595</v>
       </c>
       <c r="B24" s="13"/>
       <c r="C24" s="12" t="s">
-        <v>1592</v>
+        <v>1596</v>
       </c>
       <c r="D24" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>1593</v>
+        <v>1597</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>1594</v>
+        <v>1598</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>1595</v>
+        <v>1599</v>
       </c>
       <c r="I24" s="13"/>
       <c r="J24" s="13"/>
       <c r="K24" s="12" t="s">
-        <v>1596</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>1597</v>
+        <v>1601</v>
       </c>
       <c r="B25" s="13"/>
       <c r="C25" s="12" t="s">
-        <v>1598</v>
+        <v>1602</v>
       </c>
       <c r="D25" s="12" t="s">
         <v>817</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>1599</v>
+        <v>1603</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>1600</v>
+        <v>1604</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>1601</v>
+        <v>1605</v>
       </c>
       <c r="I25" s="13"/>
       <c r="J25" s="13"/>
       <c r="K25" s="12" t="s">
-        <v>1602</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>1603</v>
+        <v>1607</v>
       </c>
       <c r="B26" s="13"/>
       <c r="C26" s="12" t="s">
-        <v>1604</v>
+        <v>1608</v>
       </c>
       <c r="D26" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>1605</v>
+        <v>1609</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>1606</v>
+        <v>1610</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>1607</v>
+        <v>1611</v>
       </c>
       <c r="I26" s="13"/>
       <c r="J26" s="13"/>
       <c r="K26" s="12" t="s">
-        <v>1608</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
       <c r="B27" s="13"/>
       <c r="C27" s="12" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="D27" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F27" s="12" t="s">
+        <v>1615</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>1616</v>
+      </c>
+      <c r="H27" s="12" t="s">
         <v>1611</v>
-      </c>
-      <c r="G27" s="12" t="s">
-        <v>1612</v>
-      </c>
-      <c r="H27" s="12" t="s">
-        <v>1607</v>
       </c>
       <c r="I27" s="13"/>
       <c r="J27" s="13"/>
       <c r="K27" s="12" t="s">
-        <v>1613</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>1614</v>
+        <v>1618</v>
       </c>
       <c r="B28" s="13"/>
       <c r="C28" s="12" t="s">
-        <v>1615</v>
+        <v>1619</v>
       </c>
       <c r="D28" s="12" t="s">
         <v>835</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>1616</v>
+        <v>1620</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>1617</v>
+        <v>1621</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>1618</v>
+        <v>1622</v>
       </c>
       <c r="I28" s="13"/>
       <c r="J28" s="13"/>
       <c r="K28" s="12" t="s">
-        <v>1619</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="C29" s="13"/>
       <c r="D29" s="12" t="s">
         <v>835</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>1621</v>
+        <v>1625</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>1622</v>
+        <v>1626</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>1623</v>
+        <v>1627</v>
       </c>
       <c r="I29" s="13"/>
       <c r="J29" s="13"/>
       <c r="K29" s="12" t="s">
-        <v>1624</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>1625</v>
+        <v>1629</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="12" t="s">
-        <v>1626</v>
+        <v>1630</v>
       </c>
       <c r="D30" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>1627</v>
+        <v>1631</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>1628</v>
+        <v>1632</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>1629</v>
+        <v>1633</v>
       </c>
       <c r="I30" s="13"/>
       <c r="J30" s="13"/>
       <c r="K30" s="12" t="s">
-        <v>1630</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>1631</v>
+        <v>1635</v>
       </c>
       <c r="B31" s="13"/>
       <c r="C31" s="12" t="s">
-        <v>1632</v>
+        <v>1636</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>1633</v>
+        <v>1637</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>1634</v>
+        <v>1638</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>1635</v>
+        <v>1639</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>1636</v>
+        <v>1640</v>
       </c>
       <c r="I31" s="13"/>
       <c r="J31" s="13"/>
       <c r="K31" s="12" t="s">
-        <v>1637</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>1638</v>
+        <v>1642</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>1638</v>
+        <v>1642</v>
       </c>
       <c r="C32" s="13"/>
       <c r="D32" s="12" t="s">
         <v>835</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>1639</v>
+        <v>1643</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>1640</v>
+        <v>1644</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>1641</v>
+        <v>1645</v>
       </c>
       <c r="I32" s="13"/>
       <c r="J32" s="13"/>
       <c r="K32" s="12" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>1643</v>
+        <v>1647</v>
       </c>
       <c r="B33" s="13"/>
       <c r="C33" s="12" t="s">
-        <v>1644</v>
+        <v>1648</v>
       </c>
       <c r="D33" s="12" t="s">
         <v>817</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>1645</v>
+        <v>1649</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>1646</v>
+        <v>1650</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>1647</v>
+        <v>1651</v>
       </c>
       <c r="I33" s="13"/>
       <c r="J33" s="13"/>
       <c r="K33" s="12" t="s">
-        <v>1648</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>1649</v>
+        <v>1653</v>
       </c>
       <c r="B34" s="13"/>
       <c r="C34" s="12" t="s">
-        <v>1650</v>
+        <v>1654</v>
       </c>
       <c r="D34" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>1651</v>
+        <v>1655</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>1652</v>
+        <v>1656</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>1653</v>
+        <v>1657</v>
       </c>
       <c r="I34" s="13"/>
       <c r="J34" s="13"/>
       <c r="K34" s="12" t="s">
-        <v>1654</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>1655</v>
+        <v>1659</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>1655</v>
+        <v>1659</v>
       </c>
       <c r="C35" s="13"/>
       <c r="D35" s="12" t="s">
         <v>835</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>1656</v>
+        <v>1660</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>1657</v>
+        <v>1661</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>1658</v>
+        <v>1662</v>
       </c>
       <c r="I35" s="13"/>
       <c r="J35" s="13"/>
       <c r="K35" s="12" t="s">
-        <v>1659</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>1660</v>
+        <v>1664</v>
       </c>
       <c r="B36" s="13"/>
       <c r="C36" s="12" t="s">
-        <v>1661</v>
+        <v>1665</v>
       </c>
       <c r="D36" s="12" t="s">
         <v>817</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>1662</v>
+        <v>1666</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>1663</v>
+        <v>1667</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>1664</v>
+        <v>1668</v>
       </c>
       <c r="I36" s="13"/>
       <c r="J36" s="13"/>
       <c r="K36" s="12" t="s">
-        <v>1665</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>1666</v>
+        <v>1670</v>
       </c>
       <c r="B37" s="13"/>
       <c r="C37" s="12" t="s">
-        <v>1667</v>
+        <v>1671</v>
       </c>
       <c r="D37" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>1668</v>
+        <v>1672</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>1669</v>
+        <v>1673</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>1670</v>
+        <v>1674</v>
       </c>
       <c r="I37" s="13"/>
       <c r="J37" s="13"/>
       <c r="K37" s="12" t="s">
-        <v>1671</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>1672</v>
+        <v>1676</v>
       </c>
       <c r="B38" s="13"/>
       <c r="C38" s="12" t="s">
-        <v>1673</v>
+        <v>1677</v>
       </c>
       <c r="D38" s="12" t="s">
         <v>817</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>1674</v>
+        <v>1678</v>
       </c>
       <c r="G38" s="12" t="s">
-        <v>1675</v>
+        <v>1679</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="I38" s="13"/>
       <c r="J38" s="13"/>
       <c r="K38" s="12" t="s">
-        <v>1677</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>1678</v>
+        <v>1682</v>
       </c>
       <c r="B39" s="13"/>
       <c r="C39" s="12" t="s">
-        <v>1679</v>
+        <v>1683</v>
       </c>
       <c r="D39" s="12" t="s">
         <v>835</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>1680</v>
+        <v>1684</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>1681</v>
+        <v>1685</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>1682</v>
+        <v>1686</v>
       </c>
       <c r="I39" s="13"/>
       <c r="J39" s="13"/>
       <c r="K39" s="12" t="s">
-        <v>1683</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>1684</v>
+        <v>1688</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>1684</v>
+        <v>1688</v>
       </c>
       <c r="C40" s="13"/>
       <c r="D40" s="12" t="s">
         <v>835</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>1685</v>
+        <v>1689</v>
       </c>
       <c r="G40" s="12" t="s">
-        <v>1686</v>
+        <v>1690</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>1687</v>
+        <v>1691</v>
       </c>
       <c r="I40" s="13"/>
       <c r="J40" s="13"/>
       <c r="K40" s="12" t="s">
-        <v>1688</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>1689</v>
+        <v>1693</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>1689</v>
+        <v>1693</v>
       </c>
       <c r="C41" s="13"/>
       <c r="D41" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>1690</v>
+        <v>1694</v>
       </c>
       <c r="G41" s="12" t="s">
-        <v>1691</v>
+        <v>1695</v>
       </c>
       <c r="H41" s="12" t="s">
-        <v>1692</v>
+        <v>1696</v>
       </c>
       <c r="I41" s="13"/>
       <c r="J41" s="13"/>
       <c r="K41" s="12" t="s">
-        <v>1693</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>1694</v>
+        <v>1698</v>
       </c>
       <c r="B42" s="13"/>
       <c r="C42" s="12" t="s">
-        <v>1695</v>
+        <v>1699</v>
       </c>
       <c r="D42" s="12" t="s">
         <v>835</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>1696</v>
+        <v>1700</v>
       </c>
       <c r="G42" s="12" t="s">
-        <v>1697</v>
+        <v>1701</v>
       </c>
       <c r="H42" s="12" t="s">
-        <v>1698</v>
+        <v>1702</v>
       </c>
       <c r="I42" s="13"/>
       <c r="J42" s="13"/>
       <c r="K42" s="12" t="s">
-        <v>1699</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>1701</v>
+        <v>1705</v>
       </c>
       <c r="C43" s="13"/>
       <c r="D43" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>1702</v>
+        <v>1706</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>1703</v>
+        <v>1707</v>
       </c>
       <c r="H43" s="12" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="I43" s="13"/>
       <c r="J43" s="13"/>
       <c r="K43" s="12" t="s">
-        <v>1705</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>1706</v>
+        <v>1710</v>
       </c>
       <c r="B44" s="13"/>
       <c r="C44" s="12" t="s">
-        <v>1707</v>
+        <v>1711</v>
       </c>
       <c r="D44" s="12" t="s">
         <v>835</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>1708</v>
+        <v>1712</v>
       </c>
       <c r="G44" s="12" t="s">
-        <v>1709</v>
+        <v>1713</v>
       </c>
       <c r="H44" s="12" t="s">
-        <v>1710</v>
+        <v>1714</v>
       </c>
       <c r="I44" s="13"/>
       <c r="J44" s="13"/>
       <c r="K44" s="12" t="s">
-        <v>1711</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>1712</v>
+        <v>1716</v>
       </c>
       <c r="B45" s="13"/>
       <c r="C45" s="12" t="s">
-        <v>1713</v>
+        <v>1717</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>1633</v>
+        <v>1637</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F45" s="12" t="s">
-        <v>1714</v>
+        <v>1718</v>
       </c>
       <c r="G45" s="12" t="s">
-        <v>1715</v>
+        <v>1719</v>
       </c>
       <c r="H45" s="12" t="s">
-        <v>1716</v>
+        <v>1720</v>
       </c>
       <c r="I45" s="13"/>
       <c r="J45" s="13"/>
       <c r="K45" s="12" t="s">
-        <v>1717</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>1718</v>
+        <v>1722</v>
       </c>
       <c r="B46" s="13"/>
       <c r="C46" s="12" t="s">
-        <v>1719</v>
+        <v>1723</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>1633</v>
+        <v>1637</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F46" s="12" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="G46" s="12" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="H46" s="12" t="s">
-        <v>1722</v>
+        <v>1726</v>
       </c>
       <c r="I46" s="13"/>
       <c r="J46" s="13"/>
       <c r="K46" s="12" t="s">
-        <v>1723</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>1724</v>
+        <v>1728</v>
       </c>
       <c r="B47" s="13"/>
       <c r="C47" s="12" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="D47" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F47" s="12" t="s">
+        <v>1730</v>
+      </c>
+      <c r="G47" s="12" t="s">
+        <v>1731</v>
+      </c>
+      <c r="H47" s="12" t="s">
         <v>1726</v>
-      </c>
-      <c r="G47" s="12" t="s">
-        <v>1727</v>
-      </c>
-      <c r="H47" s="12" t="s">
-        <v>1722</v>
       </c>
       <c r="I47" s="13"/>
       <c r="J47" s="13"/>
       <c r="K47" s="12" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="s">
-        <v>1729</v>
+        <v>1733</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>1729</v>
+        <v>1733</v>
       </c>
       <c r="C48" s="13"/>
       <c r="D48" s="12" t="s">
@@ -18226,600 +18238,600 @@
         <v>1001</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>1730</v>
+        <v>1734</v>
       </c>
       <c r="G48" s="12" t="s">
-        <v>1731</v>
+        <v>1735</v>
       </c>
       <c r="H48" s="12" t="s">
-        <v>1732</v>
+        <v>1736</v>
       </c>
       <c r="I48" s="12" t="s">
-        <v>1447</v>
+        <v>1451</v>
       </c>
       <c r="J48" s="13"/>
       <c r="K48" s="12" t="s">
-        <v>1733</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="12" t="s">
-        <v>1734</v>
+        <v>1738</v>
       </c>
       <c r="B49" s="13"/>
       <c r="C49" s="12" t="s">
-        <v>1735</v>
+        <v>1739</v>
       </c>
       <c r="D49" s="12" t="s">
         <v>817</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>1736</v>
+        <v>1740</v>
       </c>
       <c r="G49" s="12" t="s">
-        <v>1737</v>
+        <v>1741</v>
       </c>
       <c r="H49" s="12" t="s">
-        <v>1738</v>
+        <v>1742</v>
       </c>
       <c r="I49" s="13"/>
       <c r="J49" s="13"/>
       <c r="K49" s="12" t="s">
-        <v>1739</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="12" t="s">
-        <v>1740</v>
+        <v>1744</v>
       </c>
       <c r="B50" s="13"/>
       <c r="C50" s="12" t="s">
-        <v>1741</v>
+        <v>1745</v>
       </c>
       <c r="D50" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>1742</v>
+        <v>1746</v>
       </c>
       <c r="G50" s="12" t="s">
-        <v>1743</v>
+        <v>1747</v>
       </c>
       <c r="H50" s="12" t="s">
-        <v>1744</v>
+        <v>1748</v>
       </c>
       <c r="I50" s="13"/>
       <c r="J50" s="13"/>
       <c r="K50" s="12" t="s">
-        <v>1745</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="12" t="s">
-        <v>1746</v>
+        <v>1750</v>
       </c>
       <c r="B51" s="13"/>
       <c r="C51" s="12" t="s">
-        <v>1747</v>
+        <v>1751</v>
       </c>
       <c r="D51" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F51" s="12" t="s">
-        <v>1748</v>
+        <v>1752</v>
       </c>
       <c r="G51" s="12" t="s">
-        <v>1749</v>
+        <v>1753</v>
       </c>
       <c r="H51" s="12" t="s">
-        <v>1750</v>
+        <v>1754</v>
       </c>
       <c r="I51" s="13"/>
       <c r="J51" s="13"/>
       <c r="K51" s="12" t="s">
-        <v>1751</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="12" t="s">
-        <v>1752</v>
+        <v>1756</v>
       </c>
       <c r="B52" s="13"/>
       <c r="C52" s="12" t="s">
-        <v>1753</v>
+        <v>1757</v>
       </c>
       <c r="D52" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F52" s="12" t="s">
-        <v>1754</v>
+        <v>1758</v>
       </c>
       <c r="G52" s="12" t="s">
-        <v>1755</v>
+        <v>1759</v>
       </c>
       <c r="H52" s="12" t="s">
-        <v>1756</v>
+        <v>1760</v>
       </c>
       <c r="I52" s="13"/>
       <c r="J52" s="13"/>
       <c r="K52" s="12" t="s">
-        <v>1757</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="12" t="s">
-        <v>1758</v>
+        <v>1762</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>1758</v>
+        <v>1762</v>
       </c>
       <c r="C53" s="13"/>
       <c r="D53" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F53" s="12" t="s">
-        <v>1759</v>
+        <v>1763</v>
       </c>
       <c r="G53" s="12" t="s">
-        <v>1760</v>
+        <v>1764</v>
       </c>
       <c r="H53" s="12" t="s">
-        <v>1761</v>
+        <v>1765</v>
       </c>
       <c r="I53" s="13"/>
       <c r="J53" s="13"/>
       <c r="K53" s="12" t="s">
-        <v>1762</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="12" t="s">
-        <v>1763</v>
+        <v>1767</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>1763</v>
+        <v>1767</v>
       </c>
       <c r="C54" s="13"/>
       <c r="D54" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F54" s="12" t="s">
-        <v>1764</v>
+        <v>1768</v>
       </c>
       <c r="G54" s="12" t="s">
-        <v>1765</v>
+        <v>1769</v>
       </c>
       <c r="H54" s="12" t="s">
-        <v>1766</v>
+        <v>1770</v>
       </c>
       <c r="I54" s="13"/>
       <c r="J54" s="13"/>
       <c r="K54" s="12" t="s">
-        <v>1767</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="12" t="s">
-        <v>1768</v>
+        <v>1772</v>
       </c>
       <c r="B55" s="13"/>
       <c r="C55" s="12" t="s">
-        <v>1769</v>
+        <v>1773</v>
       </c>
       <c r="D55" s="12" t="s">
         <v>835</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F55" s="12" t="s">
-        <v>1770</v>
+        <v>1774</v>
       </c>
       <c r="G55" s="12" t="s">
-        <v>1771</v>
+        <v>1775</v>
       </c>
       <c r="H55" s="12" t="s">
-        <v>1772</v>
+        <v>1776</v>
       </c>
       <c r="I55" s="13"/>
       <c r="J55" s="13"/>
       <c r="K55" s="12" t="s">
-        <v>1773</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="12" t="s">
-        <v>1774</v>
+        <v>1778</v>
       </c>
       <c r="B56" s="13"/>
       <c r="C56" s="12" t="s">
-        <v>1775</v>
+        <v>1779</v>
       </c>
       <c r="D56" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F56" s="12" t="s">
-        <v>1776</v>
+        <v>1780</v>
       </c>
       <c r="G56" s="12" t="s">
-        <v>1777</v>
+        <v>1781</v>
       </c>
       <c r="H56" s="12" t="s">
-        <v>1778</v>
+        <v>1782</v>
       </c>
       <c r="I56" s="13"/>
       <c r="J56" s="13"/>
       <c r="K56" s="12" t="s">
-        <v>1779</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="12" t="s">
-        <v>1780</v>
+        <v>1784</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>1780</v>
+        <v>1784</v>
       </c>
       <c r="C57" s="13"/>
       <c r="D57" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F57" s="12" t="s">
-        <v>1781</v>
+        <v>1785</v>
       </c>
       <c r="G57" s="12" t="s">
-        <v>1782</v>
+        <v>1786</v>
       </c>
       <c r="H57" s="12" t="s">
-        <v>1783</v>
+        <v>1787</v>
       </c>
       <c r="I57" s="13"/>
       <c r="J57" s="13"/>
       <c r="K57" s="12" t="s">
-        <v>1784</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="12" t="s">
-        <v>1785</v>
+        <v>1789</v>
       </c>
       <c r="B58" s="13"/>
       <c r="C58" s="12" t="s">
-        <v>1786</v>
+        <v>1790</v>
       </c>
       <c r="D58" s="12" t="s">
         <v>835</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>1787</v>
+        <v>1791</v>
       </c>
       <c r="G58" s="12" t="s">
-        <v>1788</v>
+        <v>1792</v>
       </c>
       <c r="H58" s="12" t="s">
-        <v>1789</v>
+        <v>1793</v>
       </c>
       <c r="I58" s="13"/>
       <c r="J58" s="13"/>
       <c r="K58" s="12" t="s">
-        <v>1790</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="12" t="s">
-        <v>1791</v>
+        <v>1795</v>
       </c>
       <c r="B59" s="13"/>
       <c r="C59" s="12" t="s">
-        <v>1792</v>
+        <v>1796</v>
       </c>
       <c r="D59" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F59" s="12" t="s">
-        <v>1793</v>
+        <v>1797</v>
       </c>
       <c r="G59" s="12" t="s">
-        <v>1794</v>
+        <v>1798</v>
       </c>
       <c r="H59" s="12" t="s">
-        <v>1795</v>
+        <v>1799</v>
       </c>
       <c r="I59" s="13"/>
       <c r="J59" s="13"/>
       <c r="K59" s="12" t="s">
-        <v>1796</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="12" t="s">
-        <v>1797</v>
+        <v>1801</v>
       </c>
       <c r="B60" s="13"/>
       <c r="C60" s="12" t="s">
-        <v>1798</v>
+        <v>1802</v>
       </c>
       <c r="D60" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F60" s="12" t="s">
-        <v>1799</v>
+        <v>1803</v>
       </c>
       <c r="G60" s="12" t="s">
-        <v>1800</v>
+        <v>1804</v>
       </c>
       <c r="H60" s="12" t="s">
-        <v>1766</v>
+        <v>1770</v>
       </c>
       <c r="I60" s="13"/>
       <c r="J60" s="13"/>
       <c r="K60" s="12" t="s">
-        <v>1801</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="12" t="s">
-        <v>1802</v>
+        <v>1806</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>1802</v>
+        <v>1806</v>
       </c>
       <c r="C61" s="13"/>
       <c r="D61" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F61" s="12" t="s">
-        <v>1803</v>
+        <v>1807</v>
       </c>
       <c r="G61" s="12" t="s">
-        <v>1804</v>
+        <v>1808</v>
       </c>
       <c r="H61" s="12" t="s">
-        <v>1805</v>
+        <v>1809</v>
       </c>
       <c r="I61" s="13"/>
       <c r="J61" s="13"/>
       <c r="K61" s="12" t="s">
-        <v>1806</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="12" t="s">
-        <v>1807</v>
+        <v>1811</v>
       </c>
       <c r="B62" s="12" t="s">
-        <v>1808</v>
+        <v>1812</v>
       </c>
       <c r="C62" s="13"/>
       <c r="D62" s="12" t="s">
         <v>835</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F62" s="12" t="s">
-        <v>1809</v>
+        <v>1813</v>
       </c>
       <c r="G62" s="12" t="s">
-        <v>1810</v>
+        <v>1814</v>
       </c>
       <c r="H62" s="12" t="s">
-        <v>1811</v>
+        <v>1815</v>
       </c>
       <c r="I62" s="13"/>
       <c r="J62" s="13"/>
       <c r="K62" s="12" t="s">
-        <v>1812</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="12" t="s">
-        <v>1813</v>
+        <v>1817</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>1814</v>
+        <v>1818</v>
       </c>
       <c r="C63" s="13"/>
       <c r="D63" s="12" t="s">
         <v>817</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F63" s="12" t="s">
-        <v>1815</v>
+        <v>1819</v>
       </c>
       <c r="G63" s="12" t="s">
-        <v>1816</v>
+        <v>1820</v>
       </c>
       <c r="H63" s="12" t="s">
-        <v>1817</v>
+        <v>1821</v>
       </c>
       <c r="I63" s="13"/>
       <c r="J63" s="13"/>
       <c r="K63" s="12" t="s">
-        <v>1818</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="12" t="s">
-        <v>1819</v>
+        <v>1823</v>
       </c>
       <c r="B64" s="13"/>
       <c r="C64" s="12" t="s">
-        <v>1820</v>
+        <v>1824</v>
       </c>
       <c r="D64" s="12" t="s">
         <v>835</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F64" s="12" t="s">
-        <v>1821</v>
+        <v>1825</v>
       </c>
       <c r="G64" s="12" t="s">
-        <v>1822</v>
+        <v>1826</v>
       </c>
       <c r="H64" s="12" t="s">
-        <v>1823</v>
+        <v>1827</v>
       </c>
       <c r="I64" s="13"/>
       <c r="J64" s="13"/>
       <c r="K64" s="12" t="s">
-        <v>1824</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="12" t="s">
-        <v>1825</v>
+        <v>1829</v>
       </c>
       <c r="B65" s="13"/>
       <c r="C65" s="12" t="s">
-        <v>1826</v>
+        <v>1830</v>
       </c>
       <c r="D65" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F65" s="12" t="s">
-        <v>1827</v>
+        <v>1831</v>
       </c>
       <c r="G65" s="12" t="s">
-        <v>1828</v>
+        <v>1832</v>
       </c>
       <c r="H65" s="12" t="s">
-        <v>1817</v>
+        <v>1821</v>
       </c>
       <c r="I65" s="13"/>
       <c r="J65" s="13"/>
       <c r="K65" s="12" t="s">
-        <v>1829</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="12" t="s">
-        <v>1830</v>
+        <v>1834</v>
       </c>
       <c r="B66" s="13"/>
       <c r="C66" s="12" t="s">
-        <v>1831</v>
+        <v>1835</v>
       </c>
       <c r="D66" s="12" t="s">
         <v>835</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F66" s="12" t="s">
-        <v>1832</v>
+        <v>1836</v>
       </c>
       <c r="G66" s="12" t="s">
-        <v>1833</v>
+        <v>1837</v>
       </c>
       <c r="H66" s="12" t="s">
-        <v>1834</v>
+        <v>1838</v>
       </c>
       <c r="I66" s="13"/>
       <c r="J66" s="13"/>
       <c r="K66" s="12" t="s">
-        <v>1835</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="12" t="s">
-        <v>1836</v>
+        <v>1840</v>
       </c>
       <c r="B67" s="13"/>
       <c r="C67" s="12" t="s">
-        <v>1837</v>
+        <v>1841</v>
       </c>
       <c r="D67" s="12" t="s">
         <v>817</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F67" s="12" t="s">
-        <v>1838</v>
+        <v>1842</v>
       </c>
       <c r="G67" s="12" t="s">
-        <v>1839</v>
+        <v>1843</v>
       </c>
       <c r="H67" s="12" t="s">
-        <v>1840</v>
+        <v>1844</v>
       </c>
       <c r="I67" s="13"/>
       <c r="J67" s="13"/>
       <c r="K67" s="12" t="s">
-        <v>1841</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="12" t="s">
-        <v>1842</v>
+        <v>1846</v>
       </c>
       <c r="B68" s="13"/>
       <c r="C68" s="12" t="s">
-        <v>1843</v>
+        <v>1847</v>
       </c>
       <c r="D68" s="12" t="s">
         <v>794</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="F68" s="12" t="s">
+        <v>1848</v>
+      </c>
+      <c r="G68" s="12" t="s">
+        <v>1849</v>
+      </c>
+      <c r="H68" s="12" t="s">
         <v>1844</v>
-      </c>
-      <c r="G68" s="12" t="s">
-        <v>1845</v>
-      </c>
-      <c r="H68" s="12" t="s">
-        <v>1840</v>
       </c>
       <c r="I68" s="13"/>
       <c r="J68" s="13"/>
       <c r="K68" s="12" t="s">
-        <v>1846</v>
+        <v>1850</v>
       </c>
     </row>
   </sheetData>
@@ -18857,12 +18869,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>1847</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>1848</v>
+        <v>1852</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -18873,953 +18885,953 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>1849</v>
+        <v>1853</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1850</v>
+        <v>1854</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>1851</v>
+        <v>1855</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>1852</v>
+        <v>1856</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>1144</v>
+        <v>1148</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>1853</v>
+        <v>1857</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>1854</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>1855</v>
+        <v>1859</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>1856</v>
+        <v>1860</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>1857</v>
+        <v>1861</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>1858</v>
+        <v>1862</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>1859</v>
+        <v>1863</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>1860</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>1861</v>
+        <v>1865</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="12" t="s">
-        <v>1862</v>
+        <v>1866</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>1862</v>
+        <v>1866</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>1863</v>
+        <v>1867</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>1864</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>1865</v>
+        <v>1869</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="12" t="s">
-        <v>1866</v>
+        <v>1870</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>1867</v>
+        <v>1871</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>1868</v>
+        <v>1872</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>1869</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>1870</v>
+        <v>1874</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>1871</v>
+        <v>1875</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>1872</v>
+        <v>1876</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>1873</v>
+        <v>1877</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>1874</v>
+        <v>1878</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>1875</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>1876</v>
+        <v>1880</v>
       </c>
       <c r="B9" s="13"/>
       <c r="C9" s="12" t="s">
-        <v>1872</v>
+        <v>1876</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>1877</v>
+        <v>1881</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>1878</v>
+        <v>1882</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>1879</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>1880</v>
+        <v>1884</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="12" t="s">
-        <v>1872</v>
+        <v>1876</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>1877</v>
+        <v>1881</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>1878</v>
+        <v>1882</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>1879</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>1881</v>
+        <v>1885</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="12" t="s">
-        <v>1872</v>
+        <v>1876</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>1877</v>
+        <v>1881</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>1878</v>
+        <v>1882</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>1879</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>1882</v>
+        <v>1886</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="12" t="s">
-        <v>1872</v>
+        <v>1876</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>1877</v>
+        <v>1881</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>1878</v>
+        <v>1882</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>1879</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>1883</v>
+        <v>1887</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="12" t="s">
-        <v>1872</v>
+        <v>1876</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>1877</v>
+        <v>1881</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>1878</v>
+        <v>1882</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>1879</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>1884</v>
+        <v>1888</v>
       </c>
       <c r="B14" s="13"/>
       <c r="C14" s="12" t="s">
-        <v>1885</v>
+        <v>1889</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>1886</v>
+        <v>1890</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>1887</v>
+        <v>1891</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>1888</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>1889</v>
+        <v>1893</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="12" t="s">
-        <v>1885</v>
+        <v>1889</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>1886</v>
+        <v>1890</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>1887</v>
+        <v>1891</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>1888</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>1890</v>
+        <v>1894</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="12" t="s">
-        <v>1885</v>
+        <v>1889</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>1886</v>
+        <v>1890</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>1887</v>
+        <v>1891</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>1888</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>1891</v>
+        <v>1895</v>
       </c>
       <c r="B17" s="13"/>
       <c r="C17" s="12" t="s">
-        <v>1885</v>
+        <v>1889</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>1886</v>
+        <v>1890</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>1887</v>
+        <v>1891</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>1888</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>1892</v>
+        <v>1896</v>
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="12" t="s">
-        <v>1885</v>
+        <v>1889</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>1886</v>
+        <v>1890</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>1887</v>
+        <v>1891</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>1888</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>1893</v>
+        <v>1897</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="12" t="s">
-        <v>1885</v>
+        <v>1889</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>1886</v>
+        <v>1890</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>1887</v>
+        <v>1891</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>1888</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>1894</v>
+        <v>1898</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="12" t="s">
-        <v>1872</v>
+        <v>1876</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>1857</v>
+        <v>1861</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>1895</v>
+        <v>1899</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>1896</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>1897</v>
+        <v>1901</v>
       </c>
       <c r="B21" s="13"/>
       <c r="C21" s="12" t="s">
-        <v>1872</v>
+        <v>1876</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>1857</v>
+        <v>1861</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>1895</v>
+        <v>1899</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>1896</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>1898</v>
+        <v>1902</v>
       </c>
       <c r="B22" s="13"/>
       <c r="C22" s="12" t="s">
-        <v>1899</v>
+        <v>1903</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>1900</v>
+        <v>1904</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>1901</v>
+        <v>1905</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>1902</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>1903</v>
+        <v>1907</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="12" t="s">
-        <v>1899</v>
+        <v>1903</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>1900</v>
+        <v>1904</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>1901</v>
+        <v>1905</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>1902</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>1904</v>
+        <v>1908</v>
       </c>
       <c r="B24" s="13"/>
       <c r="C24" s="12" t="s">
-        <v>1899</v>
+        <v>1903</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>1900</v>
+        <v>1904</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>1901</v>
+        <v>1905</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>1902</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>1905</v>
+        <v>1909</v>
       </c>
       <c r="B25" s="13"/>
       <c r="C25" s="12" t="s">
-        <v>1899</v>
+        <v>1903</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>1900</v>
+        <v>1904</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>1901</v>
+        <v>1905</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>1902</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>1906</v>
+        <v>1910</v>
       </c>
       <c r="B26" s="13"/>
       <c r="C26" s="12" t="s">
-        <v>1899</v>
+        <v>1903</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>1900</v>
+        <v>1904</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>1901</v>
+        <v>1905</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>1902</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>1907</v>
+        <v>1911</v>
       </c>
       <c r="B27" s="13"/>
       <c r="C27" s="12" t="s">
-        <v>1899</v>
+        <v>1903</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>1900</v>
+        <v>1904</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>1901</v>
+        <v>1905</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>1902</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>1908</v>
+        <v>1912</v>
       </c>
       <c r="B28" s="13"/>
       <c r="C28" s="12" t="s">
-        <v>1899</v>
+        <v>1903</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>1900</v>
+        <v>1904</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>1901</v>
+        <v>1905</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>1902</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>1909</v>
+        <v>1913</v>
       </c>
       <c r="B29" s="13"/>
       <c r="C29" s="12" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>1910</v>
+        <v>1914</v>
       </c>
       <c r="E29" s="12" t="s">
         <v>59</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>1911</v>
+        <v>1915</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>1912</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>1913</v>
+        <v>1917</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="12" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>1910</v>
+        <v>1914</v>
       </c>
       <c r="E30" s="12" t="s">
         <v>59</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>1911</v>
+        <v>1915</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>1912</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="B31" s="13"/>
       <c r="C31" s="12" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>1910</v>
+        <v>1914</v>
       </c>
       <c r="E31" s="12" t="s">
         <v>59</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>1911</v>
+        <v>1915</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>1912</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>1915</v>
+        <v>1919</v>
       </c>
       <c r="B32" s="13"/>
       <c r="C32" s="12" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>1910</v>
+        <v>1914</v>
       </c>
       <c r="E32" s="12" t="s">
         <v>59</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>1911</v>
+        <v>1915</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>1912</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>1916</v>
+        <v>1920</v>
       </c>
       <c r="B33" s="13"/>
       <c r="C33" s="12" t="s">
-        <v>1872</v>
+        <v>1876</v>
       </c>
       <c r="D33" s="12" t="s">
         <v>61</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>1917</v>
+        <v>1921</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>1918</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>1919</v>
+        <v>1923</v>
       </c>
       <c r="B34" s="13"/>
       <c r="C34" s="12" t="s">
-        <v>1872</v>
+        <v>1876</v>
       </c>
       <c r="D34" s="12" t="s">
         <v>61</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>1920</v>
+        <v>1924</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>1921</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>1922</v>
+        <v>1926</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="12" t="s">
-        <v>1872</v>
+        <v>1876</v>
       </c>
       <c r="D35" s="12" t="s">
         <v>61</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>1920</v>
+        <v>1924</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>1921</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>1923</v>
+        <v>1927</v>
       </c>
       <c r="B36" s="13"/>
       <c r="C36" s="12" t="s">
-        <v>1872</v>
+        <v>1876</v>
       </c>
       <c r="D36" s="12" t="s">
         <v>61</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>1920</v>
+        <v>1924</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>1921</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>1924</v>
+        <v>1928</v>
       </c>
       <c r="B37" s="13"/>
       <c r="C37" s="12" t="s">
-        <v>1925</v>
+        <v>1929</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>1927</v>
+        <v>1931</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>1928</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>1929</v>
+        <v>1933</v>
       </c>
       <c r="B38" s="13"/>
       <c r="C38" s="12" t="s">
-        <v>1925</v>
+        <v>1929</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>1927</v>
+        <v>1931</v>
       </c>
       <c r="G38" s="12" t="s">
-        <v>1928</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>1930</v>
+        <v>1934</v>
       </c>
       <c r="B39" s="13"/>
       <c r="C39" s="12" t="s">
-        <v>1872</v>
+        <v>1876</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>1641</v>
+        <v>1645</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>1931</v>
+        <v>1935</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>1932</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>1933</v>
+        <v>1937</v>
       </c>
       <c r="B40" s="13"/>
       <c r="C40" s="12" t="s">
-        <v>1872</v>
+        <v>1876</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>1641</v>
+        <v>1645</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>1931</v>
+        <v>1935</v>
       </c>
       <c r="G40" s="12" t="s">
-        <v>1932</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>1934</v>
+        <v>1938</v>
       </c>
       <c r="B41" s="13"/>
       <c r="C41" s="12" t="s">
-        <v>1935</v>
+        <v>1939</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>1936</v>
+        <v>1940</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>1937</v>
+        <v>1941</v>
       </c>
       <c r="G41" s="12" t="s">
-        <v>1938</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>1939</v>
+        <v>1943</v>
       </c>
       <c r="B42" s="13"/>
       <c r="C42" s="12" t="s">
-        <v>1940</v>
+        <v>1944</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>1941</v>
+        <v>1945</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>1942</v>
+        <v>1946</v>
       </c>
       <c r="G42" s="12" t="s">
-        <v>1943</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>1944</v>
+        <v>1948</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="12" t="s">
-        <v>1945</v>
+        <v>1949</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>1738</v>
+        <v>1742</v>
       </c>
       <c r="E43" s="12" t="s">
         <v>281</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>1946</v>
+        <v>1950</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>1947</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>1948</v>
+        <v>1952</v>
       </c>
       <c r="B44" s="13"/>
       <c r="C44" s="12" t="s">
-        <v>1949</v>
+        <v>1953</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>1941</v>
+        <v>1945</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>1950</v>
+        <v>1954</v>
       </c>
       <c r="G44" s="12" t="s">
-        <v>1951</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>1952</v>
+        <v>1956</v>
       </c>
       <c r="B45" s="13"/>
       <c r="C45" s="12" t="s">
-        <v>1949</v>
+        <v>1953</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>1941</v>
+        <v>1945</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="F45" s="12" t="s">
-        <v>1950</v>
+        <v>1954</v>
       </c>
       <c r="G45" s="12" t="s">
-        <v>1951</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>1953</v>
+        <v>1957</v>
       </c>
       <c r="B46" s="13"/>
       <c r="C46" s="12" t="s">
-        <v>1949</v>
+        <v>1953</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>1941</v>
+        <v>1945</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="F46" s="12" t="s">
-        <v>1950</v>
+        <v>1954</v>
       </c>
       <c r="G46" s="12" t="s">
-        <v>1951</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>1954</v>
+        <v>1958</v>
       </c>
       <c r="B47" s="13"/>
       <c r="C47" s="12" t="s">
-        <v>1949</v>
+        <v>1953</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>1941</v>
+        <v>1945</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>1950</v>
+        <v>1954</v>
       </c>
       <c r="G47" s="12" t="s">
-        <v>1951</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="s">
-        <v>1955</v>
+        <v>1959</v>
       </c>
       <c r="B48" s="13"/>
       <c r="C48" s="12" t="s">
-        <v>1949</v>
+        <v>1953</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>1941</v>
+        <v>1945</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>1950</v>
+        <v>1954</v>
       </c>
       <c r="G48" s="12" t="s">
-        <v>1951</v>
+        <v>1955</v>
       </c>
     </row>
   </sheetData>
@@ -19856,12 +19868,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>1956</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>1957</v>
+        <v>1961</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -19871,243 +19883,243 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>1850</v>
+        <v>1854</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1958</v>
+        <v>1962</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>1959</v>
+        <v>1963</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>1960</v>
+        <v>1964</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>1961</v>
+        <v>1965</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>1962</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>1963</v>
+        <v>1967</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>1964</v>
+        <v>1968</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>1866</v>
+        <v>1870</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="12" t="s">
-        <v>1965</v>
+        <v>1969</v>
       </c>
       <c r="F5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>1966</v>
+        <v>1970</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>1964</v>
+        <v>1968</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>1866</v>
+        <v>1870</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="12" t="s">
-        <v>1965</v>
+        <v>1969</v>
       </c>
       <c r="F6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>1967</v>
+        <v>1971</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>1964</v>
+        <v>1968</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>1866</v>
+        <v>1870</v>
       </c>
       <c r="D7" s="13"/>
       <c r="E7" s="12" t="s">
-        <v>1965</v>
+        <v>1969</v>
       </c>
       <c r="F7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>1968</v>
+        <v>1972</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>1969</v>
+        <v>1973</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>1970</v>
+        <v>1974</v>
       </c>
       <c r="D8" s="13"/>
       <c r="E8" s="12" t="s">
-        <v>1971</v>
+        <v>1975</v>
       </c>
       <c r="F8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>1972</v>
+        <v>1976</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>1973</v>
+        <v>1977</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>1872</v>
+        <v>1876</v>
       </c>
       <c r="D9" s="13"/>
       <c r="E9" s="12" t="s">
-        <v>1974</v>
+        <v>1978</v>
       </c>
       <c r="F9" s="13"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>1975</v>
+        <v>1979</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>1976</v>
+        <v>1980</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>1941</v>
+        <v>1945</v>
       </c>
       <c r="D10" s="13"/>
       <c r="E10" s="12" t="s">
-        <v>1977</v>
+        <v>1981</v>
       </c>
       <c r="F10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>1978</v>
+        <v>1982</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>1979</v>
+        <v>1983</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>1941</v>
+        <v>1945</v>
       </c>
       <c r="D11" s="13"/>
       <c r="E11" s="12" t="s">
-        <v>1980</v>
+        <v>1984</v>
       </c>
       <c r="F11" s="13"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>1981</v>
+        <v>1985</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>1979</v>
+        <v>1983</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>1941</v>
+        <v>1945</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="12" t="s">
-        <v>1980</v>
+        <v>1984</v>
       </c>
       <c r="F12" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>1982</v>
+        <v>1986</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>1983</v>
+        <v>1987</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>1984</v>
+        <v>1988</v>
       </c>
       <c r="D13" s="13"/>
       <c r="E13" s="12" t="s">
-        <v>1985</v>
+        <v>1989</v>
       </c>
       <c r="F13" s="13"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>1986</v>
+        <v>1990</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>1987</v>
+        <v>1991</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>1988</v>
+        <v>1992</v>
       </c>
       <c r="D14" s="13"/>
       <c r="E14" s="12" t="s">
-        <v>1985</v>
+        <v>1989</v>
       </c>
       <c r="F14" s="13"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>1989</v>
+        <v>1993</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>1990</v>
+        <v>1994</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>1991</v>
+        <v>1995</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="12" t="s">
-        <v>1992</v>
+        <v>1996</v>
       </c>
       <c r="F15" s="13"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>1993</v>
+        <v>1997</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>1994</v>
+        <v>1998</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>1995</v>
+        <v>1999</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>1996</v>
+        <v>2000</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>1997</v>
+        <v>2001</v>
       </c>
       <c r="F16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>1998</v>
+        <v>2002</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>1999</v>
+        <v>2003</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>1722</v>
+        <v>1726</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="12" t="s">
-        <v>2000</v>
+        <v>2004</v>
       </c>
       <c r="F17" s="13"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>2001</v>
+        <v>2005</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>2002</v>
+        <v>2006</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>2003</v>
+        <v>2007</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="13"/>
@@ -20115,13 +20127,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>2004</v>
+        <v>2008</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>2005</v>
+        <v>2009</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>2003</v>
+        <v>2007</v>
       </c>
       <c r="D19" s="13"/>
       <c r="E19" s="13"/>
@@ -20129,13 +20141,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>2006</v>
+        <v>2010</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>2005</v>
+        <v>2009</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>2003</v>
+        <v>2007</v>
       </c>
       <c r="D20" s="13"/>
       <c r="E20" s="13"/>
@@ -20143,13 +20155,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
+        <v>2011</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>2012</v>
+      </c>
+      <c r="C21" s="12" t="s">
         <v>2007</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>2008</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>2003</v>
       </c>
       <c r="D21" s="13"/>
       <c r="E21" s="13"/>
@@ -20157,13 +20169,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>2009</v>
+        <v>2013</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="D22" s="13"/>
       <c r="E22" s="13"/>
@@ -20171,10 +20183,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>2013</v>
+        <v>2017</v>
       </c>
       <c r="C23" s="13"/>
       <c r="D23" s="13"/>
@@ -20185,10 +20197,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>2014</v>
+        <v>2018</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="C24" s="13"/>
       <c r="D24" s="13"/>
@@ -20199,10 +20211,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="C25" s="13"/>
       <c r="D25" s="13"/>
@@ -20213,10 +20225,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="C26" s="13"/>
       <c r="D26" s="13"/>
@@ -20227,10 +20239,10 @@
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="C27" s="13"/>
       <c r="D27" s="13"/>
@@ -20241,10 +20253,10 @@
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>2023</v>
+        <v>2027</v>
       </c>
       <c r="C28" s="13"/>
       <c r="D28" s="13"/>
@@ -20255,10 +20267,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>2024</v>
+        <v>2028</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>2025</v>
+        <v>2029</v>
       </c>
       <c r="C29" s="12" t="s">
         <v>61</v>
@@ -20269,13 +20281,13 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>2026</v>
+        <v>2030</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>2027</v>
+        <v>2031</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>2028</v>
+        <v>2032</v>
       </c>
       <c r="D30" s="13"/>
       <c r="E30" s="13"/>
@@ -20283,13 +20295,13 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>2029</v>
+        <v>2033</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>2027</v>
+        <v>2031</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>2028</v>
+        <v>2032</v>
       </c>
       <c r="D31" s="13"/>
       <c r="E31" s="13"/>
@@ -20297,13 +20309,13 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>2030</v>
+        <v>2034</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>2031</v>
+        <v>2035</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>2032</v>
+        <v>2036</v>
       </c>
       <c r="D32" s="13"/>
       <c r="E32" s="13"/>
@@ -20311,13 +20323,13 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>2033</v>
+        <v>2037</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>2034</v>
+        <v>2038</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>2035</v>
+        <v>2039</v>
       </c>
       <c r="D33" s="13"/>
       <c r="E33" s="13"/>
@@ -20325,13 +20337,13 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>2036</v>
+        <v>2040</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>2034</v>
+        <v>2038</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>2035</v>
+        <v>2039</v>
       </c>
       <c r="D34" s="13"/>
       <c r="E34" s="13"/>
@@ -20339,13 +20351,13 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>2037</v>
+        <v>2041</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>2034</v>
+        <v>2038</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>2035</v>
+        <v>2039</v>
       </c>
       <c r="D35" s="13"/>
       <c r="E35" s="13"/>
@@ -20353,13 +20365,13 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
+        <v>2042</v>
+      </c>
+      <c r="B36" s="12" t="s">
         <v>2038</v>
       </c>
-      <c r="B36" s="12" t="s">
-        <v>2034</v>
-      </c>
       <c r="C36" s="12" t="s">
-        <v>2035</v>
+        <v>2039</v>
       </c>
       <c r="D36" s="13"/>
       <c r="E36" s="13"/>
@@ -20367,13 +20379,13 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
+        <v>2043</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>2038</v>
+      </c>
+      <c r="C37" s="12" t="s">
         <v>2039</v>
-      </c>
-      <c r="B37" s="12" t="s">
-        <v>2034</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>2035</v>
       </c>
       <c r="D37" s="13"/>
       <c r="E37" s="13"/>
@@ -20381,13 +20393,13 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>2040</v>
+        <v>2044</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>2041</v>
+        <v>2045</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>2042</v>
+        <v>2046</v>
       </c>
       <c r="D38" s="13"/>
       <c r="E38" s="13"/>
@@ -20395,13 +20407,13 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>2043</v>
+        <v>2047</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>2041</v>
+        <v>2045</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>2042</v>
+        <v>2046</v>
       </c>
       <c r="D39" s="13"/>
       <c r="E39" s="13"/>
@@ -20409,13 +20421,13 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>2044</v>
+        <v>2048</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>2045</v>
+        <v>2049</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>2046</v>
+        <v>2050</v>
       </c>
       <c r="D40" s="13"/>
       <c r="E40" s="13"/>
@@ -20423,13 +20435,13 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>2047</v>
+        <v>2051</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>2048</v>
+        <v>2052</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>2049</v>
+        <v>2053</v>
       </c>
       <c r="D41" s="13"/>
       <c r="E41" s="13"/>
@@ -20437,13 +20449,13 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>2050</v>
+        <v>2054</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>2048</v>
+        <v>2052</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>2049</v>
+        <v>2053</v>
       </c>
       <c r="D42" s="13"/>
       <c r="E42" s="13"/>
@@ -20451,13 +20463,13 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>2051</v>
+        <v>2055</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>2052</v>
+        <v>2056</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>1995</v>
+        <v>1999</v>
       </c>
       <c r="D43" s="13"/>
       <c r="E43" s="13"/>
@@ -20465,13 +20477,13 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>2053</v>
+        <v>2057</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>2054</v>
+        <v>2058</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>2055</v>
+        <v>2059</v>
       </c>
       <c r="D44" s="13"/>
       <c r="E44" s="13"/>
@@ -20479,13 +20491,13 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>2056</v>
+        <v>2060</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>2057</v>
+        <v>2061</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>2058</v>
+        <v>2062</v>
       </c>
       <c r="D45" s="13"/>
       <c r="E45" s="13"/>
@@ -20493,13 +20505,13 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>2059</v>
+        <v>2063</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>2060</v>
+        <v>2064</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>2058</v>
+        <v>2062</v>
       </c>
       <c r="D46" s="13"/>
       <c r="E46" s="13"/>
@@ -20507,13 +20519,13 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
+        <v>2065</v>
+      </c>
+      <c r="B47" s="12" t="s">
         <v>2061</v>
       </c>
-      <c r="B47" s="12" t="s">
-        <v>2057</v>
-      </c>
       <c r="C47" s="12" t="s">
-        <v>2058</v>
+        <v>2062</v>
       </c>
       <c r="D47" s="13"/>
       <c r="E47" s="13"/>
@@ -20521,16 +20533,16 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="s">
-        <v>2062</v>
+        <v>2066</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>2063</v>
+        <v>2067</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>2064</v>
+        <v>2068</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>2065</v>
+        <v>2069</v>
       </c>
       <c r="E48" s="13"/>
       <c r="F48" s="13"/>
@@ -20569,12 +20581,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>2066</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>2067</v>
+        <v>2071</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -20584,30 +20596,30 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>2068</v>
+        <v>2072</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1491</v>
+        <v>1495</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>2069</v>
+        <v>2073</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>1143</v>
+        <v>1147</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>2070</v>
+        <v>2074</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>2071</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>2072</v>
+        <v>2076</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>2073</v>
+        <v>2077</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -20618,16 +20630,16 @@
     </row>
     <row r="6" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>2074</v>
+        <v>2078</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>2075</v>
+        <v>2079</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>2076</v>
+        <v>2080</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>2077</v>
+        <v>2081</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>461</v>
@@ -20636,34 +20648,34 @@
     </row>
     <row r="7" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>2078</v>
+        <v>2082</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>2079</v>
+        <v>2083</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>2080</v>
+        <v>2084</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>2077</v>
+        <v>2081</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>2081</v>
+        <v>2085</v>
       </c>
       <c r="F7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>2082</v>
+        <v>2086</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>2083</v>
+        <v>2087</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>2084</v>
+        <v>2088</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>2085</v>
+        <v>2089</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>379</v>
@@ -20672,52 +20684,52 @@
     </row>
     <row r="9" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>2086</v>
+        <v>2090</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>2087</v>
+        <v>2091</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>2088</v>
+        <v>2092</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>2085</v>
+        <v>2089</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>2089</v>
+        <v>2093</v>
       </c>
       <c r="F9" s="13"/>
     </row>
     <row r="10" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>2090</v>
+        <v>2094</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>2091</v>
+        <v>2095</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>2092</v>
+        <v>2096</v>
       </c>
       <c r="D10" s="12" t="s">
+        <v>2097</v>
+      </c>
+      <c r="E10" s="12" t="s">
         <v>2093</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>2089</v>
       </c>
       <c r="F10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>2094</v>
+        <v>2098</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>2095</v>
+        <v>2099</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>2096</v>
+        <v>2100</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>2097</v>
+        <v>2101</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>379</v>
@@ -20726,16 +20738,16 @@
     </row>
     <row r="12" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>2098</v>
+        <v>2102</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>2099</v>
+        <v>2103</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>2100</v>
+        <v>2104</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>2101</v>
+        <v>2105</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>379</v>
@@ -20744,106 +20756,106 @@
     </row>
     <row r="13" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>2102</v>
+        <v>2106</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>2103</v>
+        <v>2107</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>2104</v>
+        <v>2108</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>2105</v>
+        <v>2109</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>2089</v>
+        <v>2093</v>
       </c>
       <c r="F13" s="13"/>
     </row>
     <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>2106</v>
+        <v>2110</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>2107</v>
+        <v>2111</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>2108</v>
+        <v>2112</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>2077</v>
+        <v>2081</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>2081</v>
+        <v>2085</v>
       </c>
       <c r="F14" s="13"/>
     </row>
     <row r="15" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>2109</v>
+        <v>2113</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>2110</v>
+        <v>2114</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>2111</v>
+        <v>2115</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>2077</v>
+        <v>2081</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>2112</v>
+        <v>2116</v>
       </c>
       <c r="F15" s="13"/>
     </row>
     <row r="16" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>2113</v>
+        <v>2117</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>2114</v>
+        <v>2118</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>2115</v>
+        <v>2119</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>2101</v>
+        <v>2105</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>2089</v>
+        <v>2093</v>
       </c>
       <c r="F16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>2116</v>
+        <v>2120</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>2117</v>
+        <v>2121</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>2118</v>
+        <v>2122</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>2077</v>
+        <v>2081</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>2089</v>
+        <v>2093</v>
       </c>
       <c r="F17" s="13"/>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>2119</v>
+        <v>2123</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>2120</v>
+        <v>2124</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>2121</v>
+        <v>2125</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>2122</v>
+        <v>2126</v>
       </c>
       <c r="E18" s="12" t="s">
         <v>379</v>
@@ -20852,37 +20864,37 @@
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>2123</v>
+        <v>2127</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>2124</v>
+        <v>2128</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>2125</v>
+        <v>2129</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>2077</v>
+        <v>2081</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>2089</v>
+        <v>2093</v>
       </c>
       <c r="F19" s="13"/>
     </row>
     <row r="20" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>2126</v>
+        <v>2130</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>2127</v>
+        <v>2131</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>2128</v>
+        <v>2132</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>2077</v>
+        <v>2081</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>2089</v>
+        <v>2093</v>
       </c>
       <c r="F20" s="13"/>
     </row>
@@ -20917,12 +20929,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>2129</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>2130</v>
+        <v>2134</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -20932,87 +20944,87 @@
         <v>39</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>2131</v>
+        <v>2135</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>1853</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>2132</v>
+        <v>2136</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>1204</v>
+        <v>1208</v>
       </c>
       <c r="C5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>2132</v>
+        <v>2136</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>1199</v>
+        <v>1203</v>
       </c>
       <c r="C6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>2132</v>
+        <v>2136</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="C7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>2132</v>
+        <v>2136</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="C8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>2132</v>
+        <v>2136</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="C9" s="13"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>2132</v>
+        <v>2136</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>2133</v>
+        <v>2137</v>
       </c>
       <c r="C10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>2134</v>
+        <v>2138</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>1294</v>
+        <v>1298</v>
       </c>
       <c r="C11" s="13"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>2134</v>
+        <v>2138</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="C12" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>2134</v>
+        <v>2138</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>369</v>
@@ -21021,7 +21033,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>2134</v>
+        <v>2138</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>461</v>
@@ -21030,7 +21042,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>2134</v>
+        <v>2138</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>379</v>
@@ -21039,7 +21051,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>2134</v>
+        <v>2138</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>383</v>
@@ -21048,16 +21060,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>2134</v>
+        <v>2138</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>1336</v>
+        <v>1340</v>
       </c>
       <c r="C17" s="13"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>2134</v>
+        <v>2138</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>399</v>
@@ -21066,7 +21078,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>2135</v>
+        <v>2139</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>178</v>
@@ -21075,16 +21087,16 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>2135</v>
+        <v>2139</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>2136</v>
+        <v>2140</v>
       </c>
       <c r="C20" s="13"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>2135</v>
+        <v>2139</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>383</v>
@@ -21093,25 +21105,25 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>2135</v>
+        <v>2139</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>2137</v>
+        <v>2141</v>
       </c>
       <c r="C22" s="13"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>2135</v>
+        <v>2139</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>2138</v>
+        <v>2142</v>
       </c>
       <c r="C23" s="13"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>2135</v>
+        <v>2139</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>227</v>
@@ -21120,7 +21132,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>2139</v>
+        <v>2143</v>
       </c>
       <c r="B25" s="12" t="s">
         <v>890</v>
@@ -21129,188 +21141,188 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>2139</v>
+        <v>2143</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>2140</v>
+        <v>2144</v>
       </c>
       <c r="C26" s="13"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>2139</v>
+        <v>2143</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>2141</v>
+        <v>2145</v>
       </c>
       <c r="C27" s="13"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>2139</v>
+        <v>2143</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>2142</v>
+        <v>2146</v>
       </c>
       <c r="C28" s="13"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>2139</v>
+        <v>2143</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>2143</v>
+        <v>2147</v>
       </c>
       <c r="C29" s="13"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>2139</v>
+        <v>2143</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>2144</v>
+        <v>2148</v>
       </c>
       <c r="C30" s="13"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>2139</v>
+        <v>2143</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>2145</v>
+        <v>2149</v>
       </c>
       <c r="C31" s="13"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>2139</v>
+        <v>2143</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>2146</v>
+        <v>2150</v>
       </c>
       <c r="C32" s="13"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>2139</v>
+        <v>2143</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>1320</v>
+        <v>1324</v>
       </c>
       <c r="C33" s="13"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>2139</v>
+        <v>2143</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>2147</v>
+        <v>2151</v>
       </c>
       <c r="C34" s="13"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>2139</v>
+        <v>2143</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>2133</v>
+        <v>2137</v>
       </c>
       <c r="C35" s="13"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>2148</v>
+        <v>2152</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>2136</v>
+        <v>2140</v>
       </c>
       <c r="C36" s="13"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>2148</v>
+        <v>2152</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>2149</v>
+        <v>2153</v>
       </c>
       <c r="C37" s="13"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>2148</v>
+        <v>2152</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>2150</v>
+        <v>2154</v>
       </c>
       <c r="C38" s="13"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>2148</v>
+        <v>2152</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="C39" s="13"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>2148</v>
+        <v>2152</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>2151</v>
+        <v>2155</v>
       </c>
       <c r="C40" s="13"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>2148</v>
+        <v>2152</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>2152</v>
+        <v>2156</v>
       </c>
       <c r="C41" s="13"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>2148</v>
+        <v>2152</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>1272</v>
+        <v>1276</v>
       </c>
       <c r="C42" s="13"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>2153</v>
+        <v>2157</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>2154</v>
+        <v>2158</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>2155</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>2153</v>
+        <v>2157</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>2156</v>
+        <v>2160</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>2155</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>2153</v>
+        <v>2157</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>2157</v>
+        <v>2161</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>2155</v>
+        <v>2159</v>
       </c>
     </row>
   </sheetData>
@@ -21347,12 +21359,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>2158</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>2159</v>
+        <v>2163</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -21362,116 +21374,116 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>2160</v>
+        <v>2164</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>2161</v>
+        <v>2165</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>2162</v>
+        <v>2166</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>2163</v>
+        <v>2167</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>1853</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>2164</v>
+        <v>2168</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>2165</v>
+        <v>2169</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>2166</v>
+        <v>2170</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>2167</v>
+        <v>2171</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>2168</v>
+        <v>2172</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>2169</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>2170</v>
+        <v>2174</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>2171</v>
+        <v>2175</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>2172</v>
+        <v>2176</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>2173</v>
+        <v>2177</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>2174</v>
+        <v>2178</v>
       </c>
       <c r="F6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>2175</v>
+        <v>2179</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>2176</v>
+        <v>2180</v>
       </c>
       <c r="C7" s="13" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D7" s="12" t="s">
         <v>2177</v>
       </c>
-      <c r="D7" s="12" t="s">
-        <v>2173</v>
-      </c>
       <c r="E7" s="12" t="s">
-        <v>2178</v>
+        <v>2182</v>
       </c>
       <c r="F7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>2179</v>
+        <v>2183</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>2180</v>
+        <v>2184</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>2172</v>
+        <v>2176</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>2181</v>
+        <v>2185</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>2182</v>
+        <v>2186</v>
       </c>
       <c r="F8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>2183</v>
+        <v>2187</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>2184</v>
+        <v>2188</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>2185</v>
+        <v>2189</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>2186</v>
+        <v>2190</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>2187</v>
+        <v>2191</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>2188</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21479,54 +21491,54 @@
         <v>375</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>2189</v>
+        <v>2193</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>2190</v>
+        <v>2194</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>2191</v>
+        <v>2195</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>2192</v>
+        <v>2196</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>2193</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>2194</v>
+        <v>2198</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>2195</v>
+        <v>2199</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>2172</v>
+        <v>2176</v>
       </c>
       <c r="D11" s="12" t="s">
+        <v>2200</v>
+      </c>
+      <c r="E11" s="13" t="s">
         <v>2196</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>2192</v>
       </c>
       <c r="F11" s="13"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>2197</v>
+        <v>2201</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>2198</v>
+        <v>2202</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>2172</v>
+        <v>2176</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>2199</v>
+        <v>2203</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>2200</v>
+        <v>2204</v>
       </c>
       <c r="F12" s="13"/>
     </row>
@@ -21535,16 +21547,16 @@
         <v>417</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>2201</v>
+        <v>2205</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>2172</v>
+        <v>2176</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>2202</v>
+        <v>2206</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>2203</v>
+        <v>2207</v>
       </c>
       <c r="F13" s="13"/>
     </row>
@@ -21553,482 +21565,482 @@
         <v>442</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>2204</v>
+        <v>2208</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>2172</v>
+        <v>2176</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>2205</v>
+        <v>2209</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>2192</v>
+        <v>2196</v>
       </c>
       <c r="F14" s="13"/>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>2206</v>
+        <v>2210</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>2207</v>
+        <v>2211</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>2208</v>
+        <v>2212</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>2209</v>
+        <v>2213</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>2210</v>
+        <v>2214</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>2211</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>2212</v>
+        <v>2216</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>2213</v>
+        <v>2217</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>2214</v>
+        <v>2218</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>2215</v>
+        <v>2219</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>2216</v>
+        <v>2220</v>
       </c>
       <c r="F16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>2217</v>
+        <v>2221</v>
       </c>
       <c r="B17" s="12" t="s">
+        <v>2222</v>
+      </c>
+      <c r="C17" s="13" t="s">
         <v>2218</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>2214</v>
-      </c>
       <c r="D17" s="12" t="s">
-        <v>2219</v>
+        <v>2223</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>2220</v>
+        <v>2224</v>
       </c>
       <c r="F17" s="13"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>2221</v>
+        <v>2225</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>2222</v>
+        <v>2226</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>2223</v>
+        <v>2227</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>2224</v>
+        <v>2228</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>2225</v>
+        <v>2229</v>
       </c>
       <c r="F18" s="13"/>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>2226</v>
+        <v>2230</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>2227</v>
+        <v>2231</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>2228</v>
+        <v>2232</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>2229</v>
+        <v>2233</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>2230</v>
+        <v>2234</v>
       </c>
       <c r="F19" s="13"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>2231</v>
+        <v>2235</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>2232</v>
+        <v>2236</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>2172</v>
+        <v>2176</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>2233</v>
+        <v>2237</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>2234</v>
+        <v>2238</v>
       </c>
       <c r="F20" s="13"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>2235</v>
+        <v>2239</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>2172</v>
+        <v>2176</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>2237</v>
+        <v>2241</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>2238</v>
+        <v>2242</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>2239</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>2240</v>
+        <v>2244</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>2241</v>
+        <v>2245</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>2172</v>
+        <v>2176</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>2242</v>
+        <v>2246</v>
       </c>
       <c r="E22" s="13"/>
       <c r="F22" s="13"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>2243</v>
+        <v>2247</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>2244</v>
+        <v>2248</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>2185</v>
+        <v>2189</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>2245</v>
+        <v>2249</v>
       </c>
       <c r="E23" s="13"/>
       <c r="F23" s="13"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>2246</v>
+        <v>2250</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>2247</v>
+        <v>2251</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>2248</v>
+        <v>2252</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>2249</v>
+        <v>2253</v>
       </c>
       <c r="F24" s="13"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>2250</v>
+        <v>2254</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>2251</v>
+        <v>2255</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>369</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>2252</v>
+        <v>2256</v>
       </c>
       <c r="E25" s="13"/>
       <c r="F25" s="13"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>2253</v>
+        <v>2257</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>2254</v>
+        <v>2258</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>2255</v>
+        <v>2259</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>2256</v>
+        <v>2260</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>2257</v>
+        <v>2261</v>
       </c>
       <c r="F26" s="13"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>2258</v>
+        <v>2262</v>
       </c>
       <c r="B27" s="12" t="s">
+        <v>2263</v>
+      </c>
+      <c r="C27" s="13" t="s">
         <v>2259</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>2255</v>
-      </c>
       <c r="D27" s="13" t="s">
-        <v>2260</v>
+        <v>2264</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>2257</v>
+        <v>2261</v>
       </c>
       <c r="F27" s="13"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>2261</v>
+        <v>2265</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>2262</v>
+        <v>2266</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>2263</v>
+        <v>2267</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>2264</v>
+        <v>2268</v>
       </c>
       <c r="E28" s="13"/>
       <c r="F28" s="13" t="s">
-        <v>2265</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>2266</v>
+        <v>2270</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>2267</v>
+        <v>2271</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>1320</v>
+        <v>1324</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>2268</v>
+        <v>2272</v>
       </c>
       <c r="E29" s="13"/>
       <c r="F29" s="13"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>2269</v>
+        <v>2273</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>2270</v>
+        <v>2274</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>2271</v>
+        <v>2275</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>2255</v>
+        <v>2259</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>2272</v>
+        <v>2276</v>
       </c>
       <c r="F30" s="13"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>2273</v>
+        <v>2277</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>2274</v>
+        <v>2278</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>2275</v>
+        <v>2279</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>2276</v>
+        <v>2280</v>
       </c>
       <c r="E31" s="13"/>
       <c r="F31" s="13"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>2278</v>
+        <v>2282</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>2275</v>
+        <v>2279</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>2279</v>
+        <v>2283</v>
       </c>
       <c r="E32" s="13"/>
       <c r="F32" s="13"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>2280</v>
+        <v>2284</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>2281</v>
+        <v>2285</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>2275</v>
+        <v>2279</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>2282</v>
+        <v>2286</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>2283</v>
+        <v>2287</v>
       </c>
       <c r="F33" s="13"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>2284</v>
+        <v>2288</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>2285</v>
+        <v>2289</v>
       </c>
       <c r="C34" s="12" t="s">
         <v>383</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>2286</v>
+        <v>2290</v>
       </c>
       <c r="E34" s="13"/>
       <c r="F34" s="13" t="s">
-        <v>2287</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>2288</v>
+        <v>2292</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>2289</v>
+        <v>2293</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>2290</v>
+        <v>2294</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>2291</v>
+        <v>2295</v>
       </c>
       <c r="E35" s="13"/>
       <c r="F35" s="13"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>2292</v>
+        <v>2296</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>2293</v>
+        <v>2297</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>2294</v>
+        <v>2298</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>2295</v>
+        <v>2299</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>2296</v>
+        <v>2300</v>
       </c>
       <c r="F36" s="13"/>
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>2297</v>
+        <v>2301</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>2298</v>
+        <v>2302</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>2172</v>
+        <v>2176</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>2299</v>
+        <v>2303</v>
       </c>
       <c r="E37" s="13"/>
       <c r="F37" s="12" t="s">
-        <v>2300</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>2301</v>
+        <v>2305</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>2302</v>
+        <v>2306</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>2172</v>
+        <v>2176</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>2303</v>
+        <v>2307</v>
       </c>
       <c r="E38" s="13"/>
       <c r="F38" s="13"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>2304</v>
+        <v>2308</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>2305</v>
+        <v>2309</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>2172</v>
+        <v>2176</v>
       </c>
       <c r="D39" s="13"/>
       <c r="E39" s="13"/>
       <c r="F39" s="12" t="s">
-        <v>2306</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>2307</v>
+        <v>2311</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>2308</v>
+        <v>2312</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>2172</v>
+        <v>2176</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>2309</v>
+        <v>2313</v>
       </c>
       <c r="E40" s="13"/>
       <c r="F40" s="12" t="s">
-        <v>2310</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>2311</v>
+        <v>2315</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>2312</v>
+        <v>2316</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>2172</v>
+        <v>2176</v>
       </c>
       <c r="D41" s="13"/>
       <c r="E41" s="13"/>
@@ -22036,16 +22048,16 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>2313</v>
+        <v>2317</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>2314</v>
+        <v>2318</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>2172</v>
+        <v>2176</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>2315</v>
+        <v>2319</v>
       </c>
       <c r="E42" s="13"/>
       <c r="F42" s="13"/>
@@ -28259,7 +28271,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H119"/>
+  <dimension ref="A1:H120"/>
   <sheetFormatPr defaultColWidth="7.2421875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.37"/>
@@ -30867,22 +30879,44 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="12" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B119" s="12" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C119" s="12" t="s">
         <v>1101</v>
       </c>
-      <c r="B119" s="12" t="s">
+      <c r="D119" s="12" t="s">
         <v>1102</v>
       </c>
-      <c r="C119" s="13"/>
-      <c r="D119" s="13"/>
-      <c r="E119" s="13"/>
+      <c r="E119" s="12" t="s">
+        <v>1103</v>
+      </c>
       <c r="F119" s="13"/>
       <c r="G119" s="13"/>
-      <c r="H119" s="13"/>
+      <c r="H119" s="12" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="12" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B120" s="12" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C120" s="13"/>
+      <c r="D120" s="13"/>
+      <c r="E120" s="13"/>
+      <c r="F120" s="13"/>
+      <c r="G120" s="13"/>
+      <c r="H120" s="13"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H119"/>
+  <autoFilter ref="A4:H120"/>
   <mergeCells count="1">
     <mergeCell ref="A2:H2"/>
   </mergeCells>
@@ -30914,12 +30948,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -30928,161 +30962,161 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>1107</v>
+        <v>1111</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>1111</v>
+        <v>1115</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>1112</v>
+        <v>1116</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>1113</v>
+        <v>1117</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>1114</v>
+        <v>1118</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>1115</v>
+        <v>1119</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="D7" s="13"/>
       <c r="E7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="D8" s="13"/>
       <c r="E8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>1119</v>
+        <v>1123</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="D9" s="13"/>
       <c r="E9" s="13"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>1121</v>
+        <v>1125</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="D10" s="13"/>
       <c r="E10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>1122</v>
+        <v>1126</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>1123</v>
+        <v>1127</v>
       </c>
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>1125</v>
+        <v>1129</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>1126</v>
+        <v>1130</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>1127</v>
+        <v>1131</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="E13" s="13"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>1129</v>
+        <v>1133</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>1130</v>
+        <v>1134</v>
       </c>
       <c r="D14" s="13"/>
       <c r="E14" s="12" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>1132</v>
+        <v>1136</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>972</v>
@@ -31092,39 +31126,39 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>1133</v>
+        <v>1137</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>1134</v>
+        <v>1138</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>1129</v>
+        <v>1133</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>1135</v>
+        <v>1139</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>1136</v>
+        <v>1140</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="13"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>1137</v>
+        <v>1141</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>1138</v>
+        <v>1142</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="13"/>
@@ -31165,12 +31199,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1139</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>1140</v>
+        <v>1144</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -31188,74 +31222,74 @@
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>1141</v>
+        <v>1145</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1142</v>
+        <v>1146</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>1143</v>
+        <v>1147</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>1144</v>
+        <v>1148</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>1145</v>
+        <v>1149</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>1146</v>
+        <v>1150</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>1147</v>
+        <v>1151</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>1148</v>
+        <v>1152</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>1149</v>
+        <v>1153</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>1150</v>
+        <v>1154</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>1151</v>
+        <v>1155</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>1153</v>
+        <v>1157</v>
       </c>
       <c r="N4" s="10" t="s">
-        <v>1154</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>1155</v>
+        <v>1159</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>1156</v>
+        <v>1160</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="F5" s="13"/>
       <c r="G5" s="12" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="12" t="s">
-        <v>1161</v>
+        <v>1165</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="K5" s="12" t="s">
         <v>393</v>
@@ -31268,30 +31302,30 @@
     </row>
     <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>1163</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>1164</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>1157</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>1158</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>1159</v>
       </c>
       <c r="F6" s="13"/>
       <c r="G6" s="12" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="H6" s="13"/>
       <c r="I6" s="12" t="s">
-        <v>1165</v>
+        <v>1169</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="K6" s="12" t="s">
         <v>393</v>
@@ -31304,30 +31338,30 @@
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>1166</v>
+        <v>1170</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="F7" s="13"/>
       <c r="G7" s="12" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="H7" s="13"/>
       <c r="I7" s="12" t="s">
-        <v>1168</v>
+        <v>1172</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="K7" s="12" t="s">
         <v>393</v>
@@ -31340,27 +31374,27 @@
     </row>
     <row r="8" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>1169</v>
+        <v>1173</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>1170</v>
+        <v>1174</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="F8" s="13"/>
       <c r="G8" s="12" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="H8" s="13"/>
       <c r="I8" s="12" t="s">
-        <v>1161</v>
+        <v>1165</v>
       </c>
       <c r="J8" s="12" t="s">
         <v>872</v>
@@ -31372,38 +31406,38 @@
         <v>393</v>
       </c>
       <c r="M8" s="12" t="s">
-        <v>1171</v>
+        <v>1175</v>
       </c>
       <c r="N8" s="12" t="s">
-        <v>1172</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="F9" s="13"/>
       <c r="G9" s="12" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="12" t="s">
-        <v>1161</v>
+        <v>1165</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="K9" s="12" t="s">
         <v>393</v>
@@ -31413,35 +31447,35 @@
       </c>
       <c r="M9" s="13"/>
       <c r="N9" s="12" t="s">
-        <v>1172</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>1175</v>
+        <v>1179</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>1176</v>
+        <v>1180</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="F10" s="13"/>
       <c r="G10" s="12" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="H10" s="13"/>
       <c r="I10" s="12" t="s">
-        <v>1161</v>
+        <v>1165</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="K10" s="12" t="s">
         <v>393</v>
@@ -31451,35 +31485,35 @@
       </c>
       <c r="M10" s="13"/>
       <c r="N10" s="12" t="s">
-        <v>1177</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>1178</v>
+        <v>1182</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>1179</v>
+        <v>1183</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="F11" s="13"/>
       <c r="G11" s="12" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="H11" s="13"/>
       <c r="I11" s="12" t="s">
-        <v>1161</v>
+        <v>1165</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="K11" s="12" t="s">
         <v>393</v>
@@ -31489,35 +31523,35 @@
       </c>
       <c r="M11" s="13"/>
       <c r="N11" s="12" t="s">
-        <v>1180</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>1181</v>
+        <v>1185</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>1182</v>
+        <v>1186</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="F12" s="13"/>
       <c r="G12" s="12" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="H12" s="13"/>
       <c r="I12" s="12" t="s">
-        <v>1161</v>
+        <v>1165</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="K12" s="12" t="s">
         <v>393</v>
@@ -31527,35 +31561,35 @@
       </c>
       <c r="M12" s="13"/>
       <c r="N12" s="12" t="s">
-        <v>1183</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>1184</v>
+        <v>1188</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>1185</v>
+        <v>1189</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>1187</v>
+        <v>1191</v>
       </c>
       <c r="F13" s="13"/>
       <c r="G13" s="12" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="H13" s="13"/>
       <c r="I13" s="12" t="s">
-        <v>1188</v>
+        <v>1192</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="K13" s="12" t="s">
         <v>393</v>
@@ -31568,30 +31602,30 @@
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>1189</v>
+        <v>1193</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>1190</v>
+        <v>1194</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="F14" s="13"/>
       <c r="G14" s="12" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="H14" s="13"/>
       <c r="I14" s="12" t="s">
-        <v>1191</v>
+        <v>1195</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="K14" s="12" t="s">
         <v>393</v>
@@ -31604,16 +31638,16 @@
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>1193</v>
+        <v>1197</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="E15" s="13"/>
       <c r="F15" s="13"/>
@@ -31622,10 +31656,10 @@
       </c>
       <c r="H15" s="13"/>
       <c r="I15" s="12" t="s">
-        <v>1196</v>
+        <v>1200</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="K15" s="12" t="s">
         <v>393</v>
@@ -31638,30 +31672,30 @@
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>1197</v>
+        <v>1201</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>1198</v>
+        <v>1202</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>1199</v>
+        <v>1203</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="E16" s="13"/>
       <c r="F16" s="12" t="s">
-        <v>1200</v>
+        <v>1204</v>
       </c>
       <c r="G16" s="12" t="s">
         <v>138</v>
       </c>
       <c r="H16" s="13"/>
       <c r="I16" s="12" t="s">
-        <v>1201</v>
+        <v>1205</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="K16" s="12" t="s">
         <v>393</v>
@@ -31674,28 +31708,28 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>1202</v>
+        <v>1206</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>1203</v>
+        <v>1207</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>1204</v>
+        <v>1208</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="E17" s="13"/>
       <c r="F17" s="13"/>
       <c r="G17" s="12" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="H17" s="13"/>
       <c r="I17" s="12" t="s">
-        <v>1205</v>
+        <v>1209</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="K17" s="12" t="s">
         <v>393</v>
@@ -31705,33 +31739,33 @@
       </c>
       <c r="M17" s="13"/>
       <c r="N17" s="12" t="s">
-        <v>1206</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>1207</v>
+        <v>1211</v>
       </c>
       <c r="B18" s="12" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C18" s="12" t="s">
         <v>1208</v>
       </c>
-      <c r="C18" s="12" t="s">
-        <v>1204</v>
-      </c>
       <c r="D18" s="12" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="E18" s="13"/>
       <c r="F18" s="13"/>
       <c r="G18" s="12" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="H18" s="13"/>
       <c r="I18" s="12" t="s">
-        <v>1205</v>
+        <v>1209</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="K18" s="12" t="s">
         <v>393</v>
@@ -31741,33 +31775,33 @@
       </c>
       <c r="M18" s="13"/>
       <c r="N18" s="12" t="s">
-        <v>1209</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>1210</v>
+        <v>1214</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>1211</v>
+        <v>1215</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>1204</v>
+        <v>1208</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>1212</v>
+        <v>1216</v>
       </c>
       <c r="E19" s="13"/>
       <c r="F19" s="13"/>
       <c r="G19" s="12" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="H19" s="13"/>
       <c r="I19" s="12" t="s">
-        <v>1213</v>
+        <v>1217</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="K19" s="12" t="s">
         <v>393</v>
@@ -31777,35 +31811,35 @@
       </c>
       <c r="M19" s="13"/>
       <c r="N19" s="12" t="s">
-        <v>1214</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>1215</v>
+        <v>1219</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>1216</v>
+        <v>1220</v>
       </c>
       <c r="C20" s="12" t="s">
+        <v>1203</v>
+      </c>
+      <c r="D20" s="12" t="s">
         <v>1199</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>1195</v>
       </c>
       <c r="E20" s="13"/>
       <c r="F20" s="12" t="s">
-        <v>1200</v>
+        <v>1204</v>
       </c>
       <c r="G20" s="12" t="s">
         <v>138</v>
       </c>
       <c r="H20" s="13"/>
       <c r="I20" s="12" t="s">
-        <v>1217</v>
+        <v>1221</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="K20" s="12" t="s">
         <v>393</v>
@@ -31818,27 +31852,27 @@
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>1218</v>
+        <v>1222</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>1219</v>
+        <v>1223</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>1199</v>
+        <v>1203</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>1212</v>
+        <v>1216</v>
       </c>
       <c r="E21" s="13"/>
       <c r="F21" s="12" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="H21" s="13"/>
       <c r="I21" s="12" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="J21" s="12" t="s">
         <v>872</v>
@@ -31850,38 +31884,38 @@
         <v>275</v>
       </c>
       <c r="M21" s="12" t="s">
-        <v>1222</v>
+        <v>1226</v>
       </c>
       <c r="N21" s="13"/>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>1223</v>
+        <v>1227</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="F22" s="13"/>
       <c r="G22" s="12" t="s">
-        <v>1225</v>
+        <v>1229</v>
       </c>
       <c r="H22" s="13" t="s">
         <v>878</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>1226</v>
+        <v>1230</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="K22" s="12" t="s">
         <v>393</v>
@@ -31894,25 +31928,25 @@
     </row>
     <row r="23" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>1227</v>
+        <v>1231</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>1228</v>
+        <v>1232</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>1204</v>
+        <v>1208</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="E23" s="13"/>
       <c r="F23" s="13"/>
       <c r="G23" s="12" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="H23" s="13"/>
       <c r="I23" s="12" t="s">
-        <v>1205</v>
+        <v>1209</v>
       </c>
       <c r="J23" s="12" t="s">
         <v>872</v>
@@ -31924,34 +31958,34 @@
         <v>393</v>
       </c>
       <c r="M23" s="12" t="s">
-        <v>1229</v>
+        <v>1233</v>
       </c>
       <c r="N23" s="12" t="s">
-        <v>1230</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>1232</v>
+        <v>1236</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="D24" s="13"/>
       <c r="E24" s="13"/>
       <c r="F24" s="13"/>
       <c r="G24" s="12" t="s">
-        <v>1225</v>
+        <v>1229</v>
       </c>
       <c r="H24" s="13"/>
       <c r="I24" s="12" t="s">
-        <v>1233</v>
+        <v>1237</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="K24" s="12" t="s">
         <v>393</v>
@@ -31964,26 +31998,26 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>1234</v>
+        <v>1238</v>
       </c>
       <c r="B25" s="12" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C25" s="12" t="s">
         <v>1235</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>1231</v>
       </c>
       <c r="D25" s="13"/>
       <c r="E25" s="13"/>
       <c r="F25" s="13"/>
       <c r="G25" s="12" t="s">
-        <v>1225</v>
+        <v>1229</v>
       </c>
       <c r="H25" s="13"/>
       <c r="I25" s="12" t="s">
-        <v>1236</v>
+        <v>1240</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="K25" s="12" t="s">
         <v>393</v>
@@ -31993,37 +32027,37 @@
       </c>
       <c r="M25" s="13"/>
       <c r="N25" s="12" t="s">
-        <v>1237</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>1238</v>
+        <v>1242</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>1239</v>
+        <v>1243</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="F26" s="13"/>
       <c r="G26" s="12" t="s">
-        <v>1225</v>
+        <v>1229</v>
       </c>
       <c r="H26" s="13" t="s">
         <v>878</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>1240</v>
+        <v>1244</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="K26" s="12" t="s">
         <v>393</v>
@@ -32036,32 +32070,32 @@
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>1241</v>
+        <v>1245</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>1242</v>
+        <v>1246</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="F27" s="13"/>
       <c r="G27" s="12" t="s">
-        <v>1225</v>
+        <v>1229</v>
       </c>
       <c r="H27" s="13" t="s">
         <v>878</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>1243</v>
+        <v>1247</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="K27" s="12" t="s">
         <v>393</v>
@@ -32074,28 +32108,28 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>1244</v>
+        <v>1248</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>1245</v>
+        <v>1249</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>1204</v>
+        <v>1208</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="E28" s="13"/>
       <c r="F28" s="13"/>
       <c r="G28" s="12" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="H28" s="13"/>
       <c r="I28" s="12" t="s">
-        <v>1246</v>
+        <v>1250</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="K28" s="12" t="s">
         <v>393</v>
@@ -32108,16 +32142,16 @@
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>1247</v>
+        <v>1251</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>1248</v>
+        <v>1252</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="E29" s="13"/>
       <c r="F29" s="13"/>
@@ -32126,10 +32160,10 @@
       </c>
       <c r="H29" s="13"/>
       <c r="I29" s="12" t="s">
-        <v>1196</v>
+        <v>1200</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="K29" s="12" t="s">
         <v>393</v>
@@ -32139,21 +32173,21 @@
       </c>
       <c r="M29" s="13"/>
       <c r="N29" s="12" t="s">
-        <v>1249</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="E30" s="13"/>
       <c r="F30" s="13"/>
@@ -32162,10 +32196,10 @@
       </c>
       <c r="H30" s="13"/>
       <c r="I30" s="12" t="s">
-        <v>1252</v>
+        <v>1256</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="K30" s="12" t="s">
         <v>393</v>
@@ -32178,16 +32212,16 @@
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>1253</v>
+        <v>1257</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="E31" s="13"/>
       <c r="F31" s="13"/>
@@ -32196,10 +32230,10 @@
       </c>
       <c r="H31" s="13"/>
       <c r="I31" s="12" t="s">
-        <v>1196</v>
+        <v>1200</v>
       </c>
       <c r="J31" s="12" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="K31" s="12" t="s">
         <v>393</v>
@@ -32209,35 +32243,35 @@
       </c>
       <c r="M31" s="13"/>
       <c r="N31" s="12" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>1256</v>
+        <v>1260</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>1257</v>
+        <v>1261</v>
       </c>
       <c r="C32" s="12" t="s">
+        <v>1203</v>
+      </c>
+      <c r="D32" s="12" t="s">
         <v>1199</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>1195</v>
       </c>
       <c r="E32" s="13"/>
       <c r="F32" s="12" t="s">
-        <v>1200</v>
+        <v>1204</v>
       </c>
       <c r="G32" s="12" t="s">
         <v>138</v>
       </c>
       <c r="H32" s="13"/>
       <c r="I32" s="12" t="s">
-        <v>1258</v>
+        <v>1262</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="K32" s="12" t="s">
         <v>393</v>
@@ -32278,29 +32312,29 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>1260</v>
+        <v>1264</v>
       </c>
       <c r="B2" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>1261</v>
+        <v>1265</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1262</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>1263</v>
+        <v>1267</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>1264</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32308,79 +32342,79 @@
         <v>412</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>1266</v>
+        <v>1270</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>1267</v>
+        <v>1271</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>1269</v>
+        <v>1273</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>1271</v>
+        <v>1275</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>1272</v>
+        <v>1276</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>1273</v>
+        <v>1277</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>1274</v>
+        <v>1278</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>1275</v>
+        <v>1279</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32388,247 +32422,247 @@
         <v>227</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>1276</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>1277</v>
+        <v>1281</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>1278</v>
+        <v>1282</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>1279</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>1280</v>
+        <v>1284</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>1281</v>
+        <v>1285</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>1282</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>1283</v>
+        <v>1287</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>1284</v>
+        <v>1288</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>1286</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>1289</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>1290</v>
+        <v>1294</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>1291</v>
+        <v>1295</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>1292</v>
+        <v>1296</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>1293</v>
+        <v>1297</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>1294</v>
+        <v>1298</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>1295</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>1296</v>
+        <v>1300</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>1297</v>
+        <v>1301</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>1298</v>
+        <v>1302</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>1299</v>
+        <v>1303</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>1300</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>1301</v>
+        <v>1305</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>1303</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>1304</v>
+        <v>1308</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>1305</v>
+        <v>1309</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>1306</v>
+        <v>1310</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>1307</v>
+        <v>1311</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>1308</v>
+        <v>1312</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>1309</v>
+        <v>1313</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>1310</v>
+        <v>1314</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>1311</v>
+        <v>1315</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>1312</v>
+        <v>1316</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>1313</v>
+        <v>1317</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32636,31 +32670,31 @@
         <v>369</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="s">
-        <v>1314</v>
+        <v>1318</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="12" t="s">
-        <v>1315</v>
+        <v>1319</v>
       </c>
       <c r="B49" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="12" t="s">
-        <v>1316</v>
+        <v>1320</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32668,15 +32702,15 @@
         <v>399</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="12" t="s">
-        <v>1317</v>
+        <v>1321</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32684,111 +32718,111 @@
         <v>383</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="12" t="s">
-        <v>1318</v>
+        <v>1322</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="12" t="s">
-        <v>1319</v>
+        <v>1323</v>
       </c>
       <c r="B55" s="12" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="12" t="s">
-        <v>1320</v>
+        <v>1324</v>
       </c>
       <c r="B56" s="12" t="s">
-        <v>1321</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="12" t="s">
-        <v>1322</v>
+        <v>1326</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>1323</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="12" t="s">
-        <v>1324</v>
+        <v>1328</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>1323</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="12" t="s">
-        <v>1325</v>
+        <v>1329</v>
       </c>
       <c r="B59" s="12" t="s">
-        <v>1323</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="12" t="s">
-        <v>1326</v>
+        <v>1330</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>1323</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="12" t="s">
-        <v>1327</v>
+        <v>1331</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="12" t="s">
-        <v>1328</v>
+        <v>1332</v>
       </c>
       <c r="B62" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="12" t="s">
-        <v>1329</v>
+        <v>1333</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="12" t="s">
-        <v>1330</v>
+        <v>1334</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="12" t="s">
-        <v>1331</v>
+        <v>1335</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="12" t="s">
-        <v>1332</v>
+        <v>1336</v>
       </c>
       <c r="B66" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32796,71 +32830,71 @@
         <v>1062</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="12" t="s">
-        <v>1333</v>
+        <v>1337</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="12" t="s">
-        <v>1334</v>
+        <v>1338</v>
       </c>
       <c r="B69" s="12" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="12" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="B70" s="12" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="12" t="s">
-        <v>1336</v>
+        <v>1340</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="12" t="s">
-        <v>1337</v>
+        <v>1341</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="12" t="s">
-        <v>1338</v>
+        <v>1342</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="12" t="s">
-        <v>1339</v>
+        <v>1343</v>
       </c>
       <c r="B74" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="12" t="s">
-        <v>1340</v>
+        <v>1344</v>
       </c>
       <c r="B75" s="12" t="s">
-        <v>1341</v>
+        <v>1345</v>
       </c>
     </row>
   </sheetData>
@@ -32893,269 +32927,269 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1342</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>1343</v>
+        <v>1347</v>
       </c>
       <c r="B2" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>1344</v>
+        <v>1348</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1345</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>1346</v>
+        <v>1350</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>1347</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>1348</v>
+        <v>1352</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>1349</v>
+        <v>1353</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>1350</v>
+        <v>1354</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>1351</v>
+        <v>1355</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>1352</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>1353</v>
+        <v>1357</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>1352</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>1354</v>
+        <v>1358</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>1355</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>1356</v>
+        <v>1360</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>1357</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>1358</v>
+        <v>1362</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B14" s="12" t="s">
         <v>1359</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>1355</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>1362</v>
+        <v>1366</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>1363</v>
+        <v>1367</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>1352</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>1364</v>
+        <v>1368</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>1365</v>
+        <v>1369</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>1366</v>
+        <v>1370</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>1367</v>
+        <v>1371</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>1352</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>1368</v>
+        <v>1372</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>1352</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>1369</v>
+        <v>1373</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>1352</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>1370</v>
+        <v>1374</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>1355</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>1371</v>
+        <v>1375</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>1352</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>1373</v>
+        <v>1377</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>1374</v>
+        <v>1378</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>1375</v>
+        <v>1379</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>1264</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>1377</v>
+        <v>1381</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>1378</v>
+        <v>1382</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>1352</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>1379</v>
+        <v>1383</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>1341</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>1380</v>
+        <v>1384</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>1352</v>
+        <v>1356</v>
       </c>
     </row>
   </sheetData>
